--- a/data/tractor_operations.xlsx
+++ b/data/tractor_operations.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -58,102 +58,6 @@
   </si>
   <si>
     <t>Season</t>
-  </si>
-  <si>
-    <t>2025-3-1</t>
-  </si>
-  <si>
-    <t>BU892</t>
-  </si>
-  <si>
-    <t>Jimmy Mack</t>
-  </si>
-  <si>
-    <t>DG010001</t>
-  </si>
-  <si>
-    <t>Banking</t>
-  </si>
-  <si>
-    <t>2025/26</t>
-  </si>
-  <si>
-    <t>2024-9-22</t>
-  </si>
-  <si>
-    <t>KK12</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>DG4</t>
-  </si>
-  <si>
-    <t>Harrow</t>
-  </si>
-  <si>
-    <t>2025-4-1</t>
-  </si>
-  <si>
-    <t>Palanjenta</t>
-  </si>
-  <si>
-    <t>LF06005</t>
-  </si>
-  <si>
-    <t>Fertilizer delivary</t>
-  </si>
-  <si>
-    <t>2025-06-05</t>
-  </si>
-  <si>
-    <t>BR4582</t>
-  </si>
-  <si>
-    <t>P Sibale</t>
-  </si>
-  <si>
-    <t>DG11000</t>
-  </si>
-  <si>
-    <t>DG25006</t>
-  </si>
-  <si>
-    <t>Harrowing</t>
-  </si>
-  <si>
-    <t>2025-06-03</t>
-  </si>
-  <si>
-    <t>KK1049</t>
-  </si>
-  <si>
-    <t>C January</t>
-  </si>
-  <si>
-    <t>LP05005</t>
-  </si>
-  <si>
-    <t>Rigging</t>
-  </si>
-  <si>
-    <t>New plant</t>
-  </si>
-  <si>
-    <t>BU900</t>
-  </si>
-  <si>
-    <t>Itimu</t>
-  </si>
-  <si>
-    <t>DG16000</t>
-  </si>
-  <si>
-    <t>Ripping</t>
-  </si>
-  <si>
-    <t>Dry Field</t>
   </si>
   <si>
     <t>Area (ha)</t>
@@ -519,7 +423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -566,7 +470,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -579,266 +483,6 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2">
-        <v>1234</v>
-      </c>
-      <c r="G2">
-        <v>1238</v>
-      </c>
-      <c r="I2">
-        <v>15</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>1234</v>
-      </c>
-      <c r="G3">
-        <v>1236</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4">
-        <v>111049</v>
-      </c>
-      <c r="G4">
-        <v>111063</v>
-      </c>
-      <c r="H4">
-        <v>14</v>
-      </c>
-      <c r="I4">
-        <v>35</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>1234.8</v>
-      </c>
-      <c r="G5">
-        <v>1268.5</v>
-      </c>
-      <c r="H5">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="I5">
-        <v>25</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="N5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6">
-        <v>1049.3</v>
-      </c>
-      <c r="G6">
-        <v>1052.8</v>
-      </c>
-      <c r="H6">
-        <v>3.5</v>
-      </c>
-      <c r="I6">
-        <v>31</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>35</v>
-      </c>
-      <c r="J7">
-        <v>1.89</v>
-      </c>
-      <c r="K7">
-        <v>18.52</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8">
-        <v>700.8</v>
-      </c>
-      <c r="G8">
-        <v>712.3</v>
-      </c>
-      <c r="H8">
-        <v>11.5</v>
-      </c>
-      <c r="I8">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="J8">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="K8">
-        <v>7.37</v>
-      </c>
-      <c r="L8">
-        <v>2.37</v>
-      </c>
-      <c r="M8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/tractor_operations.xlsx
+++ b/data/tractor_operations.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14625" windowHeight="7590"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="88">
   <si>
     <t>Date</t>
   </si>
@@ -60,14 +60,239 @@
     <t>Season</t>
   </si>
   <si>
-    <t>Area (ha)</t>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>2024-12-01</t>
+  </si>
+  <si>
+    <t>2024-12-02</t>
+  </si>
+  <si>
+    <t>2024-12-03</t>
+  </si>
+  <si>
+    <t>2024-12-04</t>
+  </si>
+  <si>
+    <t>KK10676</t>
+  </si>
+  <si>
+    <t>J Marck</t>
+  </si>
+  <si>
+    <t>LP08009</t>
+  </si>
+  <si>
+    <t>LP08001</t>
+  </si>
+  <si>
+    <t>LF10005</t>
+  </si>
+  <si>
+    <t>LF08003</t>
+  </si>
+  <si>
+    <t>Harrowing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry field conditions </t>
+  </si>
+  <si>
+    <t>2024-12-05</t>
+  </si>
+  <si>
+    <t>2024-12-06</t>
+  </si>
+  <si>
+    <t>2024-12-07</t>
+  </si>
+  <si>
+    <t>2024-12-08</t>
+  </si>
+  <si>
+    <t>2024-12-09</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>2024-12-12</t>
+  </si>
+  <si>
+    <t>2024-12-13</t>
+  </si>
+  <si>
+    <t>2024-12-16</t>
+  </si>
+  <si>
+    <t>2024-12-17</t>
+  </si>
+  <si>
+    <t>2024-12-18</t>
+  </si>
+  <si>
+    <t>2024-12-19</t>
+  </si>
+  <si>
+    <t>2024-12-20</t>
+  </si>
+  <si>
+    <t>2024-12-21</t>
+  </si>
+  <si>
+    <t>2024-12-22</t>
+  </si>
+  <si>
+    <t>2024-12-23</t>
+  </si>
+  <si>
+    <t>2024-12-24</t>
+  </si>
+  <si>
+    <t>2024-12-25</t>
+  </si>
+  <si>
+    <t>2024-12-27</t>
+  </si>
+  <si>
+    <t>2024-12-28</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024/25</t>
+  </si>
+  <si>
+    <t>Harrowing  feeder f23</t>
+  </si>
+  <si>
+    <t>Harrowing at LF8/26</t>
+  </si>
+  <si>
+    <t>Harrowing at LP8/3</t>
+  </si>
+  <si>
+    <t>Ferti. f26/3,4,5,  f15/3,4,5,6,7,8,9</t>
+  </si>
+  <si>
+    <t>Riversand to site 4</t>
+  </si>
+  <si>
+    <t>Gravel to kayeleka compound</t>
+  </si>
+  <si>
+    <t>Fuel top up</t>
+  </si>
+  <si>
+    <t>Transport to  Mr Mayenda at Mulala</t>
+  </si>
+  <si>
+    <t>Ploughing at Mulala  D. Mayenda</t>
+  </si>
+  <si>
+    <t>Transpt. from  Mr Mayenda at Mulala</t>
+  </si>
+  <si>
+    <t>Harrowing at Mulala D. Mayenda</t>
+  </si>
+  <si>
+    <t>DG20000</t>
+  </si>
+  <si>
+    <t>DG23000</t>
+  </si>
+  <si>
+    <t>Banking replant</t>
+  </si>
+  <si>
+    <t>DG15007</t>
+  </si>
+  <si>
+    <t>Banking</t>
+  </si>
+  <si>
+    <t>DG39002</t>
+  </si>
+  <si>
+    <t>DG30007</t>
+  </si>
+  <si>
+    <t>DG30006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banking </t>
+  </si>
+  <si>
+    <t>LF08026</t>
+  </si>
+  <si>
+    <t>LP10003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ploughing </t>
+  </si>
+  <si>
+    <t>Ploughing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrowing </t>
+  </si>
+  <si>
+    <t>LP08003</t>
+  </si>
+  <si>
+    <t>DG23001</t>
+  </si>
+  <si>
+    <t>DG23002</t>
+  </si>
+  <si>
+    <t>DG23003</t>
+  </si>
+  <si>
+    <t>DG23004</t>
+  </si>
+  <si>
+    <t>DG23005</t>
+  </si>
+  <si>
+    <t>DG23006</t>
+  </si>
+  <si>
+    <t>DG23007</t>
+  </si>
+  <si>
+    <t>DG21001</t>
+  </si>
+  <si>
+    <t>DG21002</t>
+  </si>
+  <si>
+    <t>DG26000</t>
+  </si>
+  <si>
+    <t>Towing KK2929 at f26</t>
+  </si>
+  <si>
+    <t>DG28000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,7 +303,17 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -113,16 +348,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -181,7 +420,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -213,9 +452,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,6 +487,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -423,21 +664,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -485,7 +727,1827 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2">
+        <v>895</v>
+      </c>
+      <c r="G2">
+        <v>904</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
+      </c>
+      <c r="I2">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2.95</v>
+      </c>
+      <c r="K2" s="3">
+        <v>4.0677966101694913</v>
+      </c>
+      <c r="L2" s="3">
+        <v>3.0508474576271185</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>904</v>
+      </c>
+      <c r="G3">
+        <v>913</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>145</v>
+      </c>
+      <c r="J3" s="2">
+        <v>2.89</v>
+      </c>
+      <c r="K3" s="3">
+        <v>50.173010380622834</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3.1141868512110724</v>
+      </c>
+      <c r="N3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>913</v>
+      </c>
+      <c r="G4">
+        <v>920</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>48</v>
+      </c>
+      <c r="J4" s="2">
+        <v>2.12</v>
+      </c>
+      <c r="K4" s="3">
+        <v>22.641509433962263</v>
+      </c>
+      <c r="L4" s="3">
+        <v>3.3018867924528301</v>
+      </c>
+      <c r="N4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>920</v>
+      </c>
+      <c r="G5">
+        <v>927</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="K5" s="3">
+        <v>21.212121212121215</v>
+      </c>
+      <c r="L5" s="3">
+        <v>4.2424242424242422</v>
+      </c>
+      <c r="N5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6">
+        <v>927</v>
+      </c>
+      <c r="G6">
+        <v>936</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>120</v>
+      </c>
+      <c r="J6" s="2">
+        <v>12</v>
+      </c>
+      <c r="K6" s="3">
+        <v>10</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="N6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7">
+        <v>936</v>
+      </c>
+      <c r="G7">
+        <v>944</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="J7" s="2">
+        <v>11.138999999999999</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3">
+        <v>0.71819732471496545</v>
+      </c>
+      <c r="N7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8">
+        <v>944</v>
+      </c>
+      <c r="G8">
+        <v>945</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>69</v>
+      </c>
+      <c r="J8" s="2">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="K8" s="3">
+        <v>22.802379378717781</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.33046926635822871</v>
+      </c>
+      <c r="N8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9">
+        <v>945</v>
+      </c>
+      <c r="G9">
+        <v>948</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3">
+        <v>0.99140779907468612</v>
+      </c>
+      <c r="N9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <v>948</v>
+      </c>
+      <c r="G10">
+        <v>949</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="N10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11">
+        <v>949</v>
+      </c>
+      <c r="G11">
+        <v>952</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
+        <v>35</v>
+      </c>
+      <c r="J11" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K11" s="3">
+        <v>15.909090909090908</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1.3636363636363635</v>
+      </c>
+      <c r="N11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12">
+        <v>952</v>
+      </c>
+      <c r="G12">
+        <v>953</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.33322225924691773</v>
+      </c>
+      <c r="N12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13">
+        <v>953</v>
+      </c>
+      <c r="G13">
+        <v>959</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.248</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3">
+        <v>4.8076923076923075</v>
+      </c>
+      <c r="N13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>959</v>
+      </c>
+      <c r="G14">
+        <v>963</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="K14" s="3">
+        <v>78.740157480314963</v>
+      </c>
+      <c r="L14" s="3">
+        <v>3.1496062992125982</v>
+      </c>
+      <c r="N14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15">
+        <v>963</v>
+      </c>
+      <c r="G15">
+        <v>966</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3">
+        <v>2.3622047244094486</v>
+      </c>
+      <c r="N15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>966</v>
+      </c>
+      <c r="G16">
+        <v>967</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="N16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>967</v>
+      </c>
+      <c r="G17">
+        <v>970</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="N17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
+        <v>970</v>
+      </c>
+      <c r="G18">
+        <v>975</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1.23</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3">
+        <v>4.0650406504065044</v>
+      </c>
+      <c r="N18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19">
+        <v>975</v>
+      </c>
+      <c r="G19">
+        <v>978</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
+        <v>153</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="K19" s="3">
+        <v>50.362080315997368</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0.9874917709019092</v>
+      </c>
+      <c r="N19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20">
+        <v>978</v>
+      </c>
+      <c r="G20">
+        <v>981</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="J20" s="2">
+        <v>3.0249999999999999</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3">
+        <v>0.99173553719008267</v>
+      </c>
+      <c r="N20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21">
+        <v>981</v>
+      </c>
+      <c r="G21">
+        <v>984</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="J21" s="2">
+        <v>3.03</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3">
+        <v>0.9900990099009902</v>
+      </c>
+      <c r="N21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22">
+        <v>984</v>
+      </c>
+      <c r="G22">
+        <v>987</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="J22" s="2">
+        <v>3.03</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3">
+        <v>0.9900990099009902</v>
+      </c>
+      <c r="N22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23">
+        <v>987</v>
+      </c>
+      <c r="G23">
+        <v>990</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="J23" s="2">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3">
+        <v>0.99833610648918469</v>
+      </c>
+      <c r="N23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24">
+        <v>990</v>
+      </c>
+      <c r="G24">
+        <v>993</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="J24" s="2">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3">
+        <v>0.99634672866157414</v>
+      </c>
+      <c r="N24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25">
+        <v>993</v>
+      </c>
+      <c r="G25">
+        <v>995</v>
+      </c>
+      <c r="H25">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3">
+        <v>1.9782393669634029</v>
+      </c>
+      <c r="N25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26">
+        <v>995</v>
+      </c>
+      <c r="G26">
+        <v>998</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>48</v>
+      </c>
+      <c r="J26" s="2">
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="K26" s="3">
+        <v>15.717092337917487</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0.98231827111984293</v>
+      </c>
+      <c r="N26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+      <c r="F27">
+        <v>998</v>
+      </c>
+      <c r="G27">
+        <v>1000</v>
+      </c>
+      <c r="H27">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2">
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3">
+        <v>0.65466448445171843</v>
+      </c>
+      <c r="N27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28">
+        <v>1000</v>
+      </c>
+      <c r="G28">
+        <v>1001</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="N28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29">
+        <v>1001</v>
+      </c>
+      <c r="G29">
+        <v>1002</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="N29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30">
+        <v>1002</v>
+      </c>
+      <c r="G30">
+        <v>1006</v>
+      </c>
+      <c r="H30">
+        <v>4</v>
+      </c>
+      <c r="J30" s="2">
+        <v>3.016</v>
+      </c>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3">
+        <v>1.3262599469496021</v>
+      </c>
+      <c r="N30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" t="s">
+        <v>63</v>
+      </c>
+      <c r="F31">
+        <v>1006</v>
+      </c>
+      <c r="G31">
+        <v>1009</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
+      </c>
+      <c r="I31">
+        <v>80</v>
+      </c>
+      <c r="J31" s="2">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="K31" s="3">
+        <v>26.42880740006607</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0.99108027750247762</v>
+      </c>
+      <c r="N31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32">
+        <v>1009</v>
+      </c>
+      <c r="G32">
+        <v>1012</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="N32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33">
+        <v>1012</v>
+      </c>
+      <c r="G33">
+        <v>1016</v>
+      </c>
+      <c r="H33">
+        <v>4</v>
+      </c>
+      <c r="J33" s="2">
+        <v>3.024</v>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3">
+        <v>1.3227513227513228</v>
+      </c>
+      <c r="N33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>87</v>
+      </c>
+      <c r="E34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34">
+        <v>1016</v>
+      </c>
+      <c r="G34">
+        <v>1019</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="J34" s="2">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3">
+        <v>0.99108027750247762</v>
+      </c>
+      <c r="N34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F35">
+        <v>1019</v>
+      </c>
+      <c r="G35">
+        <v>1020</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="N35" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36">
+        <v>1020</v>
+      </c>
+      <c r="G36">
+        <v>1022</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="N36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37">
+        <v>1022</v>
+      </c>
+      <c r="G37">
+        <v>1022</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>50</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="N37" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" t="s">
+        <v>63</v>
+      </c>
+      <c r="F38">
+        <v>1022</v>
+      </c>
+      <c r="G38">
+        <v>1026</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3.0270000000000001</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3">
+        <v>1.3214403700033035</v>
+      </c>
+      <c r="N38" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+      <c r="E39" t="s">
+        <v>63</v>
+      </c>
+      <c r="F39">
+        <v>1026</v>
+      </c>
+      <c r="G39">
+        <v>1027</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="2">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3">
+        <v>0.33189512114171921</v>
+      </c>
+      <c r="N39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" t="s">
+        <v>63</v>
+      </c>
+      <c r="F40">
+        <v>1027</v>
+      </c>
+      <c r="G40">
+        <v>1034</v>
+      </c>
+      <c r="H40">
+        <v>7</v>
+      </c>
+      <c r="J40" s="2">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3">
+        <v>2.3310023310023311</v>
+      </c>
+      <c r="N40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>66</v>
+      </c>
+      <c r="E41" t="s">
+        <v>63</v>
+      </c>
+      <c r="F41">
+        <v>1034</v>
+      </c>
+      <c r="G41">
+        <v>1036</v>
+      </c>
+      <c r="H41">
+        <v>2</v>
+      </c>
+      <c r="J41" s="2">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3">
+        <v>0.66093853271645742</v>
+      </c>
+      <c r="N41" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42">
+        <v>1036</v>
+      </c>
+      <c r="G42">
+        <v>1036.5</v>
+      </c>
+      <c r="H42">
+        <v>0.5</v>
+      </c>
+      <c r="J42" s="2">
+        <v>3.0259999999999998</v>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3">
+        <v>0.16523463317911435</v>
+      </c>
+      <c r="N42" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43">
+        <v>1036.5</v>
+      </c>
+      <c r="G43">
+        <v>1041.5</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44">
+        <v>1041.5</v>
+      </c>
+      <c r="G44">
+        <v>1042</v>
+      </c>
+      <c r="H44">
+        <v>0.5</v>
+      </c>
+      <c r="J44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>60</v>
+      </c>
+      <c r="F45">
+        <v>1042</v>
+      </c>
+      <c r="G45">
+        <v>1045</v>
+      </c>
+      <c r="H45">
+        <v>3</v>
+      </c>
+      <c r="J45" s="2">
+        <v>0</v>
+      </c>
+      <c r="N45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
+        <v>57</v>
+      </c>
+      <c r="F46">
+        <v>1045</v>
+      </c>
+      <c r="G46">
+        <v>1045.5</v>
+      </c>
+      <c r="H46">
+        <v>0.5</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0</v>
+      </c>
+      <c r="N46" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47">
+        <v>1045.5</v>
+      </c>
+      <c r="G47">
+        <v>1046</v>
+      </c>
+      <c r="H47">
+        <v>0.5</v>
+      </c>
+      <c r="J47" s="2">
+        <v>0</v>
+      </c>
+      <c r="N47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N56" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N57" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N58" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N59" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N60" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N61" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N62" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N63" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N64" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N65" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N66" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N67" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N68" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N69" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N70" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N71" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N72" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N73" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N74" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N75" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N76" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N78" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N80" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/tractor_operations.xlsx
+++ b/data/tractor_operations.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="616">
   <si>
     <t>Date</t>
   </si>
@@ -1426,12 +1426,456 @@
   </si>
   <si>
     <t>LP06005</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road  f16</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road f27</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road f04</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road f25</t>
+  </si>
+  <si>
+    <t>Ferrying push bike from Dwangwa to m/stores</t>
+  </si>
+  <si>
+    <t>Gleaning f16</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f11 harvesting</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road f11</t>
+  </si>
+  <si>
+    <t>Ferrying fertilizer from Illovo to main stores</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/8</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/9</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f25/5,6</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/10</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f31 harvesting</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road f31</t>
+  </si>
+  <si>
+    <t>Water bowser to f27 harvesting</t>
+  </si>
+  <si>
+    <t>Harvesting</t>
+  </si>
+  <si>
+    <t>DG27000</t>
+  </si>
+  <si>
+    <t>DG16000</t>
+  </si>
+  <si>
+    <t>DG25000</t>
+  </si>
+  <si>
+    <t>DG11000</t>
+  </si>
+  <si>
+    <t>Gleaning</t>
+  </si>
+  <si>
+    <t>Road maintenance</t>
+  </si>
+  <si>
+    <t>Middle bursting</t>
+  </si>
+  <si>
+    <t>DG11008</t>
+  </si>
+  <si>
+    <t>DG11009</t>
+  </si>
+  <si>
+    <t>DG11010</t>
+  </si>
+  <si>
+    <t>DG31000</t>
+  </si>
+  <si>
+    <t>2025-05-7</t>
+  </si>
+  <si>
+    <t>2025-05-9</t>
+  </si>
+  <si>
+    <t>2025-05-10</t>
+  </si>
+  <si>
+    <t>2025-05-12</t>
+  </si>
+  <si>
+    <t>2025-05-14</t>
+  </si>
+  <si>
+    <t>2025-05-15</t>
+  </si>
+  <si>
+    <t>2025-05-16</t>
+  </si>
+  <si>
+    <t>2025-05-18</t>
+  </si>
+  <si>
+    <t>2025-05-19</t>
+  </si>
+  <si>
+    <t>2025-05-20</t>
+  </si>
+  <si>
+    <t>2025-05-21</t>
+  </si>
+  <si>
+    <t>2025-05-22</t>
+  </si>
+  <si>
+    <t>2025-05-26</t>
+  </si>
+  <si>
+    <t>2025-05-27</t>
+  </si>
+  <si>
+    <t>2025-05-28</t>
+  </si>
+  <si>
+    <t>2025-05-29</t>
+  </si>
+  <si>
+    <t>2025-05-30</t>
+  </si>
+  <si>
+    <t>2025-05-31</t>
+  </si>
+  <si>
+    <t>Ferying  waterbowsery f25 harvesting</t>
+  </si>
+  <si>
+    <t>Ferying  waterbowsery f16 harvesting</t>
+  </si>
+  <si>
+    <t>Ferying  waterbowsery f11 harvesting</t>
+  </si>
+  <si>
+    <t>KK 10676</t>
+  </si>
+  <si>
+    <t>Ferrying gravel for f4 haulage road</t>
+  </si>
+  <si>
+    <t>Middle bursting f16 trust</t>
+  </si>
+  <si>
+    <t>Middle bursting f25/5</t>
+  </si>
+  <si>
+    <t>Middle bursting f25/6</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/1</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/2</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/3</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/4</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/5</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/6</t>
+  </si>
+  <si>
+    <t>Middle bursting f11/7</t>
+  </si>
+  <si>
+    <t>Ploughing f27</t>
+  </si>
+  <si>
+    <t>Ripping</t>
+  </si>
+  <si>
+    <t>DG25005</t>
+  </si>
+  <si>
+    <t>DG25006</t>
+  </si>
+  <si>
+    <t>DG11001</t>
+  </si>
+  <si>
+    <t>DG11002</t>
+  </si>
+  <si>
+    <t>DG11003</t>
+  </si>
+  <si>
+    <t>DG11004</t>
+  </si>
+  <si>
+    <t>DG11005</t>
+  </si>
+  <si>
+    <t>DG11006</t>
+  </si>
+  <si>
+    <t>DG11007</t>
+  </si>
+  <si>
+    <t>DG27001</t>
+  </si>
+  <si>
+    <t>DG27002</t>
+  </si>
+  <si>
+    <t>DG27003</t>
+  </si>
+  <si>
+    <t>DG27004</t>
+  </si>
+  <si>
+    <t>Middle busting f11/11</t>
+  </si>
+  <si>
+    <t>Middle busting f11/12</t>
+  </si>
+  <si>
+    <t>Gleaning f31/8</t>
+  </si>
+  <si>
+    <t>Middle busting f11/13</t>
+  </si>
+  <si>
+    <t>Middle busting f11/14</t>
+  </si>
+  <si>
+    <t>Middle busting f11/15</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/1,2,3,4</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road ( main avenue)</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/5,6,7,8</t>
+  </si>
+  <si>
+    <t>Ferrying gravel at the main office</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f16 gap filling</t>
+  </si>
+  <si>
+    <t>Top soil to f27 low spot area</t>
+  </si>
+  <si>
+    <t>Gravel to chawala for road maintenance</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f25/5,6 gap filling</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/9,10,11,12</t>
+  </si>
+  <si>
+    <t>Transporting poles for field office Car park</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/13,14,15</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f1/1,2,3</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f25/6 gap filling</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f32 harvesting</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road  f32</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road  f31</t>
+  </si>
+  <si>
+    <t>Gleaning f9</t>
+  </si>
+  <si>
+    <t>Tine cultivation f1/7</t>
+  </si>
+  <si>
+    <t>Gravel for haulage road  f37</t>
+  </si>
+  <si>
+    <t>Top soil to f4 low spot area</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f27 for  replanting</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f4/4,5,6</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f4 for  replanting</t>
+  </si>
+  <si>
+    <t>Water bowser to f31 harvesting</t>
+  </si>
+  <si>
+    <t>DG11011</t>
+  </si>
+  <si>
+    <t>DG11012</t>
+  </si>
+  <si>
+    <t>DG11013</t>
+  </si>
+  <si>
+    <t>DG11014</t>
+  </si>
+  <si>
+    <t>DG11015</t>
+  </si>
+  <si>
+    <t>DG31008</t>
+  </si>
+  <si>
+    <t>DG01000</t>
+  </si>
+  <si>
+    <t>Water bowser to f1 harvesting</t>
+  </si>
+  <si>
+    <t>Top soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top soil </t>
+  </si>
+  <si>
+    <t>DG32000</t>
+  </si>
+  <si>
+    <t>DG37000</t>
+  </si>
+  <si>
+    <t>DG01007</t>
+  </si>
+  <si>
+    <t>2025-06-1</t>
+  </si>
+  <si>
+    <t>2025-06-2</t>
+  </si>
+  <si>
+    <t>2025-06-3</t>
+  </si>
+  <si>
+    <t>2025-06-4</t>
+  </si>
+  <si>
+    <t>2025-06-5</t>
+  </si>
+  <si>
+    <t>2025-06-6</t>
+  </si>
+  <si>
+    <t>2025-06-7</t>
+  </si>
+  <si>
+    <t>2025-06-8</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>2025-06-11</t>
+  </si>
+  <si>
+    <t>2025-06-12</t>
+  </si>
+  <si>
+    <t>2025-06-13</t>
+  </si>
+  <si>
+    <t>2025-06-14</t>
+  </si>
+  <si>
+    <t>2025-06-15</t>
+  </si>
+  <si>
+    <t>2025-06-16</t>
+  </si>
+  <si>
+    <t>2025-06-17</t>
+  </si>
+  <si>
+    <t>2025-06-18</t>
+  </si>
+  <si>
+    <t>2025-06-19</t>
+  </si>
+  <si>
+    <t>2025-06-20</t>
+  </si>
+  <si>
+    <t>2025-06-21</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>2025-06-23</t>
+  </si>
+  <si>
+    <t>2025-06-24</t>
+  </si>
+  <si>
+    <t>2025-06-26</t>
+  </si>
+  <si>
+    <t>2025-06-27</t>
+  </si>
+  <si>
+    <t>2025-06-28</t>
+  </si>
+  <si>
+    <t>2025-06-29</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1481,11 +1925,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1788,10 +2233,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N352"/>
+  <dimension ref="A1:N441"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -17138,6 +17585,3889 @@
         <v>413</v>
       </c>
     </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>497</v>
+      </c>
+      <c r="B353" t="s">
+        <v>15</v>
+      </c>
+      <c r="C353" t="s">
+        <v>16</v>
+      </c>
+      <c r="D353" t="s">
+        <v>486</v>
+      </c>
+      <c r="E353" t="s">
+        <v>485</v>
+      </c>
+      <c r="F353">
+        <v>2172</v>
+      </c>
+      <c r="G353">
+        <v>2176</v>
+      </c>
+      <c r="H353">
+        <v>4</v>
+      </c>
+      <c r="I353">
+        <v>0</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>0</v>
+      </c>
+      <c r="L353">
+        <v>0</v>
+      </c>
+      <c r="M353" t="s">
+        <v>484</v>
+      </c>
+      <c r="N353" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>498</v>
+      </c>
+      <c r="B354" t="s">
+        <v>15</v>
+      </c>
+      <c r="C354" t="s">
+        <v>16</v>
+      </c>
+      <c r="D354" t="s">
+        <v>487</v>
+      </c>
+      <c r="E354" t="s">
+        <v>491</v>
+      </c>
+      <c r="F354">
+        <v>2176</v>
+      </c>
+      <c r="G354">
+        <v>2178</v>
+      </c>
+      <c r="H354">
+        <v>2</v>
+      </c>
+      <c r="I354">
+        <v>40</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+      <c r="M354" t="s">
+        <v>469</v>
+      </c>
+      <c r="N354" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>501</v>
+      </c>
+      <c r="B355" t="s">
+        <v>15</v>
+      </c>
+      <c r="C355" t="s">
+        <v>16</v>
+      </c>
+      <c r="D355" t="s">
+        <v>486</v>
+      </c>
+      <c r="E355" t="s">
+        <v>491</v>
+      </c>
+      <c r="F355">
+        <v>2178</v>
+      </c>
+      <c r="G355">
+        <v>2184</v>
+      </c>
+      <c r="H355">
+        <v>6</v>
+      </c>
+      <c r="I355">
+        <v>0</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>0</v>
+      </c>
+      <c r="M355" t="s">
+        <v>470</v>
+      </c>
+      <c r="N355" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>502</v>
+      </c>
+      <c r="B356" t="s">
+        <v>15</v>
+      </c>
+      <c r="C356" t="s">
+        <v>16</v>
+      </c>
+      <c r="D356" t="s">
+        <v>278</v>
+      </c>
+      <c r="E356" t="s">
+        <v>491</v>
+      </c>
+      <c r="F356">
+        <v>2184</v>
+      </c>
+      <c r="G356">
+        <v>2185</v>
+      </c>
+      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="I356">
+        <v>0</v>
+      </c>
+      <c r="J356">
+        <v>0</v>
+      </c>
+      <c r="K356">
+        <v>0</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+      <c r="M356" t="s">
+        <v>471</v>
+      </c>
+      <c r="N356" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>503</v>
+      </c>
+      <c r="B357" t="s">
+        <v>15</v>
+      </c>
+      <c r="C357" t="s">
+        <v>16</v>
+      </c>
+      <c r="D357" t="s">
+        <v>488</v>
+      </c>
+      <c r="E357" t="s">
+        <v>491</v>
+      </c>
+      <c r="F357">
+        <v>2185</v>
+      </c>
+      <c r="G357">
+        <v>2190</v>
+      </c>
+      <c r="H357">
+        <v>5</v>
+      </c>
+      <c r="I357">
+        <v>40</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>0</v>
+      </c>
+      <c r="L357">
+        <v>0</v>
+      </c>
+      <c r="M357" t="s">
+        <v>472</v>
+      </c>
+      <c r="N357" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>505</v>
+      </c>
+      <c r="B358" t="s">
+        <v>15</v>
+      </c>
+      <c r="C358" t="s">
+        <v>16</v>
+      </c>
+      <c r="E358" t="s">
+        <v>17</v>
+      </c>
+      <c r="F358">
+        <v>2190</v>
+      </c>
+      <c r="G358">
+        <v>2194</v>
+      </c>
+      <c r="H358">
+        <v>4</v>
+      </c>
+      <c r="I358">
+        <v>0</v>
+      </c>
+      <c r="J358">
+        <v>0</v>
+      </c>
+      <c r="K358">
+        <v>0</v>
+      </c>
+      <c r="L358">
+        <v>0</v>
+      </c>
+      <c r="M358" t="s">
+        <v>473</v>
+      </c>
+      <c r="N358" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>507</v>
+      </c>
+      <c r="B359" t="s">
+        <v>15</v>
+      </c>
+      <c r="C359" t="s">
+        <v>16</v>
+      </c>
+      <c r="D359" t="s">
+        <v>487</v>
+      </c>
+      <c r="E359" t="s">
+        <v>490</v>
+      </c>
+      <c r="F359">
+        <v>2194</v>
+      </c>
+      <c r="G359">
+        <v>2196</v>
+      </c>
+      <c r="H359">
+        <v>2</v>
+      </c>
+      <c r="I359">
+        <v>0</v>
+      </c>
+      <c r="J359">
+        <v>0</v>
+      </c>
+      <c r="K359">
+        <v>0</v>
+      </c>
+      <c r="L359">
+        <v>0</v>
+      </c>
+      <c r="M359" t="s">
+        <v>474</v>
+      </c>
+      <c r="N359" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>508</v>
+      </c>
+      <c r="B360" t="s">
+        <v>15</v>
+      </c>
+      <c r="C360" t="s">
+        <v>16</v>
+      </c>
+      <c r="D360" t="s">
+        <v>489</v>
+      </c>
+      <c r="E360" t="s">
+        <v>485</v>
+      </c>
+      <c r="F360">
+        <v>2196</v>
+      </c>
+      <c r="G360">
+        <v>2198</v>
+      </c>
+      <c r="H360">
+        <v>2</v>
+      </c>
+      <c r="I360">
+        <v>0</v>
+      </c>
+      <c r="J360">
+        <v>0</v>
+      </c>
+      <c r="K360">
+        <v>0</v>
+      </c>
+      <c r="L360">
+        <v>0</v>
+      </c>
+      <c r="M360" t="s">
+        <v>475</v>
+      </c>
+      <c r="N360" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>508</v>
+      </c>
+      <c r="B361" t="s">
+        <v>15</v>
+      </c>
+      <c r="C361" t="s">
+        <v>16</v>
+      </c>
+      <c r="D361" t="s">
+        <v>489</v>
+      </c>
+      <c r="E361" t="s">
+        <v>485</v>
+      </c>
+      <c r="F361">
+        <v>2198</v>
+      </c>
+      <c r="G361">
+        <v>2199</v>
+      </c>
+      <c r="H361">
+        <v>1</v>
+      </c>
+      <c r="I361">
+        <v>0</v>
+      </c>
+      <c r="J361">
+        <v>0</v>
+      </c>
+      <c r="K361">
+        <v>0</v>
+      </c>
+      <c r="L361">
+        <v>0</v>
+      </c>
+      <c r="M361" t="s">
+        <v>475</v>
+      </c>
+      <c r="N361" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>509</v>
+      </c>
+      <c r="B362" t="s">
+        <v>15</v>
+      </c>
+      <c r="C362" t="s">
+        <v>16</v>
+      </c>
+      <c r="D362" t="s">
+        <v>489</v>
+      </c>
+      <c r="E362" t="s">
+        <v>491</v>
+      </c>
+      <c r="F362">
+        <v>2199</v>
+      </c>
+      <c r="G362">
+        <v>2203</v>
+      </c>
+      <c r="H362">
+        <v>4</v>
+      </c>
+      <c r="I362">
+        <v>0</v>
+      </c>
+      <c r="J362">
+        <v>0</v>
+      </c>
+      <c r="K362">
+        <v>0</v>
+      </c>
+      <c r="L362">
+        <v>0</v>
+      </c>
+      <c r="M362" t="s">
+        <v>476</v>
+      </c>
+      <c r="N362" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>510</v>
+      </c>
+      <c r="B363" t="s">
+        <v>15</v>
+      </c>
+      <c r="C363" t="s">
+        <v>16</v>
+      </c>
+      <c r="D363" t="s">
+        <v>489</v>
+      </c>
+      <c r="E363" t="s">
+        <v>491</v>
+      </c>
+      <c r="F363">
+        <v>2203</v>
+      </c>
+      <c r="G363">
+        <v>2205</v>
+      </c>
+      <c r="H363">
+        <v>2</v>
+      </c>
+      <c r="I363">
+        <v>0</v>
+      </c>
+      <c r="J363">
+        <v>0</v>
+      </c>
+      <c r="K363">
+        <v>0</v>
+      </c>
+      <c r="L363">
+        <v>0</v>
+      </c>
+      <c r="M363" t="s">
+        <v>476</v>
+      </c>
+      <c r="N363" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>510</v>
+      </c>
+      <c r="B364" t="s">
+        <v>15</v>
+      </c>
+      <c r="C364" t="s">
+        <v>16</v>
+      </c>
+      <c r="E364" t="s">
+        <v>215</v>
+      </c>
+      <c r="F364">
+        <v>2205</v>
+      </c>
+      <c r="G364">
+        <v>2206</v>
+      </c>
+      <c r="H364">
+        <v>1</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+      <c r="J364">
+        <v>0</v>
+      </c>
+      <c r="K364">
+        <v>0</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+      <c r="M364" t="s">
+        <v>477</v>
+      </c>
+      <c r="N364" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>511</v>
+      </c>
+      <c r="B365" t="s">
+        <v>15</v>
+      </c>
+      <c r="C365" t="s">
+        <v>16</v>
+      </c>
+      <c r="E365" t="s">
+        <v>215</v>
+      </c>
+      <c r="F365">
+        <v>2206</v>
+      </c>
+      <c r="G365">
+        <v>2209</v>
+      </c>
+      <c r="H365">
+        <v>3</v>
+      </c>
+      <c r="I365">
+        <v>0</v>
+      </c>
+      <c r="J365">
+        <v>0</v>
+      </c>
+      <c r="K365">
+        <v>0</v>
+      </c>
+      <c r="L365">
+        <v>0</v>
+      </c>
+      <c r="M365" t="s">
+        <v>477</v>
+      </c>
+      <c r="N365" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>512</v>
+      </c>
+      <c r="B366" t="s">
+        <v>15</v>
+      </c>
+      <c r="C366" t="s">
+        <v>16</v>
+      </c>
+      <c r="D366" t="s">
+        <v>493</v>
+      </c>
+      <c r="E366" t="s">
+        <v>492</v>
+      </c>
+      <c r="F366">
+        <v>2209</v>
+      </c>
+      <c r="G366">
+        <v>2212</v>
+      </c>
+      <c r="H366">
+        <v>3</v>
+      </c>
+      <c r="I366">
+        <v>0</v>
+      </c>
+      <c r="J366">
+        <v>3.1</v>
+      </c>
+      <c r="K366">
+        <v>0</v>
+      </c>
+      <c r="L366">
+        <v>1.03</v>
+      </c>
+      <c r="M366" t="s">
+        <v>478</v>
+      </c>
+      <c r="N366" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>512</v>
+      </c>
+      <c r="B367" t="s">
+        <v>15</v>
+      </c>
+      <c r="C367" t="s">
+        <v>16</v>
+      </c>
+      <c r="D367" t="s">
+        <v>494</v>
+      </c>
+      <c r="E367" t="s">
+        <v>492</v>
+      </c>
+      <c r="F367">
+        <v>2212</v>
+      </c>
+      <c r="G367">
+        <v>2214</v>
+      </c>
+      <c r="H367">
+        <v>2</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>3</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>1.5</v>
+      </c>
+      <c r="M367" t="s">
+        <v>479</v>
+      </c>
+      <c r="N367" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>513</v>
+      </c>
+      <c r="B368" t="s">
+        <v>15</v>
+      </c>
+      <c r="C368" t="s">
+        <v>16</v>
+      </c>
+      <c r="D368" t="s">
+        <v>488</v>
+      </c>
+      <c r="E368" t="s">
+        <v>43</v>
+      </c>
+      <c r="F368">
+        <v>2214</v>
+      </c>
+      <c r="G368">
+        <v>2216</v>
+      </c>
+      <c r="H368">
+        <v>2</v>
+      </c>
+      <c r="I368">
+        <v>72</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368">
+        <v>0</v>
+      </c>
+      <c r="L368">
+        <v>0</v>
+      </c>
+      <c r="M368" t="s">
+        <v>480</v>
+      </c>
+      <c r="N368" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>513</v>
+      </c>
+      <c r="B369" t="s">
+        <v>15</v>
+      </c>
+      <c r="C369" t="s">
+        <v>16</v>
+      </c>
+      <c r="D369" t="s">
+        <v>495</v>
+      </c>
+      <c r="E369" t="s">
+        <v>492</v>
+      </c>
+      <c r="F369">
+        <v>2216</v>
+      </c>
+      <c r="G369">
+        <v>2219</v>
+      </c>
+      <c r="H369">
+        <v>3</v>
+      </c>
+      <c r="I369">
+        <v>0</v>
+      </c>
+      <c r="J369">
+        <v>3.1</v>
+      </c>
+      <c r="K369">
+        <v>0</v>
+      </c>
+      <c r="L369">
+        <v>1.03</v>
+      </c>
+      <c r="M369" t="s">
+        <v>481</v>
+      </c>
+      <c r="N369" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>513</v>
+      </c>
+      <c r="B370" t="s">
+        <v>15</v>
+      </c>
+      <c r="C370" t="s">
+        <v>16</v>
+      </c>
+      <c r="D370" t="s">
+        <v>496</v>
+      </c>
+      <c r="E370" t="s">
+        <v>485</v>
+      </c>
+      <c r="F370">
+        <v>2219</v>
+      </c>
+      <c r="G370">
+        <v>2223</v>
+      </c>
+      <c r="H370">
+        <v>4</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370">
+        <v>0</v>
+      </c>
+      <c r="L370">
+        <v>0</v>
+      </c>
+      <c r="M370" t="s">
+        <v>482</v>
+      </c>
+      <c r="N370" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>514</v>
+      </c>
+      <c r="B371" t="s">
+        <v>15</v>
+      </c>
+      <c r="C371" t="s">
+        <v>16</v>
+      </c>
+      <c r="D371" t="s">
+        <v>496</v>
+      </c>
+      <c r="E371" t="s">
+        <v>491</v>
+      </c>
+      <c r="F371">
+        <v>2223</v>
+      </c>
+      <c r="G371">
+        <v>2226</v>
+      </c>
+      <c r="H371">
+        <v>3</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371">
+        <v>0</v>
+      </c>
+      <c r="L371">
+        <v>0</v>
+      </c>
+      <c r="M371" t="s">
+        <v>483</v>
+      </c>
+      <c r="N371" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>499</v>
+      </c>
+      <c r="B372" t="s">
+        <v>21</v>
+      </c>
+      <c r="C372" t="s">
+        <v>307</v>
+      </c>
+      <c r="D372" t="s">
+        <v>488</v>
+      </c>
+      <c r="E372" t="s">
+        <v>485</v>
+      </c>
+      <c r="F372">
+        <v>4661</v>
+      </c>
+      <c r="G372">
+        <v>4663</v>
+      </c>
+      <c r="H372">
+        <v>2</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>0</v>
+      </c>
+      <c r="M372" t="s">
+        <v>515</v>
+      </c>
+      <c r="N372" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>500</v>
+      </c>
+      <c r="B373" t="s">
+        <v>21</v>
+      </c>
+      <c r="C373" t="s">
+        <v>307</v>
+      </c>
+      <c r="D373" t="s">
+        <v>487</v>
+      </c>
+      <c r="E373" t="s">
+        <v>485</v>
+      </c>
+      <c r="F373">
+        <v>4663</v>
+      </c>
+      <c r="G373">
+        <v>4664</v>
+      </c>
+      <c r="H373">
+        <v>1</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373">
+        <v>0</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373" t="s">
+        <v>516</v>
+      </c>
+      <c r="N373" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>503</v>
+      </c>
+      <c r="B374" t="s">
+        <v>21</v>
+      </c>
+      <c r="C374" t="s">
+        <v>307</v>
+      </c>
+      <c r="D374" t="s">
+        <v>488</v>
+      </c>
+      <c r="E374" t="s">
+        <v>485</v>
+      </c>
+      <c r="F374">
+        <v>4664</v>
+      </c>
+      <c r="G374">
+        <v>4666</v>
+      </c>
+      <c r="H374">
+        <v>2</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374">
+        <v>0</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+      <c r="M374" t="s">
+        <v>515</v>
+      </c>
+      <c r="N374" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>504</v>
+      </c>
+      <c r="B375" t="s">
+        <v>21</v>
+      </c>
+      <c r="C375" t="s">
+        <v>307</v>
+      </c>
+      <c r="D375" t="s">
+        <v>489</v>
+      </c>
+      <c r="E375" t="s">
+        <v>485</v>
+      </c>
+      <c r="F375">
+        <v>4666</v>
+      </c>
+      <c r="G375">
+        <v>4668</v>
+      </c>
+      <c r="H375">
+        <v>2</v>
+      </c>
+      <c r="I375">
+        <v>0</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375">
+        <v>0</v>
+      </c>
+      <c r="L375">
+        <v>0</v>
+      </c>
+      <c r="M375" t="s">
+        <v>517</v>
+      </c>
+      <c r="N375" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>505</v>
+      </c>
+      <c r="B376" t="s">
+        <v>21</v>
+      </c>
+      <c r="C376" t="s">
+        <v>307</v>
+      </c>
+      <c r="D376" t="s">
+        <v>489</v>
+      </c>
+      <c r="E376" t="s">
+        <v>485</v>
+      </c>
+      <c r="F376">
+        <v>4668</v>
+      </c>
+      <c r="G376">
+        <v>4669</v>
+      </c>
+      <c r="H376">
+        <v>1</v>
+      </c>
+      <c r="I376">
+        <v>0</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>0</v>
+      </c>
+      <c r="L376">
+        <v>0</v>
+      </c>
+      <c r="M376" t="s">
+        <v>517</v>
+      </c>
+      <c r="N376" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>505</v>
+      </c>
+      <c r="B377" t="s">
+        <v>21</v>
+      </c>
+      <c r="C377" t="s">
+        <v>307</v>
+      </c>
+      <c r="D377" t="s">
+        <v>487</v>
+      </c>
+      <c r="E377" t="s">
+        <v>490</v>
+      </c>
+      <c r="F377">
+        <v>4669</v>
+      </c>
+      <c r="G377">
+        <v>4671</v>
+      </c>
+      <c r="H377">
+        <v>2</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+      <c r="M377" t="s">
+        <v>474</v>
+      </c>
+      <c r="N377" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>500</v>
+      </c>
+      <c r="B378" t="s">
+        <v>518</v>
+      </c>
+      <c r="C378" t="s">
+        <v>196</v>
+      </c>
+      <c r="D378" t="s">
+        <v>278</v>
+      </c>
+      <c r="E378" t="s">
+        <v>491</v>
+      </c>
+      <c r="F378">
+        <v>1284</v>
+      </c>
+      <c r="G378">
+        <v>1286</v>
+      </c>
+      <c r="H378">
+        <v>2</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+      <c r="M378" t="s">
+        <v>519</v>
+      </c>
+      <c r="N378" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>506</v>
+      </c>
+      <c r="B379" t="s">
+        <v>518</v>
+      </c>
+      <c r="C379" t="s">
+        <v>196</v>
+      </c>
+      <c r="D379" t="s">
+        <v>487</v>
+      </c>
+      <c r="E379" t="s">
+        <v>492</v>
+      </c>
+      <c r="F379">
+        <v>1286</v>
+      </c>
+      <c r="G379">
+        <v>1291</v>
+      </c>
+      <c r="H379">
+        <v>5</v>
+      </c>
+      <c r="I379">
+        <v>80</v>
+      </c>
+      <c r="J379" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="K379">
+        <v>19.05</v>
+      </c>
+      <c r="L379">
+        <v>1.19</v>
+      </c>
+      <c r="M379" t="s">
+        <v>520</v>
+      </c>
+      <c r="N379" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>507</v>
+      </c>
+      <c r="B380" t="s">
+        <v>518</v>
+      </c>
+      <c r="C380" t="s">
+        <v>196</v>
+      </c>
+      <c r="D380" t="s">
+        <v>532</v>
+      </c>
+      <c r="E380" t="s">
+        <v>492</v>
+      </c>
+      <c r="F380">
+        <v>1291</v>
+      </c>
+      <c r="G380">
+        <v>1295</v>
+      </c>
+      <c r="H380">
+        <v>4</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>3.14</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>1.27</v>
+      </c>
+      <c r="M380" t="s">
+        <v>521</v>
+      </c>
+      <c r="N380" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>507</v>
+      </c>
+      <c r="B381" t="s">
+        <v>518</v>
+      </c>
+      <c r="C381" t="s">
+        <v>196</v>
+      </c>
+      <c r="D381" t="s">
+        <v>533</v>
+      </c>
+      <c r="E381" t="s">
+        <v>492</v>
+      </c>
+      <c r="F381">
+        <v>1295</v>
+      </c>
+      <c r="G381">
+        <v>1298</v>
+      </c>
+      <c r="H381">
+        <v>3</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>2.69</v>
+      </c>
+      <c r="K381">
+        <v>0</v>
+      </c>
+      <c r="L381">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="M381" t="s">
+        <v>522</v>
+      </c>
+      <c r="N381" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>509</v>
+      </c>
+      <c r="B382" t="s">
+        <v>518</v>
+      </c>
+      <c r="C382" t="s">
+        <v>196</v>
+      </c>
+      <c r="D382" t="s">
+        <v>534</v>
+      </c>
+      <c r="E382" t="s">
+        <v>492</v>
+      </c>
+      <c r="F382">
+        <v>1298</v>
+      </c>
+      <c r="G382">
+        <v>1301</v>
+      </c>
+      <c r="H382">
+        <v>3</v>
+      </c>
+      <c r="I382">
+        <v>128</v>
+      </c>
+      <c r="J382">
+        <v>3.06</v>
+      </c>
+      <c r="K382">
+        <v>42.67</v>
+      </c>
+      <c r="L382">
+        <v>0.98</v>
+      </c>
+      <c r="M382" t="s">
+        <v>523</v>
+      </c>
+      <c r="N382" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>510</v>
+      </c>
+      <c r="B383" t="s">
+        <v>518</v>
+      </c>
+      <c r="C383" t="s">
+        <v>196</v>
+      </c>
+      <c r="D383" t="s">
+        <v>535</v>
+      </c>
+      <c r="E383" t="s">
+        <v>492</v>
+      </c>
+      <c r="F383">
+        <v>1301</v>
+      </c>
+      <c r="G383">
+        <v>1304</v>
+      </c>
+      <c r="H383">
+        <v>3</v>
+      </c>
+      <c r="I383">
+        <v>0</v>
+      </c>
+      <c r="J383">
+        <v>3.07</v>
+      </c>
+      <c r="K383">
+        <v>0</v>
+      </c>
+      <c r="L383">
+        <v>0.98</v>
+      </c>
+      <c r="M383" t="s">
+        <v>524</v>
+      </c>
+      <c r="N383" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>510</v>
+      </c>
+      <c r="B384" t="s">
+        <v>518</v>
+      </c>
+      <c r="C384" t="s">
+        <v>196</v>
+      </c>
+      <c r="D384" t="s">
+        <v>536</v>
+      </c>
+      <c r="E384" t="s">
+        <v>492</v>
+      </c>
+      <c r="F384">
+        <v>1304</v>
+      </c>
+      <c r="G384">
+        <v>1307</v>
+      </c>
+      <c r="H384">
+        <v>3</v>
+      </c>
+      <c r="I384">
+        <v>0</v>
+      </c>
+      <c r="J384">
+        <v>2.89</v>
+      </c>
+      <c r="K384">
+        <v>0</v>
+      </c>
+      <c r="L384">
+        <v>1.04</v>
+      </c>
+      <c r="M384" t="s">
+        <v>525</v>
+      </c>
+      <c r="N384" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>510</v>
+      </c>
+      <c r="B385" t="s">
+        <v>518</v>
+      </c>
+      <c r="C385" t="s">
+        <v>196</v>
+      </c>
+      <c r="D385" t="s">
+        <v>537</v>
+      </c>
+      <c r="E385" t="s">
+        <v>492</v>
+      </c>
+      <c r="F385">
+        <v>1307</v>
+      </c>
+      <c r="G385">
+        <v>1308</v>
+      </c>
+      <c r="H385">
+        <v>1</v>
+      </c>
+      <c r="I385">
+        <v>0</v>
+      </c>
+      <c r="J385">
+        <v>1.48</v>
+      </c>
+      <c r="K385">
+        <v>0</v>
+      </c>
+      <c r="L385">
+        <v>0.68</v>
+      </c>
+      <c r="M385" t="s">
+        <v>526</v>
+      </c>
+      <c r="N385" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>510</v>
+      </c>
+      <c r="B386" t="s">
+        <v>518</v>
+      </c>
+      <c r="C386" t="s">
+        <v>196</v>
+      </c>
+      <c r="D386" t="s">
+        <v>538</v>
+      </c>
+      <c r="E386" t="s">
+        <v>492</v>
+      </c>
+      <c r="F386">
+        <v>1308</v>
+      </c>
+      <c r="G386">
+        <v>1310</v>
+      </c>
+      <c r="H386">
+        <v>2</v>
+      </c>
+      <c r="I386">
+        <v>0</v>
+      </c>
+      <c r="J386">
+        <v>3.1</v>
+      </c>
+      <c r="K386">
+        <v>0</v>
+      </c>
+      <c r="L386">
+        <v>0.65</v>
+      </c>
+      <c r="M386" t="s">
+        <v>527</v>
+      </c>
+      <c r="N386" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>510</v>
+      </c>
+      <c r="B387" t="s">
+        <v>518</v>
+      </c>
+      <c r="C387" t="s">
+        <v>196</v>
+      </c>
+      <c r="D387" t="s">
+        <v>539</v>
+      </c>
+      <c r="E387" t="s">
+        <v>492</v>
+      </c>
+      <c r="F387">
+        <v>1310</v>
+      </c>
+      <c r="G387">
+        <v>1312</v>
+      </c>
+      <c r="H387">
+        <v>2</v>
+      </c>
+      <c r="I387">
+        <v>0</v>
+      </c>
+      <c r="J387">
+        <v>3.08</v>
+      </c>
+      <c r="K387">
+        <v>0</v>
+      </c>
+      <c r="L387">
+        <v>0.65</v>
+      </c>
+      <c r="M387" t="s">
+        <v>528</v>
+      </c>
+      <c r="N387" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>511</v>
+      </c>
+      <c r="B388" t="s">
+        <v>518</v>
+      </c>
+      <c r="C388" t="s">
+        <v>196</v>
+      </c>
+      <c r="D388" t="s">
+        <v>540</v>
+      </c>
+      <c r="E388" t="s">
+        <v>492</v>
+      </c>
+      <c r="F388">
+        <v>1312</v>
+      </c>
+      <c r="G388">
+        <v>1314</v>
+      </c>
+      <c r="H388">
+        <v>2</v>
+      </c>
+      <c r="I388">
+        <v>120</v>
+      </c>
+      <c r="J388">
+        <v>3.1</v>
+      </c>
+      <c r="K388">
+        <v>38.71</v>
+      </c>
+      <c r="L388">
+        <v>0.65</v>
+      </c>
+      <c r="M388" t="s">
+        <v>529</v>
+      </c>
+      <c r="N388" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>511</v>
+      </c>
+      <c r="B389" t="s">
+        <v>518</v>
+      </c>
+      <c r="C389" t="s">
+        <v>196</v>
+      </c>
+      <c r="D389" t="s">
+        <v>541</v>
+      </c>
+      <c r="E389" t="s">
+        <v>531</v>
+      </c>
+      <c r="F389">
+        <v>1314</v>
+      </c>
+      <c r="G389">
+        <v>1321</v>
+      </c>
+      <c r="H389">
+        <v>7</v>
+      </c>
+      <c r="I389">
+        <v>0</v>
+      </c>
+      <c r="J389">
+        <v>3.11</v>
+      </c>
+      <c r="K389">
+        <v>0</v>
+      </c>
+      <c r="L389">
+        <v>2.25</v>
+      </c>
+      <c r="M389" t="s">
+        <v>530</v>
+      </c>
+      <c r="N389" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>512</v>
+      </c>
+      <c r="B390" t="s">
+        <v>518</v>
+      </c>
+      <c r="C390" t="s">
+        <v>196</v>
+      </c>
+      <c r="D390" t="s">
+        <v>542</v>
+      </c>
+      <c r="E390" t="s">
+        <v>531</v>
+      </c>
+      <c r="F390">
+        <v>1321</v>
+      </c>
+      <c r="G390">
+        <v>1331</v>
+      </c>
+      <c r="H390">
+        <v>10</v>
+      </c>
+      <c r="I390">
+        <v>0</v>
+      </c>
+      <c r="J390">
+        <v>3.13</v>
+      </c>
+      <c r="K390">
+        <v>0</v>
+      </c>
+      <c r="L390">
+        <v>2.88</v>
+      </c>
+      <c r="M390" t="s">
+        <v>530</v>
+      </c>
+      <c r="N390" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>513</v>
+      </c>
+      <c r="B391" t="s">
+        <v>518</v>
+      </c>
+      <c r="C391" t="s">
+        <v>196</v>
+      </c>
+      <c r="D391" t="s">
+        <v>543</v>
+      </c>
+      <c r="E391" t="s">
+        <v>531</v>
+      </c>
+      <c r="F391">
+        <v>1331</v>
+      </c>
+      <c r="G391">
+        <v>1340</v>
+      </c>
+      <c r="H391">
+        <v>9</v>
+      </c>
+      <c r="I391">
+        <v>120</v>
+      </c>
+      <c r="J391">
+        <v>3.13</v>
+      </c>
+      <c r="K391">
+        <v>38.340000000000003</v>
+      </c>
+      <c r="L391">
+        <v>1.88</v>
+      </c>
+      <c r="M391" t="s">
+        <v>530</v>
+      </c>
+      <c r="N391" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>514</v>
+      </c>
+      <c r="B392" t="s">
+        <v>518</v>
+      </c>
+      <c r="C392" t="s">
+        <v>196</v>
+      </c>
+      <c r="D392" t="s">
+        <v>544</v>
+      </c>
+      <c r="E392" t="s">
+        <v>531</v>
+      </c>
+      <c r="F392">
+        <v>1340</v>
+      </c>
+      <c r="G392">
+        <v>1348</v>
+      </c>
+      <c r="H392">
+        <v>8</v>
+      </c>
+      <c r="I392">
+        <v>0</v>
+      </c>
+      <c r="J392">
+        <v>4.63</v>
+      </c>
+      <c r="K392">
+        <v>0</v>
+      </c>
+      <c r="L392">
+        <v>1.73</v>
+      </c>
+      <c r="M392" t="s">
+        <v>530</v>
+      </c>
+      <c r="N392" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>588</v>
+      </c>
+      <c r="B393" t="s">
+        <v>15</v>
+      </c>
+      <c r="C393" t="s">
+        <v>16</v>
+      </c>
+      <c r="D393" t="s">
+        <v>496</v>
+      </c>
+      <c r="E393" t="s">
+        <v>485</v>
+      </c>
+      <c r="F393">
+        <v>2226</v>
+      </c>
+      <c r="G393">
+        <v>2230</v>
+      </c>
+      <c r="H393">
+        <v>4</v>
+      </c>
+      <c r="I393">
+        <v>0</v>
+      </c>
+      <c r="J393">
+        <v>0</v>
+      </c>
+      <c r="K393">
+        <v>0</v>
+      </c>
+      <c r="L393">
+        <v>0</v>
+      </c>
+      <c r="M393" t="s">
+        <v>574</v>
+      </c>
+      <c r="N393" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>588</v>
+      </c>
+      <c r="B394" t="s">
+        <v>15</v>
+      </c>
+      <c r="C394" t="s">
+        <v>307</v>
+      </c>
+      <c r="D394" t="s">
+        <v>575</v>
+      </c>
+      <c r="E394" t="s">
+        <v>492</v>
+      </c>
+      <c r="F394">
+        <v>2230</v>
+      </c>
+      <c r="G394">
+        <v>2232</v>
+      </c>
+      <c r="H394">
+        <v>2</v>
+      </c>
+      <c r="I394">
+        <v>0</v>
+      </c>
+      <c r="J394">
+        <v>2.98</v>
+      </c>
+      <c r="K394">
+        <v>0</v>
+      </c>
+      <c r="L394">
+        <v>0.67</v>
+      </c>
+      <c r="M394" t="s">
+        <v>545</v>
+      </c>
+      <c r="N394" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>588</v>
+      </c>
+      <c r="B395" t="s">
+        <v>15</v>
+      </c>
+      <c r="C395" t="s">
+        <v>307</v>
+      </c>
+      <c r="D395" t="s">
+        <v>576</v>
+      </c>
+      <c r="E395" t="s">
+        <v>492</v>
+      </c>
+      <c r="F395">
+        <v>2232</v>
+      </c>
+      <c r="G395">
+        <v>2235</v>
+      </c>
+      <c r="H395">
+        <v>3</v>
+      </c>
+      <c r="I395">
+        <v>0</v>
+      </c>
+      <c r="J395">
+        <v>3.1</v>
+      </c>
+      <c r="K395">
+        <v>0</v>
+      </c>
+      <c r="L395">
+        <v>0.97</v>
+      </c>
+      <c r="M395" t="s">
+        <v>546</v>
+      </c>
+      <c r="N395" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>589</v>
+      </c>
+      <c r="B396" t="s">
+        <v>15</v>
+      </c>
+      <c r="C396" t="s">
+        <v>16</v>
+      </c>
+      <c r="D396" t="s">
+        <v>580</v>
+      </c>
+      <c r="E396" t="s">
+        <v>490</v>
+      </c>
+      <c r="F396">
+        <v>2235</v>
+      </c>
+      <c r="G396">
+        <v>2237</v>
+      </c>
+      <c r="H396">
+        <v>2</v>
+      </c>
+      <c r="I396">
+        <v>48</v>
+      </c>
+      <c r="J396">
+        <v>0</v>
+      </c>
+      <c r="K396">
+        <v>0</v>
+      </c>
+      <c r="L396">
+        <v>0</v>
+      </c>
+      <c r="M396" t="s">
+        <v>547</v>
+      </c>
+      <c r="N396" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>589</v>
+      </c>
+      <c r="B397" t="s">
+        <v>15</v>
+      </c>
+      <c r="C397" t="s">
+        <v>16</v>
+      </c>
+      <c r="D397" t="s">
+        <v>577</v>
+      </c>
+      <c r="E397" t="s">
+        <v>492</v>
+      </c>
+      <c r="F397">
+        <v>2237</v>
+      </c>
+      <c r="G397">
+        <v>2240</v>
+      </c>
+      <c r="H397">
+        <v>3</v>
+      </c>
+      <c r="I397">
+        <v>0</v>
+      </c>
+      <c r="J397">
+        <v>3.1</v>
+      </c>
+      <c r="K397">
+        <v>0</v>
+      </c>
+      <c r="L397">
+        <v>0.97</v>
+      </c>
+      <c r="M397" t="s">
+        <v>548</v>
+      </c>
+      <c r="N397" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>589</v>
+      </c>
+      <c r="B398" t="s">
+        <v>15</v>
+      </c>
+      <c r="C398" t="s">
+        <v>16</v>
+      </c>
+      <c r="D398" t="s">
+        <v>578</v>
+      </c>
+      <c r="E398" t="s">
+        <v>492</v>
+      </c>
+      <c r="F398">
+        <v>2240</v>
+      </c>
+      <c r="G398">
+        <v>2243</v>
+      </c>
+      <c r="H398">
+        <v>3</v>
+      </c>
+      <c r="I398">
+        <v>0</v>
+      </c>
+      <c r="J398">
+        <v>3.04</v>
+      </c>
+      <c r="K398">
+        <v>0</v>
+      </c>
+      <c r="L398">
+        <v>0.99</v>
+      </c>
+      <c r="M398" t="s">
+        <v>549</v>
+      </c>
+      <c r="N398" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>589</v>
+      </c>
+      <c r="B399" t="s">
+        <v>15</v>
+      </c>
+      <c r="C399" t="s">
+        <v>16</v>
+      </c>
+      <c r="D399" t="s">
+        <v>579</v>
+      </c>
+      <c r="E399" t="s">
+        <v>492</v>
+      </c>
+      <c r="F399">
+        <v>2243</v>
+      </c>
+      <c r="G399">
+        <v>2244</v>
+      </c>
+      <c r="H399">
+        <v>1</v>
+      </c>
+      <c r="I399">
+        <v>0</v>
+      </c>
+      <c r="J399">
+        <v>0.45</v>
+      </c>
+      <c r="K399">
+        <v>0</v>
+      </c>
+      <c r="L399">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="M399" t="s">
+        <v>550</v>
+      </c>
+      <c r="N399" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>590</v>
+      </c>
+      <c r="B400" t="s">
+        <v>15</v>
+      </c>
+      <c r="C400" t="s">
+        <v>16</v>
+      </c>
+      <c r="D400" t="s">
+        <v>489</v>
+      </c>
+      <c r="E400" t="s">
+        <v>43</v>
+      </c>
+      <c r="F400">
+        <v>2244</v>
+      </c>
+      <c r="G400">
+        <v>2245</v>
+      </c>
+      <c r="H400">
+        <v>1</v>
+      </c>
+      <c r="I400">
+        <v>30</v>
+      </c>
+      <c r="J400">
+        <v>0</v>
+      </c>
+      <c r="K400">
+        <v>0</v>
+      </c>
+      <c r="L400">
+        <v>0</v>
+      </c>
+      <c r="M400" t="s">
+        <v>551</v>
+      </c>
+      <c r="N400" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>590</v>
+      </c>
+      <c r="B401" t="s">
+        <v>15</v>
+      </c>
+      <c r="C401" t="s">
+        <v>16</v>
+      </c>
+      <c r="E401" t="s">
+        <v>491</v>
+      </c>
+      <c r="F401">
+        <v>2245</v>
+      </c>
+      <c r="G401">
+        <v>2247</v>
+      </c>
+      <c r="H401">
+        <v>2</v>
+      </c>
+      <c r="I401">
+        <v>0</v>
+      </c>
+      <c r="J401">
+        <v>0</v>
+      </c>
+      <c r="K401">
+        <v>0</v>
+      </c>
+      <c r="L401">
+        <v>0</v>
+      </c>
+      <c r="M401" t="s">
+        <v>552</v>
+      </c>
+      <c r="N401" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>591</v>
+      </c>
+      <c r="B402" t="s">
+        <v>15</v>
+      </c>
+      <c r="C402" t="s">
+        <v>16</v>
+      </c>
+      <c r="E402" t="s">
+        <v>491</v>
+      </c>
+      <c r="F402">
+        <v>2247</v>
+      </c>
+      <c r="G402">
+        <v>2248</v>
+      </c>
+      <c r="H402">
+        <v>1</v>
+      </c>
+      <c r="I402">
+        <v>0</v>
+      </c>
+      <c r="J402">
+        <v>0</v>
+      </c>
+      <c r="K402">
+        <v>0</v>
+      </c>
+      <c r="L402">
+        <v>0</v>
+      </c>
+      <c r="M402" t="s">
+        <v>552</v>
+      </c>
+      <c r="N402" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>592</v>
+      </c>
+      <c r="B403" t="s">
+        <v>15</v>
+      </c>
+      <c r="C403" t="s">
+        <v>16</v>
+      </c>
+      <c r="E403" t="s">
+        <v>215</v>
+      </c>
+      <c r="F403">
+        <v>2248</v>
+      </c>
+      <c r="G403">
+        <v>2249</v>
+      </c>
+      <c r="H403">
+        <v>1</v>
+      </c>
+      <c r="I403">
+        <v>0</v>
+      </c>
+      <c r="J403">
+        <v>0</v>
+      </c>
+      <c r="K403">
+        <v>0</v>
+      </c>
+      <c r="L403">
+        <v>0</v>
+      </c>
+      <c r="M403" t="s">
+        <v>477</v>
+      </c>
+      <c r="N403" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>592</v>
+      </c>
+      <c r="B404" t="s">
+        <v>15</v>
+      </c>
+      <c r="C404" t="s">
+        <v>16</v>
+      </c>
+      <c r="D404" t="s">
+        <v>489</v>
+      </c>
+      <c r="E404" t="s">
+        <v>43</v>
+      </c>
+      <c r="F404">
+        <v>2249</v>
+      </c>
+      <c r="G404">
+        <v>2250</v>
+      </c>
+      <c r="H404">
+        <v>1</v>
+      </c>
+      <c r="I404">
+        <v>0</v>
+      </c>
+      <c r="J404">
+        <v>0</v>
+      </c>
+      <c r="K404">
+        <v>0</v>
+      </c>
+      <c r="L404">
+        <v>0</v>
+      </c>
+      <c r="M404" t="s">
+        <v>553</v>
+      </c>
+      <c r="N404" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>592</v>
+      </c>
+      <c r="B405" t="s">
+        <v>15</v>
+      </c>
+      <c r="C405" t="s">
+        <v>16</v>
+      </c>
+      <c r="E405" t="s">
+        <v>491</v>
+      </c>
+      <c r="F405">
+        <v>2250</v>
+      </c>
+      <c r="G405">
+        <v>2253</v>
+      </c>
+      <c r="H405">
+        <v>3</v>
+      </c>
+      <c r="I405">
+        <v>0</v>
+      </c>
+      <c r="J405">
+        <v>0</v>
+      </c>
+      <c r="K405">
+        <v>0</v>
+      </c>
+      <c r="L405">
+        <v>0</v>
+      </c>
+      <c r="M405" t="s">
+        <v>552</v>
+      </c>
+      <c r="N405" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>593</v>
+      </c>
+      <c r="B406" t="s">
+        <v>15</v>
+      </c>
+      <c r="C406" t="s">
+        <v>16</v>
+      </c>
+      <c r="E406" t="s">
+        <v>491</v>
+      </c>
+      <c r="F406">
+        <v>2253</v>
+      </c>
+      <c r="G406">
+        <v>2254</v>
+      </c>
+      <c r="H406">
+        <v>1</v>
+      </c>
+      <c r="I406">
+        <v>0</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406">
+        <v>0</v>
+      </c>
+      <c r="L406">
+        <v>0</v>
+      </c>
+      <c r="M406" t="s">
+        <v>554</v>
+      </c>
+      <c r="N406" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>594</v>
+      </c>
+      <c r="B407" t="s">
+        <v>15</v>
+      </c>
+      <c r="C407" t="s">
+        <v>16</v>
+      </c>
+      <c r="D407" t="s">
+        <v>581</v>
+      </c>
+      <c r="E407" t="s">
+        <v>485</v>
+      </c>
+      <c r="F407">
+        <v>2254</v>
+      </c>
+      <c r="G407">
+        <v>2255</v>
+      </c>
+      <c r="H407">
+        <v>1</v>
+      </c>
+      <c r="I407">
+        <v>0</v>
+      </c>
+      <c r="J407">
+        <v>0</v>
+      </c>
+      <c r="K407">
+        <v>0</v>
+      </c>
+      <c r="L407">
+        <v>0</v>
+      </c>
+      <c r="M407" t="s">
+        <v>582</v>
+      </c>
+      <c r="N407" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>594</v>
+      </c>
+      <c r="B408" t="s">
+        <v>15</v>
+      </c>
+      <c r="C408" t="s">
+        <v>16</v>
+      </c>
+      <c r="E408" t="s">
+        <v>491</v>
+      </c>
+      <c r="F408">
+        <v>2255</v>
+      </c>
+      <c r="G408">
+        <v>2257</v>
+      </c>
+      <c r="H408">
+        <v>2</v>
+      </c>
+      <c r="I408">
+        <v>0</v>
+      </c>
+      <c r="J408">
+        <v>0</v>
+      </c>
+      <c r="K408">
+        <v>0</v>
+      </c>
+      <c r="L408">
+        <v>0</v>
+      </c>
+      <c r="M408" t="s">
+        <v>552</v>
+      </c>
+      <c r="N408" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>595</v>
+      </c>
+      <c r="B409" t="s">
+        <v>15</v>
+      </c>
+      <c r="C409" t="s">
+        <v>16</v>
+      </c>
+      <c r="D409" t="s">
+        <v>487</v>
+      </c>
+      <c r="E409" t="s">
+        <v>26</v>
+      </c>
+      <c r="F409">
+        <v>2257</v>
+      </c>
+      <c r="G409">
+        <v>2259</v>
+      </c>
+      <c r="H409">
+        <v>2</v>
+      </c>
+      <c r="I409">
+        <v>0</v>
+      </c>
+      <c r="J409">
+        <v>0</v>
+      </c>
+      <c r="K409">
+        <v>0</v>
+      </c>
+      <c r="L409">
+        <v>0</v>
+      </c>
+      <c r="M409" t="s">
+        <v>555</v>
+      </c>
+      <c r="N409" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>596</v>
+      </c>
+      <c r="B410" t="s">
+        <v>15</v>
+      </c>
+      <c r="C410" t="s">
+        <v>16</v>
+      </c>
+      <c r="D410" t="s">
+        <v>487</v>
+      </c>
+      <c r="E410" t="s">
+        <v>26</v>
+      </c>
+      <c r="F410">
+        <v>2259</v>
+      </c>
+      <c r="G410">
+        <v>2261</v>
+      </c>
+      <c r="H410">
+        <v>2</v>
+      </c>
+      <c r="I410">
+        <v>30</v>
+      </c>
+      <c r="J410">
+        <v>0</v>
+      </c>
+      <c r="K410">
+        <v>0</v>
+      </c>
+      <c r="L410">
+        <v>0</v>
+      </c>
+      <c r="M410" t="s">
+        <v>555</v>
+      </c>
+      <c r="N410" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>597</v>
+      </c>
+      <c r="B411" t="s">
+        <v>15</v>
+      </c>
+      <c r="C411" t="s">
+        <v>16</v>
+      </c>
+      <c r="D411" t="s">
+        <v>486</v>
+      </c>
+      <c r="E411" t="s">
+        <v>583</v>
+      </c>
+      <c r="F411">
+        <v>2261</v>
+      </c>
+      <c r="G411">
+        <v>2264</v>
+      </c>
+      <c r="H411">
+        <v>3</v>
+      </c>
+      <c r="I411">
+        <v>0</v>
+      </c>
+      <c r="J411">
+        <v>0</v>
+      </c>
+      <c r="K411">
+        <v>0</v>
+      </c>
+      <c r="L411">
+        <v>0</v>
+      </c>
+      <c r="M411" t="s">
+        <v>556</v>
+      </c>
+      <c r="N411" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>598</v>
+      </c>
+      <c r="B412" t="s">
+        <v>15</v>
+      </c>
+      <c r="C412" t="s">
+        <v>16</v>
+      </c>
+      <c r="E412" t="s">
+        <v>491</v>
+      </c>
+      <c r="F412">
+        <v>2264</v>
+      </c>
+      <c r="G412">
+        <v>2265</v>
+      </c>
+      <c r="H412">
+        <v>1</v>
+      </c>
+      <c r="I412">
+        <v>0</v>
+      </c>
+      <c r="J412">
+        <v>0</v>
+      </c>
+      <c r="K412">
+        <v>0</v>
+      </c>
+      <c r="L412">
+        <v>0</v>
+      </c>
+      <c r="M412" t="s">
+        <v>557</v>
+      </c>
+      <c r="N412" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>599</v>
+      </c>
+      <c r="B413" t="s">
+        <v>15</v>
+      </c>
+      <c r="C413" t="s">
+        <v>16</v>
+      </c>
+      <c r="D413" t="s">
+        <v>488</v>
+      </c>
+      <c r="E413" t="s">
+        <v>26</v>
+      </c>
+      <c r="F413">
+        <v>2265</v>
+      </c>
+      <c r="G413">
+        <v>2268</v>
+      </c>
+      <c r="H413">
+        <v>3</v>
+      </c>
+      <c r="I413">
+        <v>35</v>
+      </c>
+      <c r="J413">
+        <v>0</v>
+      </c>
+      <c r="K413">
+        <v>0</v>
+      </c>
+      <c r="L413">
+        <v>0</v>
+      </c>
+      <c r="M413" t="s">
+        <v>558</v>
+      </c>
+      <c r="N413" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>599</v>
+      </c>
+      <c r="B414" t="s">
+        <v>15</v>
+      </c>
+      <c r="C414" t="s">
+        <v>16</v>
+      </c>
+      <c r="D414" t="s">
+        <v>489</v>
+      </c>
+      <c r="E414" t="s">
+        <v>43</v>
+      </c>
+      <c r="F414">
+        <v>2268</v>
+      </c>
+      <c r="G414">
+        <v>2269</v>
+      </c>
+      <c r="H414">
+        <v>1</v>
+      </c>
+      <c r="I414">
+        <v>0</v>
+      </c>
+      <c r="J414">
+        <v>0</v>
+      </c>
+      <c r="K414">
+        <v>0</v>
+      </c>
+      <c r="L414">
+        <v>0</v>
+      </c>
+      <c r="M414" t="s">
+        <v>559</v>
+      </c>
+      <c r="N414" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>600</v>
+      </c>
+      <c r="B415" t="s">
+        <v>15</v>
+      </c>
+      <c r="C415" t="s">
+        <v>16</v>
+      </c>
+      <c r="D415" t="s">
+        <v>486</v>
+      </c>
+      <c r="E415" t="s">
+        <v>584</v>
+      </c>
+      <c r="F415">
+        <v>2269</v>
+      </c>
+      <c r="G415">
+        <v>2271</v>
+      </c>
+      <c r="H415">
+        <v>2</v>
+      </c>
+      <c r="I415">
+        <v>0</v>
+      </c>
+      <c r="J415">
+        <v>0</v>
+      </c>
+      <c r="K415">
+        <v>0</v>
+      </c>
+      <c r="L415">
+        <v>0</v>
+      </c>
+      <c r="M415" t="s">
+        <v>556</v>
+      </c>
+      <c r="N415" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>600</v>
+      </c>
+      <c r="B416" t="s">
+        <v>15</v>
+      </c>
+      <c r="C416" t="s">
+        <v>16</v>
+      </c>
+      <c r="E416" t="s">
+        <v>17</v>
+      </c>
+      <c r="F416">
+        <v>2271</v>
+      </c>
+      <c r="G416">
+        <v>2272</v>
+      </c>
+      <c r="H416">
+        <v>1</v>
+      </c>
+      <c r="I416">
+        <v>0</v>
+      </c>
+      <c r="J416">
+        <v>0</v>
+      </c>
+      <c r="K416">
+        <v>0</v>
+      </c>
+      <c r="L416">
+        <v>0</v>
+      </c>
+      <c r="M416" t="s">
+        <v>560</v>
+      </c>
+      <c r="N416" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>601</v>
+      </c>
+      <c r="B417" t="s">
+        <v>15</v>
+      </c>
+      <c r="C417" t="s">
+        <v>16</v>
+      </c>
+      <c r="D417" t="s">
+        <v>486</v>
+      </c>
+      <c r="E417" t="s">
+        <v>584</v>
+      </c>
+      <c r="F417">
+        <v>2272</v>
+      </c>
+      <c r="G417">
+        <v>2276</v>
+      </c>
+      <c r="H417">
+        <v>4</v>
+      </c>
+      <c r="I417">
+        <v>0</v>
+      </c>
+      <c r="J417">
+        <v>0</v>
+      </c>
+      <c r="K417">
+        <v>0</v>
+      </c>
+      <c r="L417">
+        <v>0</v>
+      </c>
+      <c r="M417" t="s">
+        <v>556</v>
+      </c>
+      <c r="N417" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>602</v>
+      </c>
+      <c r="B418" t="s">
+        <v>15</v>
+      </c>
+      <c r="C418" t="s">
+        <v>16</v>
+      </c>
+      <c r="D418" t="s">
+        <v>486</v>
+      </c>
+      <c r="E418" t="s">
+        <v>584</v>
+      </c>
+      <c r="F418">
+        <v>2276</v>
+      </c>
+      <c r="G418">
+        <v>2279</v>
+      </c>
+      <c r="H418">
+        <v>3</v>
+      </c>
+      <c r="I418">
+        <v>0</v>
+      </c>
+      <c r="J418">
+        <v>0</v>
+      </c>
+      <c r="K418">
+        <v>0</v>
+      </c>
+      <c r="L418">
+        <v>0</v>
+      </c>
+      <c r="M418" t="s">
+        <v>556</v>
+      </c>
+      <c r="N418" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>602</v>
+      </c>
+      <c r="B419" t="s">
+        <v>15</v>
+      </c>
+      <c r="C419" t="s">
+        <v>16</v>
+      </c>
+      <c r="D419" t="s">
+        <v>488</v>
+      </c>
+      <c r="E419" t="s">
+        <v>26</v>
+      </c>
+      <c r="F419">
+        <v>2279</v>
+      </c>
+      <c r="G419">
+        <v>2280</v>
+      </c>
+      <c r="H419">
+        <v>1</v>
+      </c>
+      <c r="I419">
+        <v>0</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+      <c r="K419">
+        <v>0</v>
+      </c>
+      <c r="L419">
+        <v>0</v>
+      </c>
+      <c r="M419" t="s">
+        <v>558</v>
+      </c>
+      <c r="N419" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>603</v>
+      </c>
+      <c r="B420" t="s">
+        <v>15</v>
+      </c>
+      <c r="C420" t="s">
+        <v>16</v>
+      </c>
+      <c r="D420" t="s">
+        <v>486</v>
+      </c>
+      <c r="E420" t="s">
+        <v>584</v>
+      </c>
+      <c r="F420">
+        <v>2280</v>
+      </c>
+      <c r="G420">
+        <v>2282</v>
+      </c>
+      <c r="H420">
+        <v>2</v>
+      </c>
+      <c r="I420">
+        <v>35</v>
+      </c>
+      <c r="J420">
+        <v>0</v>
+      </c>
+      <c r="K420">
+        <v>0</v>
+      </c>
+      <c r="L420">
+        <v>0</v>
+      </c>
+      <c r="M420" t="s">
+        <v>556</v>
+      </c>
+      <c r="N420" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>603</v>
+      </c>
+      <c r="B421" t="s">
+        <v>15</v>
+      </c>
+      <c r="C421" t="s">
+        <v>16</v>
+      </c>
+      <c r="D421" t="s">
+        <v>489</v>
+      </c>
+      <c r="E421" t="s">
+        <v>43</v>
+      </c>
+      <c r="F421">
+        <v>2282</v>
+      </c>
+      <c r="G421">
+        <v>2283</v>
+      </c>
+      <c r="H421">
+        <v>1</v>
+      </c>
+      <c r="I421">
+        <v>0</v>
+      </c>
+      <c r="J421">
+        <v>0</v>
+      </c>
+      <c r="K421">
+        <v>0</v>
+      </c>
+      <c r="L421">
+        <v>0</v>
+      </c>
+      <c r="M421" t="s">
+        <v>561</v>
+      </c>
+      <c r="N421" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>603</v>
+      </c>
+      <c r="B422" t="s">
+        <v>15</v>
+      </c>
+      <c r="C422" t="s">
+        <v>16</v>
+      </c>
+      <c r="D422" t="s">
+        <v>581</v>
+      </c>
+      <c r="E422" t="s">
+        <v>43</v>
+      </c>
+      <c r="F422">
+        <v>2283</v>
+      </c>
+      <c r="G422">
+        <v>2284</v>
+      </c>
+      <c r="H422">
+        <v>1</v>
+      </c>
+      <c r="I422">
+        <v>0</v>
+      </c>
+      <c r="J422">
+        <v>0</v>
+      </c>
+      <c r="K422">
+        <v>0</v>
+      </c>
+      <c r="L422">
+        <v>0</v>
+      </c>
+      <c r="M422" t="s">
+        <v>562</v>
+      </c>
+      <c r="N422" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>603</v>
+      </c>
+      <c r="B423" t="s">
+        <v>15</v>
+      </c>
+      <c r="C423" t="s">
+        <v>16</v>
+      </c>
+      <c r="D423" t="s">
+        <v>533</v>
+      </c>
+      <c r="E423" t="s">
+        <v>26</v>
+      </c>
+      <c r="F423">
+        <v>2284</v>
+      </c>
+      <c r="G423">
+        <v>2285</v>
+      </c>
+      <c r="H423">
+        <v>1</v>
+      </c>
+      <c r="I423">
+        <v>0</v>
+      </c>
+      <c r="J423">
+        <v>0</v>
+      </c>
+      <c r="K423">
+        <v>0</v>
+      </c>
+      <c r="L423">
+        <v>0</v>
+      </c>
+      <c r="M423" t="s">
+        <v>563</v>
+      </c>
+      <c r="N423" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>604</v>
+      </c>
+      <c r="B424" t="s">
+        <v>15</v>
+      </c>
+      <c r="C424" t="s">
+        <v>16</v>
+      </c>
+      <c r="D424" t="s">
+        <v>585</v>
+      </c>
+      <c r="E424" t="s">
+        <v>485</v>
+      </c>
+      <c r="F424">
+        <v>2285</v>
+      </c>
+      <c r="G424">
+        <v>2287</v>
+      </c>
+      <c r="H424">
+        <v>2</v>
+      </c>
+      <c r="I424">
+        <v>0</v>
+      </c>
+      <c r="J424">
+        <v>0</v>
+      </c>
+      <c r="K424">
+        <v>0</v>
+      </c>
+      <c r="L424">
+        <v>0</v>
+      </c>
+      <c r="M424" t="s">
+        <v>564</v>
+      </c>
+      <c r="N424" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="425" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>604</v>
+      </c>
+      <c r="B425" t="s">
+        <v>15</v>
+      </c>
+      <c r="C425" t="s">
+        <v>16</v>
+      </c>
+      <c r="D425" t="s">
+        <v>585</v>
+      </c>
+      <c r="E425" t="s">
+        <v>491</v>
+      </c>
+      <c r="F425">
+        <v>2287</v>
+      </c>
+      <c r="G425">
+        <v>2290</v>
+      </c>
+      <c r="H425">
+        <v>3</v>
+      </c>
+      <c r="I425">
+        <v>0</v>
+      </c>
+      <c r="J425">
+        <v>0</v>
+      </c>
+      <c r="K425">
+        <v>0</v>
+      </c>
+      <c r="L425">
+        <v>0</v>
+      </c>
+      <c r="M425" t="s">
+        <v>565</v>
+      </c>
+      <c r="N425" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="426" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>605</v>
+      </c>
+      <c r="B426" t="s">
+        <v>15</v>
+      </c>
+      <c r="C426" t="s">
+        <v>16</v>
+      </c>
+      <c r="D426" t="s">
+        <v>585</v>
+      </c>
+      <c r="E426" t="s">
+        <v>491</v>
+      </c>
+      <c r="F426">
+        <v>2290</v>
+      </c>
+      <c r="G426">
+        <v>2291</v>
+      </c>
+      <c r="H426">
+        <v>1</v>
+      </c>
+      <c r="I426">
+        <v>0</v>
+      </c>
+      <c r="J426">
+        <v>0</v>
+      </c>
+      <c r="K426">
+        <v>0</v>
+      </c>
+      <c r="L426">
+        <v>0</v>
+      </c>
+      <c r="M426" t="s">
+        <v>565</v>
+      </c>
+      <c r="N426" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="427" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>605</v>
+      </c>
+      <c r="B427" t="s">
+        <v>15</v>
+      </c>
+      <c r="C427" t="s">
+        <v>16</v>
+      </c>
+      <c r="D427" t="s">
+        <v>496</v>
+      </c>
+      <c r="E427" t="s">
+        <v>491</v>
+      </c>
+      <c r="F427">
+        <v>2291</v>
+      </c>
+      <c r="G427">
+        <v>2292</v>
+      </c>
+      <c r="H427">
+        <v>1</v>
+      </c>
+      <c r="I427">
+        <v>35</v>
+      </c>
+      <c r="J427">
+        <v>0</v>
+      </c>
+      <c r="K427">
+        <v>0</v>
+      </c>
+      <c r="L427">
+        <v>0</v>
+      </c>
+      <c r="M427" t="s">
+        <v>566</v>
+      </c>
+      <c r="N427" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="428" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>605</v>
+      </c>
+      <c r="B428" t="s">
+        <v>15</v>
+      </c>
+      <c r="C428" t="s">
+        <v>16</v>
+      </c>
+      <c r="D428" t="s">
+        <v>158</v>
+      </c>
+      <c r="E428" t="s">
+        <v>490</v>
+      </c>
+      <c r="F428">
+        <v>2292</v>
+      </c>
+      <c r="G428">
+        <v>2295</v>
+      </c>
+      <c r="H428">
+        <v>3</v>
+      </c>
+      <c r="I428">
+        <v>0</v>
+      </c>
+      <c r="J428">
+        <v>0</v>
+      </c>
+      <c r="K428">
+        <v>0</v>
+      </c>
+      <c r="L428">
+        <v>0</v>
+      </c>
+      <c r="M428" t="s">
+        <v>567</v>
+      </c>
+      <c r="N428" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="429" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>605</v>
+      </c>
+      <c r="B429" t="s">
+        <v>15</v>
+      </c>
+      <c r="C429" t="s">
+        <v>16</v>
+      </c>
+      <c r="D429" t="s">
+        <v>587</v>
+      </c>
+      <c r="E429" t="s">
+        <v>140</v>
+      </c>
+      <c r="F429">
+        <v>2295</v>
+      </c>
+      <c r="G429">
+        <v>2297</v>
+      </c>
+      <c r="H429">
+        <v>2</v>
+      </c>
+      <c r="I429">
+        <v>0</v>
+      </c>
+      <c r="J429">
+        <v>1.45</v>
+      </c>
+      <c r="K429">
+        <v>0</v>
+      </c>
+      <c r="L429">
+        <v>1.38</v>
+      </c>
+      <c r="M429" t="s">
+        <v>568</v>
+      </c>
+      <c r="N429" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="430" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>606</v>
+      </c>
+      <c r="B430" t="s">
+        <v>15</v>
+      </c>
+      <c r="C430" t="s">
+        <v>16</v>
+      </c>
+      <c r="D430" t="s">
+        <v>586</v>
+      </c>
+      <c r="E430" t="s">
+        <v>491</v>
+      </c>
+      <c r="F430">
+        <v>2297</v>
+      </c>
+      <c r="G430">
+        <v>2298</v>
+      </c>
+      <c r="H430">
+        <v>1</v>
+      </c>
+      <c r="I430">
+        <v>0</v>
+      </c>
+      <c r="J430">
+        <v>0</v>
+      </c>
+      <c r="K430">
+        <v>0</v>
+      </c>
+      <c r="L430">
+        <v>0</v>
+      </c>
+      <c r="M430" t="s">
+        <v>569</v>
+      </c>
+      <c r="N430" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="431" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>606</v>
+      </c>
+      <c r="B431" t="s">
+        <v>15</v>
+      </c>
+      <c r="C431" t="s">
+        <v>16</v>
+      </c>
+      <c r="D431" t="s">
+        <v>278</v>
+      </c>
+      <c r="E431" t="s">
+        <v>584</v>
+      </c>
+      <c r="F431">
+        <v>2298</v>
+      </c>
+      <c r="G431">
+        <v>2300</v>
+      </c>
+      <c r="H431">
+        <v>2</v>
+      </c>
+      <c r="I431">
+        <v>0</v>
+      </c>
+      <c r="J431">
+        <v>0</v>
+      </c>
+      <c r="K431">
+        <v>0</v>
+      </c>
+      <c r="L431">
+        <v>0</v>
+      </c>
+      <c r="M431" t="s">
+        <v>570</v>
+      </c>
+      <c r="N431" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="432" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>607</v>
+      </c>
+      <c r="B432" t="s">
+        <v>15</v>
+      </c>
+      <c r="C432" t="s">
+        <v>16</v>
+      </c>
+      <c r="D432" t="s">
+        <v>486</v>
+      </c>
+      <c r="E432" t="s">
+        <v>26</v>
+      </c>
+      <c r="F432">
+        <v>2300</v>
+      </c>
+      <c r="G432">
+        <v>2308</v>
+      </c>
+      <c r="H432">
+        <v>8</v>
+      </c>
+      <c r="I432">
+        <v>0</v>
+      </c>
+      <c r="J432">
+        <v>0</v>
+      </c>
+      <c r="K432">
+        <v>0</v>
+      </c>
+      <c r="L432">
+        <v>0</v>
+      </c>
+      <c r="M432" t="s">
+        <v>571</v>
+      </c>
+      <c r="N432" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>608</v>
+      </c>
+      <c r="B433" t="s">
+        <v>15</v>
+      </c>
+      <c r="C433" t="s">
+        <v>16</v>
+      </c>
+      <c r="D433" t="s">
+        <v>486</v>
+      </c>
+      <c r="E433" t="s">
+        <v>26</v>
+      </c>
+      <c r="F433">
+        <v>2308</v>
+      </c>
+      <c r="G433">
+        <v>2312</v>
+      </c>
+      <c r="H433">
+        <v>4</v>
+      </c>
+      <c r="I433">
+        <v>0</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+      <c r="K433">
+        <v>0</v>
+      </c>
+      <c r="L433">
+        <v>0</v>
+      </c>
+      <c r="M433" t="s">
+        <v>571</v>
+      </c>
+      <c r="N433" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>609</v>
+      </c>
+      <c r="B434" t="s">
+        <v>15</v>
+      </c>
+      <c r="C434" t="s">
+        <v>16</v>
+      </c>
+      <c r="D434" t="s">
+        <v>486</v>
+      </c>
+      <c r="E434" t="s">
+        <v>26</v>
+      </c>
+      <c r="F434">
+        <v>2312</v>
+      </c>
+      <c r="G434">
+        <v>2318</v>
+      </c>
+      <c r="H434">
+        <v>6</v>
+      </c>
+      <c r="I434">
+        <v>0</v>
+      </c>
+      <c r="J434">
+        <v>0</v>
+      </c>
+      <c r="K434">
+        <v>0</v>
+      </c>
+      <c r="L434">
+        <v>0</v>
+      </c>
+      <c r="M434" t="s">
+        <v>571</v>
+      </c>
+      <c r="N434" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="435" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>610</v>
+      </c>
+      <c r="B435" t="s">
+        <v>15</v>
+      </c>
+      <c r="C435" t="s">
+        <v>16</v>
+      </c>
+      <c r="D435" t="s">
+        <v>486</v>
+      </c>
+      <c r="E435" t="s">
+        <v>26</v>
+      </c>
+      <c r="F435">
+        <v>2318</v>
+      </c>
+      <c r="G435">
+        <v>2325</v>
+      </c>
+      <c r="H435">
+        <v>7</v>
+      </c>
+      <c r="I435">
+        <v>50</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+      <c r="K435">
+        <v>0</v>
+      </c>
+      <c r="L435">
+        <v>0</v>
+      </c>
+      <c r="M435" t="s">
+        <v>571</v>
+      </c>
+      <c r="N435" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="436" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>611</v>
+      </c>
+      <c r="B436" t="s">
+        <v>15</v>
+      </c>
+      <c r="C436" t="s">
+        <v>16</v>
+      </c>
+      <c r="D436" t="s">
+        <v>486</v>
+      </c>
+      <c r="E436" t="s">
+        <v>26</v>
+      </c>
+      <c r="F436">
+        <v>2325</v>
+      </c>
+      <c r="G436">
+        <v>2334</v>
+      </c>
+      <c r="H436">
+        <v>9</v>
+      </c>
+      <c r="I436">
+        <v>0</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+      <c r="K436">
+        <v>0</v>
+      </c>
+      <c r="L436">
+        <v>0</v>
+      </c>
+      <c r="M436" t="s">
+        <v>571</v>
+      </c>
+      <c r="N436" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="437" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>612</v>
+      </c>
+      <c r="B437" t="s">
+        <v>15</v>
+      </c>
+      <c r="C437" t="s">
+        <v>16</v>
+      </c>
+      <c r="D437" t="s">
+        <v>486</v>
+      </c>
+      <c r="E437" t="s">
+        <v>26</v>
+      </c>
+      <c r="F437">
+        <v>2334</v>
+      </c>
+      <c r="G437">
+        <v>2342</v>
+      </c>
+      <c r="H437">
+        <v>8</v>
+      </c>
+      <c r="I437">
+        <v>40</v>
+      </c>
+      <c r="J437">
+        <v>0</v>
+      </c>
+      <c r="K437">
+        <v>0</v>
+      </c>
+      <c r="L437">
+        <v>0</v>
+      </c>
+      <c r="M437" t="s">
+        <v>571</v>
+      </c>
+      <c r="N437" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="438" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>613</v>
+      </c>
+      <c r="B438" t="s">
+        <v>15</v>
+      </c>
+      <c r="C438" t="s">
+        <v>16</v>
+      </c>
+      <c r="D438" t="s">
+        <v>278</v>
+      </c>
+      <c r="E438" t="s">
+        <v>43</v>
+      </c>
+      <c r="F438">
+        <v>2342</v>
+      </c>
+      <c r="G438">
+        <v>2343</v>
+      </c>
+      <c r="H438">
+        <v>1</v>
+      </c>
+      <c r="I438">
+        <v>0</v>
+      </c>
+      <c r="J438">
+        <v>0</v>
+      </c>
+      <c r="K438">
+        <v>0</v>
+      </c>
+      <c r="L438">
+        <v>0</v>
+      </c>
+      <c r="M438" t="s">
+        <v>572</v>
+      </c>
+      <c r="N438" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="439" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>613</v>
+      </c>
+      <c r="B439" t="s">
+        <v>15</v>
+      </c>
+      <c r="C439" t="s">
+        <v>16</v>
+      </c>
+      <c r="D439" t="s">
+        <v>486</v>
+      </c>
+      <c r="E439" t="s">
+        <v>26</v>
+      </c>
+      <c r="F439">
+        <v>2343</v>
+      </c>
+      <c r="G439">
+        <v>2352</v>
+      </c>
+      <c r="H439">
+        <v>9</v>
+      </c>
+      <c r="I439">
+        <v>0</v>
+      </c>
+      <c r="J439">
+        <v>0</v>
+      </c>
+      <c r="K439">
+        <v>0</v>
+      </c>
+      <c r="L439">
+        <v>0</v>
+      </c>
+      <c r="M439" t="s">
+        <v>571</v>
+      </c>
+      <c r="N439" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="440" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>614</v>
+      </c>
+      <c r="B440" t="s">
+        <v>15</v>
+      </c>
+      <c r="C440" t="s">
+        <v>16</v>
+      </c>
+      <c r="D440" t="s">
+        <v>278</v>
+      </c>
+      <c r="E440" t="s">
+        <v>26</v>
+      </c>
+      <c r="F440">
+        <v>2352</v>
+      </c>
+      <c r="G440">
+        <v>2360</v>
+      </c>
+      <c r="H440">
+        <v>8</v>
+      </c>
+      <c r="I440">
+        <v>0</v>
+      </c>
+      <c r="J440">
+        <v>0</v>
+      </c>
+      <c r="K440">
+        <v>0</v>
+      </c>
+      <c r="L440">
+        <v>0</v>
+      </c>
+      <c r="M440" t="s">
+        <v>573</v>
+      </c>
+      <c r="N440" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="441" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>615</v>
+      </c>
+      <c r="B441" t="s">
+        <v>15</v>
+      </c>
+      <c r="C441" t="s">
+        <v>16</v>
+      </c>
+      <c r="D441" t="s">
+        <v>278</v>
+      </c>
+      <c r="E441" t="s">
+        <v>26</v>
+      </c>
+      <c r="F441">
+        <v>2360</v>
+      </c>
+      <c r="G441">
+        <v>2367</v>
+      </c>
+      <c r="H441">
+        <v>7</v>
+      </c>
+      <c r="I441">
+        <v>45</v>
+      </c>
+      <c r="J441">
+        <v>0</v>
+      </c>
+      <c r="K441">
+        <v>0</v>
+      </c>
+      <c r="L441">
+        <v>0</v>
+      </c>
+      <c r="M441" t="s">
+        <v>573</v>
+      </c>
+      <c r="N441" t="s">
+        <v>413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tractor_operations.xlsx
+++ b/data/tractor_operations.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="812">
   <si>
     <t>Date</t>
   </si>
@@ -1867,6 +1867,594 @@
   </si>
   <si>
     <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f27/3,4</t>
+  </si>
+  <si>
+    <t>Top soil f27 feeder</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f27 for replanting</t>
+  </si>
+  <si>
+    <t>Top soil f4 feeder</t>
+  </si>
+  <si>
+    <t>Top soil f4  for backfilling</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f31/1,2,3,4</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f27/1,2</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f32/1,2,3</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/1 for gap filling</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f1/1 for gap filling</t>
+  </si>
+  <si>
+    <t>Top soil f32/1 feeder</t>
+  </si>
+  <si>
+    <t>Gravel for 37 haulage crossing</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to 16</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f31/5,6,7,8,9</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f32/5,6,7</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f4 for replanting</t>
+  </si>
+  <si>
+    <t>DG4000</t>
+  </si>
+  <si>
+    <t>DG01001</t>
+  </si>
+  <si>
+    <t>DG32001</t>
+  </si>
+  <si>
+    <t>M. Nathan</t>
+  </si>
+  <si>
+    <t>F. Palanjeta</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>Ploughing f4</t>
+  </si>
+  <si>
+    <t>Harrowing f27</t>
+  </si>
+  <si>
+    <t>Harrowing f4</t>
+  </si>
+  <si>
+    <t>Cross harrowing f4</t>
+  </si>
+  <si>
+    <t>Cross harrowing f27</t>
+  </si>
+  <si>
+    <t>Water bowsery to f32 harvesting</t>
+  </si>
+  <si>
+    <t>Ridging f27</t>
+  </si>
+  <si>
+    <t>Ripping feeder f27</t>
+  </si>
+  <si>
+    <t>Ridging f4</t>
+  </si>
+  <si>
+    <t>Seedcane delivery f27 replanting</t>
+  </si>
+  <si>
+    <t>Water bowsery to f37 harvesting</t>
+  </si>
+  <si>
+    <t>Ripping feeder f32</t>
+  </si>
+  <si>
+    <t>Harrowing feeder f32</t>
+  </si>
+  <si>
+    <t>Feeder works</t>
+  </si>
+  <si>
+    <t>2025-06-9</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/8 for gap filling</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/5 for gap filling</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/13 for gap filling</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/10,11,12</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f18 harvesting</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery  to f1/1,2,3</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f37/1,2  for gap filling</t>
+  </si>
+  <si>
+    <t>Waterbowsery to</t>
+  </si>
+  <si>
+    <t>DG18000</t>
+  </si>
+  <si>
+    <t>On break down</t>
+  </si>
+  <si>
+    <t>Ferrying top soil to f4 feeder</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f37/3,4</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f4/3,4</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/2 for gap filling</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f1/5 for gap filling</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f11/6,7,8,9</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f34 harvesting</t>
+  </si>
+  <si>
+    <t>Gravel to f20 backfilling canal</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f25/5,6</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f31/1</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f36/1,2</t>
+  </si>
+  <si>
+    <t>Ferrying top f37/3 feeder maintenance</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f22 harvesting</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f11/10</t>
+  </si>
+  <si>
+    <t>Gravel to f20 haulage crossing</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f20 harvesting</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f11/13,14,15</t>
+  </si>
+  <si>
+    <t>Ferrying top soil to f31 feeder</t>
+  </si>
+  <si>
+    <t>Gravel to f18 haulage crossing</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f1/4,5,6</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f34/1,2,3,4,5</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f31/3 &amp; f32/1</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f31/4, f32/4</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f11/1,2</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f32/5, f31/8</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f36/1</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f32/6, f37/4</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f32/6</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f18/1,2, f20/5,6,7,8</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f31/8</t>
+  </si>
+  <si>
+    <t>Ferrying top soil to f20 feeder</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f22/1,2,3,4</t>
+  </si>
+  <si>
+    <t>Waterbowsery to f8 harvesting</t>
+  </si>
+  <si>
+    <t>Ferrying top soil to f18/4 feeder</t>
+  </si>
+  <si>
+    <t>Gravel to f8 haulage crossing</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f34/1</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f25/5</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery to f18/1,2,3</t>
+  </si>
+  <si>
+    <t>Ferrying top soil to f18/1 feeder</t>
+  </si>
+  <si>
+    <t>Seedcane delivery to f34/3</t>
+  </si>
+  <si>
+    <t>DG01005</t>
+  </si>
+  <si>
+    <t>DG22000</t>
+  </si>
+  <si>
+    <t>DG20005</t>
+  </si>
+  <si>
+    <t>DG18005</t>
+  </si>
+  <si>
+    <t>DG34005</t>
+  </si>
+  <si>
+    <t>DG32005</t>
+  </si>
+  <si>
+    <t>DG31001</t>
+  </si>
+  <si>
+    <t>DG36001</t>
+  </si>
+  <si>
+    <t>DG34001</t>
+  </si>
+  <si>
+    <t>DG32006</t>
+  </si>
+  <si>
+    <t>DG22001</t>
+  </si>
+  <si>
+    <t>DG18004</t>
+  </si>
+  <si>
+    <t>DG18001</t>
+  </si>
+  <si>
+    <t>DG34003</t>
+  </si>
+  <si>
+    <t>DG01004</t>
+  </si>
+  <si>
+    <t>DG31003</t>
+  </si>
+  <si>
+    <t>DG31004</t>
+  </si>
+  <si>
+    <t>DG20004</t>
+  </si>
+  <si>
+    <t>DG22004</t>
+  </si>
+  <si>
+    <t>DG34004</t>
+  </si>
+  <si>
+    <t>DG20006</t>
+  </si>
+  <si>
+    <t>DG37004</t>
+  </si>
+  <si>
+    <t>DG20008</t>
+  </si>
+  <si>
+    <t>DG08000</t>
+  </si>
+  <si>
+    <t>2025-07-16</t>
+  </si>
+  <si>
+    <t>2025-07-17</t>
+  </si>
+  <si>
+    <t>2025-07-18</t>
+  </si>
+  <si>
+    <t>2025-07-19</t>
+  </si>
+  <si>
+    <t>2025-07-20</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
+    <t>2025-07-26</t>
+  </si>
+  <si>
+    <t>2025-07-27</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-07-29</t>
+  </si>
+  <si>
+    <t>2025-07-30</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>2025-07-1</t>
+  </si>
+  <si>
+    <t>2025-07-2</t>
+  </si>
+  <si>
+    <t>2025-07-3</t>
+  </si>
+  <si>
+    <t>2025-07-4</t>
+  </si>
+  <si>
+    <t>2025-07-5</t>
+  </si>
+  <si>
+    <t>2025-07-6</t>
+  </si>
+  <si>
+    <t>2025-07-7</t>
+  </si>
+  <si>
+    <t>2025-07-8</t>
+  </si>
+  <si>
+    <t>2025-07-9</t>
+  </si>
+  <si>
+    <t>2025-07-10</t>
+  </si>
+  <si>
+    <t>2025-07-11</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
+  </si>
+  <si>
+    <t>2025-07-13</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
+    <t>Tine cultivation f37/2</t>
+  </si>
+  <si>
+    <t>Seedcane delivery f4 replanting</t>
+  </si>
+  <si>
+    <t>Tine cultivation f37/3</t>
+  </si>
+  <si>
+    <t>Tine cultivation f37/4</t>
+  </si>
+  <si>
+    <t>Transporting tyre to f4 breakdown</t>
+  </si>
+  <si>
+    <t>Water bowsery to f22 harvesting</t>
+  </si>
+  <si>
+    <t>Removing stamps at site 4 compound</t>
+  </si>
+  <si>
+    <t>Middle busting f37/2</t>
+  </si>
+  <si>
+    <t>Middle busting f37/3</t>
+  </si>
+  <si>
+    <t>Middle busting f37/4</t>
+  </si>
+  <si>
+    <t>Middle busting f34/1</t>
+  </si>
+  <si>
+    <t>Middle busting f34/2</t>
+  </si>
+  <si>
+    <t>Boom sprayer calibration</t>
+  </si>
+  <si>
+    <t>Middle busting f34/3</t>
+  </si>
+  <si>
+    <t>Middle busting f34/4</t>
+  </si>
+  <si>
+    <t>Middle busting f34/5</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f11/3,4,5</t>
+  </si>
+  <si>
+    <t>Fertilizer delivery f20/1,2,3,4</t>
+  </si>
+  <si>
+    <t>Middle busting f20/1</t>
+  </si>
+  <si>
+    <t>Middle busting f20/2</t>
+  </si>
+  <si>
+    <t>Middle busting f20/3</t>
+  </si>
+  <si>
+    <t>Middle busting f20/4</t>
+  </si>
+  <si>
+    <t>Middle busting f18/3</t>
+  </si>
+  <si>
+    <t>Middle busting f18/4</t>
+  </si>
+  <si>
+    <t>Middle busting f18/5</t>
+  </si>
+  <si>
+    <t>Towing haulage vehicle kk7468 at liwaadzi</t>
+  </si>
+  <si>
+    <t>Middle busting f22/1</t>
+  </si>
+  <si>
+    <t>Middle busting f22/2</t>
+  </si>
+  <si>
+    <t>Middle busting f22/3</t>
+  </si>
+  <si>
+    <t>Middle busting f22/4</t>
+  </si>
+  <si>
+    <t>Middle busting f18/1</t>
+  </si>
+  <si>
+    <t>Middle busting f18/2</t>
+  </si>
+  <si>
+    <t>Middle busting f20/5</t>
+  </si>
+  <si>
+    <t>Middle busting f20/6</t>
+  </si>
+  <si>
+    <t>Middle busting f20/7</t>
+  </si>
+  <si>
+    <t>Middle busting f20/8</t>
+  </si>
+  <si>
+    <t>Middle busting f8/1</t>
+  </si>
+  <si>
+    <t>Middle busting f8/2</t>
+  </si>
+  <si>
+    <t>Middle busting f8/3</t>
+  </si>
+  <si>
+    <t>Boom sprayer</t>
+  </si>
+  <si>
+    <t>DG37002</t>
+  </si>
+  <si>
+    <t>Tree cutting</t>
+  </si>
+  <si>
+    <t>DG34002</t>
+  </si>
+  <si>
+    <t>DG20001</t>
+  </si>
+  <si>
+    <t>DG20002</t>
+  </si>
+  <si>
+    <t>DG18002</t>
+  </si>
+  <si>
+    <t>DG18003</t>
+  </si>
+  <si>
+    <t>DG22003</t>
+  </si>
+  <si>
+    <t>DG20003</t>
+  </si>
+  <si>
+    <t>DG22002</t>
+  </si>
+  <si>
+    <t>DG20007</t>
+  </si>
+  <si>
+    <t>DG08001</t>
+  </si>
+  <si>
+    <t>DG08002</t>
+  </si>
+  <si>
+    <t>DG08003</t>
   </si>
 </sst>
 </file>
@@ -1925,12 +2513,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2233,11 +2822,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N441"/>
+  <dimension ref="A1:N613"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="43.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21468,6 +22063,7545 @@
         <v>413</v>
       </c>
     </row>
+    <row r="442" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>607</v>
+      </c>
+      <c r="B442" t="s">
+        <v>137</v>
+      </c>
+      <c r="C442" t="s">
+        <v>635</v>
+      </c>
+      <c r="D442" t="s">
+        <v>486</v>
+      </c>
+      <c r="E442" t="s">
+        <v>43</v>
+      </c>
+      <c r="F442">
+        <v>8787</v>
+      </c>
+      <c r="G442">
+        <v>8788</v>
+      </c>
+      <c r="H442">
+        <v>1</v>
+      </c>
+      <c r="I442">
+        <v>50</v>
+      </c>
+      <c r="J442">
+        <v>0</v>
+      </c>
+      <c r="K442">
+        <v>0</v>
+      </c>
+      <c r="L442">
+        <v>0</v>
+      </c>
+      <c r="M442" t="s">
+        <v>616</v>
+      </c>
+      <c r="N442" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>607</v>
+      </c>
+      <c r="B443" t="s">
+        <v>137</v>
+      </c>
+      <c r="C443" t="s">
+        <v>635</v>
+      </c>
+      <c r="D443" t="s">
+        <v>486</v>
+      </c>
+      <c r="E443" t="s">
+        <v>17</v>
+      </c>
+      <c r="F443">
+        <v>8788</v>
+      </c>
+      <c r="G443">
+        <v>8789</v>
+      </c>
+      <c r="H443">
+        <v>1</v>
+      </c>
+      <c r="I443">
+        <v>0</v>
+      </c>
+      <c r="J443">
+        <v>0</v>
+      </c>
+      <c r="K443">
+        <v>0</v>
+      </c>
+      <c r="L443">
+        <v>0</v>
+      </c>
+      <c r="M443" t="s">
+        <v>617</v>
+      </c>
+      <c r="N443" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>607</v>
+      </c>
+      <c r="B444" t="s">
+        <v>137</v>
+      </c>
+      <c r="C444" t="s">
+        <v>635</v>
+      </c>
+      <c r="D444" t="s">
+        <v>486</v>
+      </c>
+      <c r="E444" t="s">
+        <v>26</v>
+      </c>
+      <c r="F444">
+        <v>8789</v>
+      </c>
+      <c r="G444">
+        <v>8792</v>
+      </c>
+      <c r="H444">
+        <v>3</v>
+      </c>
+      <c r="I444">
+        <v>0</v>
+      </c>
+      <c r="J444">
+        <v>0</v>
+      </c>
+      <c r="K444">
+        <v>0</v>
+      </c>
+      <c r="L444">
+        <v>0</v>
+      </c>
+      <c r="M444" t="s">
+        <v>618</v>
+      </c>
+      <c r="N444" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="445" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>608</v>
+      </c>
+      <c r="B445" t="s">
+        <v>137</v>
+      </c>
+      <c r="C445" t="s">
+        <v>635</v>
+      </c>
+      <c r="D445" t="s">
+        <v>278</v>
+      </c>
+      <c r="E445" t="s">
+        <v>17</v>
+      </c>
+      <c r="F445">
+        <v>8792</v>
+      </c>
+      <c r="G445">
+        <v>8793</v>
+      </c>
+      <c r="H445">
+        <v>1</v>
+      </c>
+      <c r="I445">
+        <v>0</v>
+      </c>
+      <c r="J445">
+        <v>0</v>
+      </c>
+      <c r="K445">
+        <v>0</v>
+      </c>
+      <c r="L445">
+        <v>0</v>
+      </c>
+      <c r="M445" t="s">
+        <v>619</v>
+      </c>
+      <c r="N445" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="446" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>608</v>
+      </c>
+      <c r="B446" t="s">
+        <v>137</v>
+      </c>
+      <c r="C446" t="s">
+        <v>635</v>
+      </c>
+      <c r="D446" t="s">
+        <v>486</v>
+      </c>
+      <c r="E446" t="s">
+        <v>17</v>
+      </c>
+      <c r="F446">
+        <v>8793</v>
+      </c>
+      <c r="G446">
+        <v>8794</v>
+      </c>
+      <c r="H446">
+        <v>1</v>
+      </c>
+      <c r="I446">
+        <v>0</v>
+      </c>
+      <c r="J446">
+        <v>0</v>
+      </c>
+      <c r="K446">
+        <v>0</v>
+      </c>
+      <c r="L446">
+        <v>0</v>
+      </c>
+      <c r="M446" t="s">
+        <v>617</v>
+      </c>
+      <c r="N446" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="447" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>609</v>
+      </c>
+      <c r="B447" t="s">
+        <v>137</v>
+      </c>
+      <c r="C447" t="s">
+        <v>635</v>
+      </c>
+      <c r="D447" t="s">
+        <v>632</v>
+      </c>
+      <c r="E447" t="s">
+        <v>17</v>
+      </c>
+      <c r="F447">
+        <v>8794</v>
+      </c>
+      <c r="G447">
+        <v>8795</v>
+      </c>
+      <c r="H447">
+        <v>1</v>
+      </c>
+      <c r="I447">
+        <v>0</v>
+      </c>
+      <c r="J447">
+        <v>0</v>
+      </c>
+      <c r="K447">
+        <v>0</v>
+      </c>
+      <c r="L447">
+        <v>0</v>
+      </c>
+      <c r="M447" t="s">
+        <v>620</v>
+      </c>
+      <c r="N447" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="448" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>609</v>
+      </c>
+      <c r="B448" t="s">
+        <v>137</v>
+      </c>
+      <c r="C448" t="s">
+        <v>635</v>
+      </c>
+      <c r="D448" t="s">
+        <v>486</v>
+      </c>
+      <c r="E448" t="s">
+        <v>26</v>
+      </c>
+      <c r="F448">
+        <v>8795</v>
+      </c>
+      <c r="G448">
+        <v>8797</v>
+      </c>
+      <c r="H448">
+        <v>2</v>
+      </c>
+      <c r="I448">
+        <v>0</v>
+      </c>
+      <c r="J448">
+        <v>0</v>
+      </c>
+      <c r="K448">
+        <v>0</v>
+      </c>
+      <c r="L448">
+        <v>0</v>
+      </c>
+      <c r="M448" t="s">
+        <v>618</v>
+      </c>
+      <c r="N448" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>610</v>
+      </c>
+      <c r="B449" t="s">
+        <v>137</v>
+      </c>
+      <c r="C449" t="s">
+        <v>635</v>
+      </c>
+      <c r="D449" t="s">
+        <v>496</v>
+      </c>
+      <c r="E449" t="s">
+        <v>43</v>
+      </c>
+      <c r="F449">
+        <v>8797</v>
+      </c>
+      <c r="G449">
+        <v>8798</v>
+      </c>
+      <c r="H449">
+        <v>1</v>
+      </c>
+      <c r="I449">
+        <v>60</v>
+      </c>
+      <c r="J449">
+        <v>0</v>
+      </c>
+      <c r="K449">
+        <v>0</v>
+      </c>
+      <c r="L449">
+        <v>0</v>
+      </c>
+      <c r="M449" t="s">
+        <v>621</v>
+      </c>
+      <c r="N449" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>610</v>
+      </c>
+      <c r="B450" t="s">
+        <v>137</v>
+      </c>
+      <c r="C450" t="s">
+        <v>635</v>
+      </c>
+      <c r="D450" t="s">
+        <v>278</v>
+      </c>
+      <c r="E450" t="s">
+        <v>17</v>
+      </c>
+      <c r="F450">
+        <v>8798</v>
+      </c>
+      <c r="G450">
+        <v>8799</v>
+      </c>
+      <c r="H450">
+        <v>1</v>
+      </c>
+      <c r="I450">
+        <v>0</v>
+      </c>
+      <c r="J450">
+        <v>0</v>
+      </c>
+      <c r="K450">
+        <v>0</v>
+      </c>
+      <c r="L450">
+        <v>0</v>
+      </c>
+      <c r="M450" t="s">
+        <v>620</v>
+      </c>
+      <c r="N450" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>610</v>
+      </c>
+      <c r="B451" t="s">
+        <v>137</v>
+      </c>
+      <c r="C451" t="s">
+        <v>635</v>
+      </c>
+      <c r="D451" t="s">
+        <v>486</v>
+      </c>
+      <c r="E451" t="s">
+        <v>26</v>
+      </c>
+      <c r="F451">
+        <v>8799</v>
+      </c>
+      <c r="G451">
+        <v>8800</v>
+      </c>
+      <c r="H451">
+        <v>1</v>
+      </c>
+      <c r="I451">
+        <v>0</v>
+      </c>
+      <c r="J451">
+        <v>0</v>
+      </c>
+      <c r="K451">
+        <v>0</v>
+      </c>
+      <c r="L451">
+        <v>0</v>
+      </c>
+      <c r="M451" t="s">
+        <v>618</v>
+      </c>
+      <c r="N451" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>637</v>
+      </c>
+      <c r="B452" t="s">
+        <v>137</v>
+      </c>
+      <c r="C452" t="s">
+        <v>635</v>
+      </c>
+      <c r="D452" t="s">
+        <v>486</v>
+      </c>
+      <c r="E452" t="s">
+        <v>43</v>
+      </c>
+      <c r="F452">
+        <v>8800</v>
+      </c>
+      <c r="G452">
+        <v>8801</v>
+      </c>
+      <c r="H452">
+        <v>1</v>
+      </c>
+      <c r="I452">
+        <v>0</v>
+      </c>
+      <c r="J452">
+        <v>0</v>
+      </c>
+      <c r="K452">
+        <v>0</v>
+      </c>
+      <c r="L452">
+        <v>0</v>
+      </c>
+      <c r="M452" t="s">
+        <v>622</v>
+      </c>
+      <c r="N452" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>637</v>
+      </c>
+      <c r="B453" t="s">
+        <v>137</v>
+      </c>
+      <c r="C453" t="s">
+        <v>635</v>
+      </c>
+      <c r="D453" t="s">
+        <v>585</v>
+      </c>
+      <c r="E453" t="s">
+        <v>43</v>
+      </c>
+      <c r="F453">
+        <v>8801</v>
+      </c>
+      <c r="G453">
+        <v>8802</v>
+      </c>
+      <c r="H453">
+        <v>1</v>
+      </c>
+      <c r="I453">
+        <v>0</v>
+      </c>
+      <c r="J453">
+        <v>0</v>
+      </c>
+      <c r="K453">
+        <v>0</v>
+      </c>
+      <c r="L453">
+        <v>0</v>
+      </c>
+      <c r="M453" t="s">
+        <v>623</v>
+      </c>
+      <c r="N453" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>637</v>
+      </c>
+      <c r="B454" t="s">
+        <v>137</v>
+      </c>
+      <c r="C454" t="s">
+        <v>635</v>
+      </c>
+      <c r="D454" t="s">
+        <v>486</v>
+      </c>
+      <c r="E454" t="s">
+        <v>26</v>
+      </c>
+      <c r="F454">
+        <v>8802</v>
+      </c>
+      <c r="G454">
+        <v>8803</v>
+      </c>
+      <c r="H454">
+        <v>1</v>
+      </c>
+      <c r="I454">
+        <v>0</v>
+      </c>
+      <c r="J454">
+        <v>0</v>
+      </c>
+      <c r="K454">
+        <v>0</v>
+      </c>
+      <c r="L454">
+        <v>0</v>
+      </c>
+      <c r="M454" t="s">
+        <v>618</v>
+      </c>
+      <c r="N454" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>637</v>
+      </c>
+      <c r="B455" t="s">
+        <v>137</v>
+      </c>
+      <c r="C455" t="s">
+        <v>635</v>
+      </c>
+      <c r="D455" t="s">
+        <v>534</v>
+      </c>
+      <c r="E455" t="s">
+        <v>26</v>
+      </c>
+      <c r="F455">
+        <v>8803</v>
+      </c>
+      <c r="G455">
+        <v>8804</v>
+      </c>
+      <c r="H455">
+        <v>1</v>
+      </c>
+      <c r="I455">
+        <v>0</v>
+      </c>
+      <c r="J455">
+        <v>0</v>
+      </c>
+      <c r="K455">
+        <v>0</v>
+      </c>
+      <c r="L455">
+        <v>0</v>
+      </c>
+      <c r="M455" t="s">
+        <v>624</v>
+      </c>
+      <c r="N455" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>637</v>
+      </c>
+      <c r="B456" t="s">
+        <v>137</v>
+      </c>
+      <c r="C456" t="s">
+        <v>635</v>
+      </c>
+      <c r="D456" t="s">
+        <v>633</v>
+      </c>
+      <c r="E456" t="s">
+        <v>26</v>
+      </c>
+      <c r="F456">
+        <v>8804</v>
+      </c>
+      <c r="G456">
+        <v>8805</v>
+      </c>
+      <c r="H456">
+        <v>1</v>
+      </c>
+      <c r="I456">
+        <v>0</v>
+      </c>
+      <c r="J456">
+        <v>0</v>
+      </c>
+      <c r="K456">
+        <v>0</v>
+      </c>
+      <c r="L456">
+        <v>0</v>
+      </c>
+      <c r="M456" t="s">
+        <v>625</v>
+      </c>
+      <c r="N456" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>611</v>
+      </c>
+      <c r="B457" t="s">
+        <v>137</v>
+      </c>
+      <c r="C457" t="s">
+        <v>635</v>
+      </c>
+      <c r="D457" t="s">
+        <v>634</v>
+      </c>
+      <c r="E457" t="s">
+        <v>17</v>
+      </c>
+      <c r="F457">
+        <v>8805</v>
+      </c>
+      <c r="G457">
+        <v>8806</v>
+      </c>
+      <c r="H457">
+        <v>1</v>
+      </c>
+      <c r="I457">
+        <v>0</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
+      <c r="K457">
+        <v>0</v>
+      </c>
+      <c r="L457">
+        <v>0</v>
+      </c>
+      <c r="M457" t="s">
+        <v>626</v>
+      </c>
+      <c r="N457" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>611</v>
+      </c>
+      <c r="B458" t="s">
+        <v>137</v>
+      </c>
+      <c r="C458" t="s">
+        <v>635</v>
+      </c>
+      <c r="D458" t="s">
+        <v>586</v>
+      </c>
+      <c r="E458" t="s">
+        <v>17</v>
+      </c>
+      <c r="F458">
+        <v>8806</v>
+      </c>
+      <c r="G458">
+        <v>8807</v>
+      </c>
+      <c r="H458">
+        <v>1</v>
+      </c>
+      <c r="I458">
+        <v>0</v>
+      </c>
+      <c r="J458">
+        <v>0</v>
+      </c>
+      <c r="K458">
+        <v>0</v>
+      </c>
+      <c r="L458">
+        <v>0</v>
+      </c>
+      <c r="M458" t="s">
+        <v>627</v>
+      </c>
+      <c r="N458" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>611</v>
+      </c>
+      <c r="B459" t="s">
+        <v>137</v>
+      </c>
+      <c r="C459" t="s">
+        <v>635</v>
+      </c>
+      <c r="D459" t="s">
+        <v>486</v>
+      </c>
+      <c r="E459" t="s">
+        <v>26</v>
+      </c>
+      <c r="F459">
+        <v>8807</v>
+      </c>
+      <c r="G459">
+        <v>8809</v>
+      </c>
+      <c r="H459">
+        <v>2</v>
+      </c>
+      <c r="I459">
+        <v>0</v>
+      </c>
+      <c r="J459">
+        <v>0</v>
+      </c>
+      <c r="K459">
+        <v>0</v>
+      </c>
+      <c r="L459">
+        <v>0</v>
+      </c>
+      <c r="M459" t="s">
+        <v>618</v>
+      </c>
+      <c r="N459" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>612</v>
+      </c>
+      <c r="B460" t="s">
+        <v>137</v>
+      </c>
+      <c r="C460" t="s">
+        <v>635</v>
+      </c>
+      <c r="D460" t="s">
+        <v>486</v>
+      </c>
+      <c r="E460" t="s">
+        <v>26</v>
+      </c>
+      <c r="F460">
+        <v>8809</v>
+      </c>
+      <c r="G460">
+        <v>8812</v>
+      </c>
+      <c r="H460">
+        <v>3</v>
+      </c>
+      <c r="I460">
+        <v>45</v>
+      </c>
+      <c r="J460">
+        <v>0</v>
+      </c>
+      <c r="K460">
+        <v>0</v>
+      </c>
+      <c r="L460">
+        <v>0</v>
+      </c>
+      <c r="M460" t="s">
+        <v>618</v>
+      </c>
+      <c r="N460" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>612</v>
+      </c>
+      <c r="B461" t="s">
+        <v>137</v>
+      </c>
+      <c r="C461" t="s">
+        <v>635</v>
+      </c>
+      <c r="D461" t="s">
+        <v>487</v>
+      </c>
+      <c r="E461" t="s">
+        <v>43</v>
+      </c>
+      <c r="F461">
+        <v>8812</v>
+      </c>
+      <c r="G461">
+        <v>8813</v>
+      </c>
+      <c r="H461">
+        <v>1</v>
+      </c>
+      <c r="I461">
+        <v>0</v>
+      </c>
+      <c r="J461">
+        <v>0</v>
+      </c>
+      <c r="K461">
+        <v>0</v>
+      </c>
+      <c r="L461">
+        <v>0</v>
+      </c>
+      <c r="M461" t="s">
+        <v>628</v>
+      </c>
+      <c r="N461" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>613</v>
+      </c>
+      <c r="B462" t="s">
+        <v>137</v>
+      </c>
+      <c r="C462" t="s">
+        <v>635</v>
+      </c>
+      <c r="D462" t="s">
+        <v>496</v>
+      </c>
+      <c r="E462" t="s">
+        <v>43</v>
+      </c>
+      <c r="F462">
+        <v>8813</v>
+      </c>
+      <c r="G462">
+        <v>8814</v>
+      </c>
+      <c r="H462">
+        <v>1</v>
+      </c>
+      <c r="I462">
+        <v>0</v>
+      </c>
+      <c r="J462">
+        <v>0</v>
+      </c>
+      <c r="K462">
+        <v>0</v>
+      </c>
+      <c r="L462">
+        <v>0</v>
+      </c>
+      <c r="M462" t="s">
+        <v>629</v>
+      </c>
+      <c r="N462" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>613</v>
+      </c>
+      <c r="B463" t="s">
+        <v>137</v>
+      </c>
+      <c r="C463" t="s">
+        <v>635</v>
+      </c>
+      <c r="D463" t="s">
+        <v>585</v>
+      </c>
+      <c r="E463" t="s">
+        <v>43</v>
+      </c>
+      <c r="F463">
+        <v>8814</v>
+      </c>
+      <c r="G463">
+        <v>8815</v>
+      </c>
+      <c r="H463">
+        <v>1</v>
+      </c>
+      <c r="I463">
+        <v>0</v>
+      </c>
+      <c r="J463">
+        <v>0</v>
+      </c>
+      <c r="K463">
+        <v>0</v>
+      </c>
+      <c r="L463">
+        <v>0</v>
+      </c>
+      <c r="M463" t="s">
+        <v>630</v>
+      </c>
+      <c r="N463" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>613</v>
+      </c>
+      <c r="B464" t="s">
+        <v>137</v>
+      </c>
+      <c r="C464" t="s">
+        <v>636</v>
+      </c>
+      <c r="D464" t="s">
+        <v>486</v>
+      </c>
+      <c r="E464" t="s">
+        <v>26</v>
+      </c>
+      <c r="F464">
+        <v>8815</v>
+      </c>
+      <c r="G464">
+        <v>8816</v>
+      </c>
+      <c r="H464">
+        <v>1</v>
+      </c>
+      <c r="I464">
+        <v>0</v>
+      </c>
+      <c r="J464">
+        <v>0</v>
+      </c>
+      <c r="K464">
+        <v>0</v>
+      </c>
+      <c r="L464">
+        <v>0</v>
+      </c>
+      <c r="M464" t="s">
+        <v>618</v>
+      </c>
+      <c r="N464" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>614</v>
+      </c>
+      <c r="B465" t="s">
+        <v>137</v>
+      </c>
+      <c r="C465" t="s">
+        <v>636</v>
+      </c>
+      <c r="D465" t="s">
+        <v>278</v>
+      </c>
+      <c r="E465" t="s">
+        <v>26</v>
+      </c>
+      <c r="F465">
+        <v>8816</v>
+      </c>
+      <c r="G465">
+        <v>8819</v>
+      </c>
+      <c r="H465">
+        <v>3</v>
+      </c>
+      <c r="I465">
+        <v>50</v>
+      </c>
+      <c r="J465">
+        <v>0</v>
+      </c>
+      <c r="K465">
+        <v>0</v>
+      </c>
+      <c r="L465">
+        <v>0</v>
+      </c>
+      <c r="M465" t="s">
+        <v>631</v>
+      </c>
+      <c r="N465" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>615</v>
+      </c>
+      <c r="B466" t="s">
+        <v>137</v>
+      </c>
+      <c r="C466" t="s">
+        <v>636</v>
+      </c>
+      <c r="D466" t="s">
+        <v>278</v>
+      </c>
+      <c r="E466" t="s">
+        <v>26</v>
+      </c>
+      <c r="F466">
+        <v>8819</v>
+      </c>
+      <c r="G466">
+        <v>8822</v>
+      </c>
+      <c r="H466">
+        <v>3</v>
+      </c>
+      <c r="I466">
+        <v>0</v>
+      </c>
+      <c r="J466">
+        <v>0</v>
+      </c>
+      <c r="K466">
+        <v>0</v>
+      </c>
+      <c r="L466">
+        <v>0</v>
+      </c>
+      <c r="M466" t="s">
+        <v>631</v>
+      </c>
+      <c r="N466" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>588</v>
+      </c>
+      <c r="B467" t="s">
+        <v>28</v>
+      </c>
+      <c r="C467" t="s">
+        <v>196</v>
+      </c>
+      <c r="D467" t="s">
+        <v>486</v>
+      </c>
+      <c r="E467" t="s">
+        <v>531</v>
+      </c>
+      <c r="F467">
+        <v>1348</v>
+      </c>
+      <c r="G467">
+        <v>1351</v>
+      </c>
+      <c r="H467">
+        <v>3</v>
+      </c>
+      <c r="I467">
+        <v>30</v>
+      </c>
+      <c r="J467">
+        <v>5.25</v>
+      </c>
+      <c r="K467">
+        <v>5.7</v>
+      </c>
+      <c r="L467">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M467" t="s">
+        <v>530</v>
+      </c>
+      <c r="N467" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>589</v>
+      </c>
+      <c r="B468" t="s">
+        <v>28</v>
+      </c>
+      <c r="C468" t="s">
+        <v>196</v>
+      </c>
+      <c r="D468" t="s">
+        <v>278</v>
+      </c>
+      <c r="E468" t="s">
+        <v>531</v>
+      </c>
+      <c r="F468">
+        <v>1351</v>
+      </c>
+      <c r="G468">
+        <v>1361</v>
+      </c>
+      <c r="H468">
+        <v>10</v>
+      </c>
+      <c r="I468">
+        <v>220</v>
+      </c>
+      <c r="J468">
+        <v>2.6</v>
+      </c>
+      <c r="K468">
+        <v>84.62</v>
+      </c>
+      <c r="L468">
+        <v>3.85</v>
+      </c>
+      <c r="M468" t="s">
+        <v>638</v>
+      </c>
+      <c r="N468" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>590</v>
+      </c>
+      <c r="B469" t="s">
+        <v>28</v>
+      </c>
+      <c r="C469" t="s">
+        <v>196</v>
+      </c>
+      <c r="D469" t="s">
+        <v>278</v>
+      </c>
+      <c r="E469" t="s">
+        <v>531</v>
+      </c>
+      <c r="F469">
+        <v>1361</v>
+      </c>
+      <c r="G469">
+        <v>1363</v>
+      </c>
+      <c r="H469">
+        <v>2</v>
+      </c>
+      <c r="I469">
+        <v>0</v>
+      </c>
+      <c r="J469">
+        <v>0.52</v>
+      </c>
+      <c r="K469">
+        <v>0</v>
+      </c>
+      <c r="L469">
+        <v>3.85</v>
+      </c>
+      <c r="M469" t="s">
+        <v>638</v>
+      </c>
+      <c r="N469" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>594</v>
+      </c>
+      <c r="B470" t="s">
+        <v>28</v>
+      </c>
+      <c r="C470" t="s">
+        <v>196</v>
+      </c>
+      <c r="D470" t="s">
+        <v>278</v>
+      </c>
+      <c r="E470" t="s">
+        <v>531</v>
+      </c>
+      <c r="F470">
+        <v>1363</v>
+      </c>
+      <c r="G470">
+        <v>1377</v>
+      </c>
+      <c r="H470">
+        <v>14</v>
+      </c>
+      <c r="I470">
+        <v>0</v>
+      </c>
+      <c r="J470">
+        <v>3.64</v>
+      </c>
+      <c r="K470">
+        <v>0</v>
+      </c>
+      <c r="L470">
+        <v>3.85</v>
+      </c>
+      <c r="M470" t="s">
+        <v>638</v>
+      </c>
+      <c r="N470" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>595</v>
+      </c>
+      <c r="B471" t="s">
+        <v>28</v>
+      </c>
+      <c r="C471" t="s">
+        <v>196</v>
+      </c>
+      <c r="D471" t="s">
+        <v>278</v>
+      </c>
+      <c r="E471" t="s">
+        <v>531</v>
+      </c>
+      <c r="F471">
+        <v>1377</v>
+      </c>
+      <c r="G471">
+        <v>1385</v>
+      </c>
+      <c r="H471">
+        <v>8</v>
+      </c>
+      <c r="I471">
+        <v>55</v>
+      </c>
+      <c r="J471">
+        <v>2.08</v>
+      </c>
+      <c r="K471" s="3">
+        <v>26.44</v>
+      </c>
+      <c r="L471">
+        <v>3.85</v>
+      </c>
+      <c r="M471" t="s">
+        <v>638</v>
+      </c>
+      <c r="N471" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>652</v>
+      </c>
+      <c r="B472" t="s">
+        <v>28</v>
+      </c>
+      <c r="C472" t="s">
+        <v>196</v>
+      </c>
+      <c r="D472" t="s">
+        <v>278</v>
+      </c>
+      <c r="E472" t="s">
+        <v>531</v>
+      </c>
+      <c r="F472">
+        <v>1385</v>
+      </c>
+      <c r="G472">
+        <v>1390</v>
+      </c>
+      <c r="H472">
+        <v>5</v>
+      </c>
+      <c r="I472">
+        <v>0</v>
+      </c>
+      <c r="J472">
+        <v>1.3</v>
+      </c>
+      <c r="K472">
+        <v>0</v>
+      </c>
+      <c r="L472">
+        <v>3.85</v>
+      </c>
+      <c r="M472" t="s">
+        <v>638</v>
+      </c>
+      <c r="N472" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>596</v>
+      </c>
+      <c r="B473" t="s">
+        <v>28</v>
+      </c>
+      <c r="C473" t="s">
+        <v>196</v>
+      </c>
+      <c r="D473" t="s">
+        <v>486</v>
+      </c>
+      <c r="E473" t="s">
+        <v>31</v>
+      </c>
+      <c r="F473">
+        <v>1390</v>
+      </c>
+      <c r="G473">
+        <v>1397</v>
+      </c>
+      <c r="H473">
+        <v>7</v>
+      </c>
+      <c r="I473">
+        <v>0</v>
+      </c>
+      <c r="J473">
+        <v>3.27</v>
+      </c>
+      <c r="K473">
+        <v>0</v>
+      </c>
+      <c r="L473">
+        <v>2.14</v>
+      </c>
+      <c r="M473" t="s">
+        <v>639</v>
+      </c>
+      <c r="N473" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>597</v>
+      </c>
+      <c r="B474" t="s">
+        <v>28</v>
+      </c>
+      <c r="C474" t="s">
+        <v>196</v>
+      </c>
+      <c r="D474" t="s">
+        <v>486</v>
+      </c>
+      <c r="E474" t="s">
+        <v>31</v>
+      </c>
+      <c r="F474">
+        <v>1397</v>
+      </c>
+      <c r="G474">
+        <v>1409</v>
+      </c>
+      <c r="H474">
+        <v>12</v>
+      </c>
+      <c r="I474">
+        <v>0</v>
+      </c>
+      <c r="J474" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="K474">
+        <v>0</v>
+      </c>
+      <c r="L474">
+        <v>2.14</v>
+      </c>
+      <c r="M474" t="s">
+        <v>639</v>
+      </c>
+      <c r="N474" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>598</v>
+      </c>
+      <c r="B475" t="s">
+        <v>28</v>
+      </c>
+      <c r="C475" t="s">
+        <v>196</v>
+      </c>
+      <c r="D475" t="s">
+        <v>486</v>
+      </c>
+      <c r="E475" t="s">
+        <v>31</v>
+      </c>
+      <c r="F475">
+        <v>1409</v>
+      </c>
+      <c r="G475">
+        <v>1415</v>
+      </c>
+      <c r="H475">
+        <v>6</v>
+      </c>
+      <c r="I475">
+        <v>20</v>
+      </c>
+      <c r="J475">
+        <v>2.79</v>
+      </c>
+      <c r="K475">
+        <v>7.17</v>
+      </c>
+      <c r="L475">
+        <v>2.15</v>
+      </c>
+      <c r="M475" t="s">
+        <v>639</v>
+      </c>
+      <c r="N475" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>599</v>
+      </c>
+      <c r="B476" t="s">
+        <v>28</v>
+      </c>
+      <c r="C476" t="s">
+        <v>196</v>
+      </c>
+      <c r="D476" t="s">
+        <v>540</v>
+      </c>
+      <c r="E476" t="s">
+        <v>492</v>
+      </c>
+      <c r="F476">
+        <v>1415</v>
+      </c>
+      <c r="G476">
+        <v>1418</v>
+      </c>
+      <c r="H476">
+        <v>3</v>
+      </c>
+      <c r="I476">
+        <v>229</v>
+      </c>
+      <c r="J476" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="K476">
+        <v>76.33</v>
+      </c>
+      <c r="L476">
+        <v>0.97</v>
+      </c>
+      <c r="M476" t="s">
+        <v>529</v>
+      </c>
+      <c r="N476" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>599</v>
+      </c>
+      <c r="B477" t="s">
+        <v>28</v>
+      </c>
+      <c r="C477" t="s">
+        <v>196</v>
+      </c>
+      <c r="D477" t="s">
+        <v>486</v>
+      </c>
+      <c r="E477" t="s">
+        <v>31</v>
+      </c>
+      <c r="F477">
+        <v>1418</v>
+      </c>
+      <c r="G477">
+        <v>1423</v>
+      </c>
+      <c r="H477">
+        <v>5</v>
+      </c>
+      <c r="I477">
+        <v>0</v>
+      </c>
+      <c r="J477">
+        <v>2.33</v>
+      </c>
+      <c r="K477">
+        <v>0</v>
+      </c>
+      <c r="L477">
+        <v>2.15</v>
+      </c>
+      <c r="M477" t="s">
+        <v>639</v>
+      </c>
+      <c r="N477" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>600</v>
+      </c>
+      <c r="B478" t="s">
+        <v>28</v>
+      </c>
+      <c r="C478" t="s">
+        <v>196</v>
+      </c>
+      <c r="D478" t="s">
+        <v>278</v>
+      </c>
+      <c r="E478" t="s">
+        <v>31</v>
+      </c>
+      <c r="F478">
+        <v>1423</v>
+      </c>
+      <c r="G478">
+        <v>1434</v>
+      </c>
+      <c r="H478">
+        <v>11</v>
+      </c>
+      <c r="I478">
+        <v>17</v>
+      </c>
+      <c r="J478">
+        <v>5.87</v>
+      </c>
+      <c r="K478">
+        <v>2.9</v>
+      </c>
+      <c r="L478">
+        <v>1.87</v>
+      </c>
+      <c r="M478" t="s">
+        <v>640</v>
+      </c>
+      <c r="N478" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>601</v>
+      </c>
+      <c r="B479" t="s">
+        <v>28</v>
+      </c>
+      <c r="C479" t="s">
+        <v>196</v>
+      </c>
+      <c r="D479" t="s">
+        <v>278</v>
+      </c>
+      <c r="E479" t="s">
+        <v>31</v>
+      </c>
+      <c r="F479">
+        <v>1434</v>
+      </c>
+      <c r="G479">
+        <v>1442</v>
+      </c>
+      <c r="H479">
+        <v>8</v>
+      </c>
+      <c r="I479">
+        <v>0</v>
+      </c>
+      <c r="J479">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="K479">
+        <v>0</v>
+      </c>
+      <c r="L479">
+        <v>1.87</v>
+      </c>
+      <c r="M479" t="s">
+        <v>641</v>
+      </c>
+      <c r="N479" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>602</v>
+      </c>
+      <c r="B480" t="s">
+        <v>28</v>
+      </c>
+      <c r="C480" t="s">
+        <v>196</v>
+      </c>
+      <c r="D480" t="s">
+        <v>486</v>
+      </c>
+      <c r="E480" t="s">
+        <v>31</v>
+      </c>
+      <c r="F480">
+        <v>1442</v>
+      </c>
+      <c r="G480">
+        <v>1449</v>
+      </c>
+      <c r="H480">
+        <v>7</v>
+      </c>
+      <c r="I480">
+        <v>23.5</v>
+      </c>
+      <c r="J480">
+        <v>5.44</v>
+      </c>
+      <c r="L480">
+        <v>1.29</v>
+      </c>
+      <c r="M480" t="s">
+        <v>642</v>
+      </c>
+      <c r="N480" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>603</v>
+      </c>
+      <c r="B481" t="s">
+        <v>28</v>
+      </c>
+      <c r="C481" t="s">
+        <v>196</v>
+      </c>
+      <c r="D481" t="s">
+        <v>585</v>
+      </c>
+      <c r="E481" t="s">
+        <v>485</v>
+      </c>
+      <c r="F481">
+        <v>1449</v>
+      </c>
+      <c r="G481">
+        <v>1450</v>
+      </c>
+      <c r="H481">
+        <v>1</v>
+      </c>
+      <c r="I481">
+        <v>16.5</v>
+      </c>
+      <c r="J481">
+        <v>0</v>
+      </c>
+      <c r="K481">
+        <v>0</v>
+      </c>
+      <c r="L481">
+        <v>0</v>
+      </c>
+      <c r="M481" t="s">
+        <v>643</v>
+      </c>
+      <c r="N481" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>603</v>
+      </c>
+      <c r="B482" t="s">
+        <v>28</v>
+      </c>
+      <c r="C482" t="s">
+        <v>196</v>
+      </c>
+      <c r="D482" t="s">
+        <v>486</v>
+      </c>
+      <c r="E482" t="s">
+        <v>31</v>
+      </c>
+      <c r="F482">
+        <v>1450</v>
+      </c>
+      <c r="G482">
+        <v>1461</v>
+      </c>
+      <c r="H482">
+        <v>11</v>
+      </c>
+      <c r="I482">
+        <v>0</v>
+      </c>
+      <c r="J482">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="K482">
+        <v>0</v>
+      </c>
+      <c r="L482">
+        <v>1.29</v>
+      </c>
+      <c r="M482" t="s">
+        <v>642</v>
+      </c>
+      <c r="N482" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>604</v>
+      </c>
+      <c r="B483" t="s">
+        <v>28</v>
+      </c>
+      <c r="C483" t="s">
+        <v>196</v>
+      </c>
+      <c r="D483" t="s">
+        <v>486</v>
+      </c>
+      <c r="E483" t="s">
+        <v>40</v>
+      </c>
+      <c r="F483">
+        <v>1461</v>
+      </c>
+      <c r="G483">
+        <v>1468</v>
+      </c>
+      <c r="H483">
+        <v>7</v>
+      </c>
+      <c r="I483">
+        <v>115</v>
+      </c>
+      <c r="J483">
+        <v>4.67</v>
+      </c>
+      <c r="K483">
+        <v>24.63</v>
+      </c>
+      <c r="L483">
+        <v>1.5</v>
+      </c>
+      <c r="M483" t="s">
+        <v>644</v>
+      </c>
+      <c r="N483" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>605</v>
+      </c>
+      <c r="B484" t="s">
+        <v>28</v>
+      </c>
+      <c r="C484" t="s">
+        <v>196</v>
+      </c>
+      <c r="D484" t="s">
+        <v>486</v>
+      </c>
+      <c r="E484" t="s">
+        <v>40</v>
+      </c>
+      <c r="F484">
+        <v>1468</v>
+      </c>
+      <c r="G484">
+        <v>1479</v>
+      </c>
+      <c r="H484">
+        <v>11</v>
+      </c>
+      <c r="I484">
+        <v>0</v>
+      </c>
+      <c r="J484">
+        <v>7.33</v>
+      </c>
+      <c r="K484">
+        <v>0</v>
+      </c>
+      <c r="L484">
+        <v>1.5</v>
+      </c>
+      <c r="M484" t="s">
+        <v>644</v>
+      </c>
+      <c r="N484" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>606</v>
+      </c>
+      <c r="B485" t="s">
+        <v>28</v>
+      </c>
+      <c r="C485" t="s">
+        <v>196</v>
+      </c>
+      <c r="D485" t="s">
+        <v>486</v>
+      </c>
+      <c r="E485" t="s">
+        <v>40</v>
+      </c>
+      <c r="F485">
+        <v>1479</v>
+      </c>
+      <c r="G485">
+        <v>1482</v>
+      </c>
+      <c r="H485">
+        <v>3</v>
+      </c>
+      <c r="I485">
+        <v>204</v>
+      </c>
+      <c r="J485">
+        <v>1.99</v>
+      </c>
+      <c r="K485">
+        <v>102.51</v>
+      </c>
+      <c r="L485">
+        <v>1.51</v>
+      </c>
+      <c r="M485" t="s">
+        <v>644</v>
+      </c>
+      <c r="N485" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>606</v>
+      </c>
+      <c r="B486" t="s">
+        <v>28</v>
+      </c>
+      <c r="C486" t="s">
+        <v>196</v>
+      </c>
+      <c r="D486" t="s">
+        <v>486</v>
+      </c>
+      <c r="E486" t="s">
+        <v>651</v>
+      </c>
+      <c r="F486">
+        <v>1482</v>
+      </c>
+      <c r="G486">
+        <v>1485</v>
+      </c>
+      <c r="H486">
+        <v>3</v>
+      </c>
+      <c r="I486">
+        <v>0</v>
+      </c>
+      <c r="J486">
+        <v>1</v>
+      </c>
+      <c r="K486">
+        <v>0</v>
+      </c>
+      <c r="L486">
+        <v>3</v>
+      </c>
+      <c r="M486" t="s">
+        <v>645</v>
+      </c>
+      <c r="N486" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>606</v>
+      </c>
+      <c r="B487" t="s">
+        <v>28</v>
+      </c>
+      <c r="C487" t="s">
+        <v>196</v>
+      </c>
+      <c r="D487" t="s">
+        <v>278</v>
+      </c>
+      <c r="E487" t="s">
+        <v>31</v>
+      </c>
+      <c r="F487">
+        <v>1485</v>
+      </c>
+      <c r="G487">
+        <v>1489</v>
+      </c>
+      <c r="H487">
+        <v>4</v>
+      </c>
+      <c r="I487">
+        <v>0</v>
+      </c>
+      <c r="J487" s="3">
+        <v>2.39</v>
+      </c>
+      <c r="K487">
+        <v>0</v>
+      </c>
+      <c r="L487">
+        <v>1.67</v>
+      </c>
+      <c r="M487" t="s">
+        <v>641</v>
+      </c>
+      <c r="N487" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>607</v>
+      </c>
+      <c r="B488" t="s">
+        <v>28</v>
+      </c>
+      <c r="C488" t="s">
+        <v>196</v>
+      </c>
+      <c r="D488" t="s">
+        <v>278</v>
+      </c>
+      <c r="E488" t="s">
+        <v>31</v>
+      </c>
+      <c r="F488">
+        <v>1489</v>
+      </c>
+      <c r="G488">
+        <v>1497</v>
+      </c>
+      <c r="H488">
+        <v>8</v>
+      </c>
+      <c r="I488">
+        <v>36</v>
+      </c>
+      <c r="J488" s="3">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K488">
+        <v>7.55</v>
+      </c>
+      <c r="L488">
+        <v>1.67</v>
+      </c>
+      <c r="M488" t="s">
+        <v>641</v>
+      </c>
+      <c r="N488" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>608</v>
+      </c>
+      <c r="B489" t="s">
+        <v>28</v>
+      </c>
+      <c r="C489" t="s">
+        <v>196</v>
+      </c>
+      <c r="D489" t="s">
+        <v>278</v>
+      </c>
+      <c r="E489" t="s">
+        <v>31</v>
+      </c>
+      <c r="F489">
+        <v>1497</v>
+      </c>
+      <c r="G489">
+        <v>1502</v>
+      </c>
+      <c r="H489">
+        <v>5</v>
+      </c>
+      <c r="I489">
+        <v>0</v>
+      </c>
+      <c r="J489">
+        <v>2.98</v>
+      </c>
+      <c r="K489">
+        <v>0</v>
+      </c>
+      <c r="L489">
+        <v>1.67</v>
+      </c>
+      <c r="M489" t="s">
+        <v>641</v>
+      </c>
+      <c r="N489" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>609</v>
+      </c>
+      <c r="B490" t="s">
+        <v>28</v>
+      </c>
+      <c r="C490" t="s">
+        <v>196</v>
+      </c>
+      <c r="D490" t="s">
+        <v>278</v>
+      </c>
+      <c r="E490" t="s">
+        <v>40</v>
+      </c>
+      <c r="F490">
+        <v>1502</v>
+      </c>
+      <c r="G490">
+        <v>1507</v>
+      </c>
+      <c r="H490">
+        <v>5</v>
+      </c>
+      <c r="I490">
+        <v>128</v>
+      </c>
+      <c r="J490" s="3">
+        <v>2.5409999999999999</v>
+      </c>
+      <c r="K490">
+        <v>50.37</v>
+      </c>
+      <c r="L490">
+        <v>1.97</v>
+      </c>
+      <c r="M490" t="s">
+        <v>646</v>
+      </c>
+      <c r="N490" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>610</v>
+      </c>
+      <c r="B491" t="s">
+        <v>28</v>
+      </c>
+      <c r="C491" t="s">
+        <v>196</v>
+      </c>
+      <c r="D491" t="s">
+        <v>278</v>
+      </c>
+      <c r="E491" t="s">
+        <v>40</v>
+      </c>
+      <c r="F491">
+        <v>1507</v>
+      </c>
+      <c r="G491">
+        <v>1515</v>
+      </c>
+      <c r="H491">
+        <v>8</v>
+      </c>
+      <c r="I491">
+        <v>0</v>
+      </c>
+      <c r="J491">
+        <v>4.05</v>
+      </c>
+      <c r="K491">
+        <v>0</v>
+      </c>
+      <c r="L491">
+        <v>1.97</v>
+      </c>
+      <c r="M491" t="s">
+        <v>646</v>
+      </c>
+      <c r="N491" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>610</v>
+      </c>
+      <c r="B492" t="s">
+        <v>28</v>
+      </c>
+      <c r="C492" t="s">
+        <v>196</v>
+      </c>
+      <c r="D492" t="s">
+        <v>486</v>
+      </c>
+      <c r="E492" t="s">
+        <v>26</v>
+      </c>
+      <c r="F492">
+        <v>1515</v>
+      </c>
+      <c r="G492">
+        <v>1523</v>
+      </c>
+      <c r="H492">
+        <v>8</v>
+      </c>
+      <c r="I492">
+        <v>0</v>
+      </c>
+      <c r="J492">
+        <v>0</v>
+      </c>
+      <c r="K492">
+        <v>0</v>
+      </c>
+      <c r="L492">
+        <v>0</v>
+      </c>
+      <c r="M492" t="s">
+        <v>647</v>
+      </c>
+      <c r="N492" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>637</v>
+      </c>
+      <c r="B493" t="s">
+        <v>28</v>
+      </c>
+      <c r="C493" t="s">
+        <v>196</v>
+      </c>
+      <c r="D493" t="s">
+        <v>586</v>
+      </c>
+      <c r="E493" t="s">
+        <v>485</v>
+      </c>
+      <c r="F493">
+        <v>1523</v>
+      </c>
+      <c r="G493">
+        <v>1524</v>
+      </c>
+      <c r="H493">
+        <v>1</v>
+      </c>
+      <c r="I493">
+        <v>0</v>
+      </c>
+      <c r="J493">
+        <v>0</v>
+      </c>
+      <c r="K493">
+        <v>0</v>
+      </c>
+      <c r="L493">
+        <v>0</v>
+      </c>
+      <c r="M493" t="s">
+        <v>648</v>
+      </c>
+      <c r="N493" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>637</v>
+      </c>
+      <c r="B494" t="s">
+        <v>28</v>
+      </c>
+      <c r="C494" t="s">
+        <v>196</v>
+      </c>
+      <c r="D494" t="s">
+        <v>585</v>
+      </c>
+      <c r="E494" t="s">
+        <v>651</v>
+      </c>
+      <c r="F494">
+        <v>1524</v>
+      </c>
+      <c r="G494">
+        <v>1526</v>
+      </c>
+      <c r="H494">
+        <v>2</v>
+      </c>
+      <c r="I494">
+        <v>0</v>
+      </c>
+      <c r="J494">
+        <v>1</v>
+      </c>
+      <c r="K494">
+        <v>0</v>
+      </c>
+      <c r="L494">
+        <v>2</v>
+      </c>
+      <c r="M494" t="s">
+        <v>649</v>
+      </c>
+      <c r="N494" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>637</v>
+      </c>
+      <c r="B495" t="s">
+        <v>28</v>
+      </c>
+      <c r="C495" t="s">
+        <v>196</v>
+      </c>
+      <c r="D495" t="s">
+        <v>585</v>
+      </c>
+      <c r="E495" t="s">
+        <v>651</v>
+      </c>
+      <c r="F495">
+        <v>1526</v>
+      </c>
+      <c r="G495">
+        <v>1529</v>
+      </c>
+      <c r="H495">
+        <v>3</v>
+      </c>
+      <c r="I495">
+        <v>0</v>
+      </c>
+      <c r="J495">
+        <v>1</v>
+      </c>
+      <c r="K495">
+        <v>0</v>
+      </c>
+      <c r="L495">
+        <v>3</v>
+      </c>
+      <c r="M495" t="s">
+        <v>650</v>
+      </c>
+      <c r="N495" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>637</v>
+      </c>
+      <c r="B496" t="s">
+        <v>28</v>
+      </c>
+      <c r="C496" t="s">
+        <v>196</v>
+      </c>
+      <c r="D496" t="s">
+        <v>486</v>
+      </c>
+      <c r="E496" t="s">
+        <v>26</v>
+      </c>
+      <c r="F496">
+        <v>1529</v>
+      </c>
+      <c r="G496">
+        <v>1534</v>
+      </c>
+      <c r="H496">
+        <v>5</v>
+      </c>
+      <c r="I496">
+        <v>0</v>
+      </c>
+      <c r="J496">
+        <v>0</v>
+      </c>
+      <c r="K496">
+        <v>0</v>
+      </c>
+      <c r="L496">
+        <v>0</v>
+      </c>
+      <c r="M496" t="s">
+        <v>647</v>
+      </c>
+      <c r="N496" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>615</v>
+      </c>
+      <c r="B497" t="s">
+        <v>28</v>
+      </c>
+      <c r="C497" t="s">
+        <v>196</v>
+      </c>
+      <c r="D497" t="s">
+        <v>278</v>
+      </c>
+      <c r="E497" t="s">
+        <v>40</v>
+      </c>
+      <c r="F497">
+        <v>1534</v>
+      </c>
+      <c r="G497">
+        <v>1541</v>
+      </c>
+      <c r="H497">
+        <v>7</v>
+      </c>
+      <c r="I497">
+        <v>70</v>
+      </c>
+      <c r="J497">
+        <v>3.55</v>
+      </c>
+      <c r="K497">
+        <v>19.72</v>
+      </c>
+      <c r="L497">
+        <v>1.97</v>
+      </c>
+      <c r="M497" t="s">
+        <v>646</v>
+      </c>
+      <c r="N497" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>615</v>
+      </c>
+      <c r="B498" t="s">
+        <v>28</v>
+      </c>
+      <c r="C498" t="s">
+        <v>196</v>
+      </c>
+      <c r="E498" t="s">
+        <v>171</v>
+      </c>
+      <c r="F498">
+        <v>1541</v>
+      </c>
+      <c r="G498">
+        <v>1541</v>
+      </c>
+      <c r="H498">
+        <v>0</v>
+      </c>
+      <c r="I498">
+        <v>0</v>
+      </c>
+      <c r="J498">
+        <v>0</v>
+      </c>
+      <c r="K498">
+        <v>0</v>
+      </c>
+      <c r="L498">
+        <v>0</v>
+      </c>
+      <c r="M498" t="s">
+        <v>171</v>
+      </c>
+      <c r="N498" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>588</v>
+      </c>
+      <c r="B499" t="s">
+        <v>15</v>
+      </c>
+      <c r="C499" t="s">
+        <v>16</v>
+      </c>
+      <c r="D499" t="s">
+        <v>278</v>
+      </c>
+      <c r="E499" t="s">
+        <v>26</v>
+      </c>
+      <c r="F499">
+        <v>2367</v>
+      </c>
+      <c r="G499">
+        <v>2378</v>
+      </c>
+      <c r="H499">
+        <v>11</v>
+      </c>
+      <c r="I499">
+        <v>35</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+      <c r="K499">
+        <v>0</v>
+      </c>
+      <c r="L499">
+        <v>0</v>
+      </c>
+      <c r="M499" t="s">
+        <v>573</v>
+      </c>
+      <c r="N499" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>589</v>
+      </c>
+      <c r="B500" t="s">
+        <v>15</v>
+      </c>
+      <c r="C500" t="s">
+        <v>16</v>
+      </c>
+      <c r="D500" t="s">
+        <v>278</v>
+      </c>
+      <c r="E500" t="s">
+        <v>26</v>
+      </c>
+      <c r="F500">
+        <v>2378</v>
+      </c>
+      <c r="G500">
+        <v>2389</v>
+      </c>
+      <c r="H500">
+        <v>11</v>
+      </c>
+      <c r="I500">
+        <v>50</v>
+      </c>
+      <c r="J500">
+        <v>0</v>
+      </c>
+      <c r="K500">
+        <v>0</v>
+      </c>
+      <c r="L500">
+        <v>0</v>
+      </c>
+      <c r="M500" t="s">
+        <v>573</v>
+      </c>
+      <c r="N500" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>590</v>
+      </c>
+      <c r="B501" t="s">
+        <v>15</v>
+      </c>
+      <c r="C501" t="s">
+        <v>16</v>
+      </c>
+      <c r="D501" t="s">
+        <v>278</v>
+      </c>
+      <c r="E501" t="s">
+        <v>26</v>
+      </c>
+      <c r="F501">
+        <v>2389</v>
+      </c>
+      <c r="G501">
+        <v>2401</v>
+      </c>
+      <c r="H501">
+        <v>12</v>
+      </c>
+      <c r="I501">
+        <v>0</v>
+      </c>
+      <c r="J501">
+        <v>0</v>
+      </c>
+      <c r="K501">
+        <v>0</v>
+      </c>
+      <c r="L501">
+        <v>0</v>
+      </c>
+      <c r="M501" t="s">
+        <v>573</v>
+      </c>
+      <c r="N501" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>591</v>
+      </c>
+      <c r="B502" t="s">
+        <v>15</v>
+      </c>
+      <c r="C502" t="s">
+        <v>16</v>
+      </c>
+      <c r="E502" t="s">
+        <v>171</v>
+      </c>
+      <c r="F502">
+        <v>2401</v>
+      </c>
+      <c r="G502">
+        <v>2401</v>
+      </c>
+      <c r="H502">
+        <v>0</v>
+      </c>
+      <c r="I502">
+        <v>50</v>
+      </c>
+      <c r="J502">
+        <v>0</v>
+      </c>
+      <c r="K502">
+        <v>0</v>
+      </c>
+      <c r="L502">
+        <v>0</v>
+      </c>
+      <c r="M502" t="s">
+        <v>171</v>
+      </c>
+      <c r="N502" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>592</v>
+      </c>
+      <c r="B503" t="s">
+        <v>15</v>
+      </c>
+      <c r="C503" t="s">
+        <v>16</v>
+      </c>
+      <c r="D503" t="s">
+        <v>278</v>
+      </c>
+      <c r="E503" t="s">
+        <v>26</v>
+      </c>
+      <c r="F503">
+        <v>2401</v>
+      </c>
+      <c r="G503">
+        <v>2415</v>
+      </c>
+      <c r="H503">
+        <v>14</v>
+      </c>
+      <c r="I503">
+        <v>0</v>
+      </c>
+      <c r="J503">
+        <v>0</v>
+      </c>
+      <c r="K503">
+        <v>0</v>
+      </c>
+      <c r="L503">
+        <v>0</v>
+      </c>
+      <c r="M503" t="s">
+        <v>573</v>
+      </c>
+      <c r="N503" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>593</v>
+      </c>
+      <c r="B504" t="s">
+        <v>15</v>
+      </c>
+      <c r="C504" t="s">
+        <v>16</v>
+      </c>
+      <c r="D504" t="s">
+        <v>278</v>
+      </c>
+      <c r="E504" t="s">
+        <v>26</v>
+      </c>
+      <c r="F504">
+        <v>2415</v>
+      </c>
+      <c r="G504">
+        <v>2426</v>
+      </c>
+      <c r="H504">
+        <v>11</v>
+      </c>
+      <c r="I504">
+        <v>50</v>
+      </c>
+      <c r="J504">
+        <v>0</v>
+      </c>
+      <c r="K504">
+        <v>0</v>
+      </c>
+      <c r="L504">
+        <v>0</v>
+      </c>
+      <c r="M504" t="s">
+        <v>573</v>
+      </c>
+      <c r="N504" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="505" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>594</v>
+      </c>
+      <c r="B505" t="s">
+        <v>15</v>
+      </c>
+      <c r="C505" t="s">
+        <v>16</v>
+      </c>
+      <c r="D505" t="s">
+        <v>278</v>
+      </c>
+      <c r="E505" t="s">
+        <v>26</v>
+      </c>
+      <c r="F505">
+        <v>2426</v>
+      </c>
+      <c r="G505">
+        <v>2435</v>
+      </c>
+      <c r="H505">
+        <v>9</v>
+      </c>
+      <c r="I505">
+        <v>0</v>
+      </c>
+      <c r="J505">
+        <v>0</v>
+      </c>
+      <c r="K505">
+        <v>0</v>
+      </c>
+      <c r="L505">
+        <v>0</v>
+      </c>
+      <c r="M505" t="s">
+        <v>573</v>
+      </c>
+      <c r="N505" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>595</v>
+      </c>
+      <c r="B506" t="s">
+        <v>15</v>
+      </c>
+      <c r="C506" t="s">
+        <v>16</v>
+      </c>
+      <c r="D506" t="s">
+        <v>278</v>
+      </c>
+      <c r="E506" t="s">
+        <v>26</v>
+      </c>
+      <c r="F506">
+        <v>2435</v>
+      </c>
+      <c r="G506">
+        <v>2443</v>
+      </c>
+      <c r="H506">
+        <v>8</v>
+      </c>
+      <c r="I506">
+        <v>0</v>
+      </c>
+      <c r="J506">
+        <v>0</v>
+      </c>
+      <c r="K506">
+        <v>0</v>
+      </c>
+      <c r="L506">
+        <v>0</v>
+      </c>
+      <c r="M506" t="s">
+        <v>573</v>
+      </c>
+      <c r="N506" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>595</v>
+      </c>
+      <c r="B507" t="s">
+        <v>15</v>
+      </c>
+      <c r="C507" t="s">
+        <v>16</v>
+      </c>
+      <c r="D507" t="s">
+        <v>493</v>
+      </c>
+      <c r="E507" t="s">
+        <v>26</v>
+      </c>
+      <c r="F507">
+        <v>2443</v>
+      </c>
+      <c r="G507">
+        <v>2444</v>
+      </c>
+      <c r="H507">
+        <v>1</v>
+      </c>
+      <c r="I507">
+        <v>0</v>
+      </c>
+      <c r="J507">
+        <v>0</v>
+      </c>
+      <c r="K507">
+        <v>0</v>
+      </c>
+      <c r="L507">
+        <v>0</v>
+      </c>
+      <c r="M507" t="s">
+        <v>653</v>
+      </c>
+      <c r="N507" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>652</v>
+      </c>
+      <c r="B508" t="s">
+        <v>15</v>
+      </c>
+      <c r="C508" t="s">
+        <v>16</v>
+      </c>
+      <c r="D508" t="s">
+        <v>278</v>
+      </c>
+      <c r="E508" t="s">
+        <v>26</v>
+      </c>
+      <c r="F508">
+        <v>2444</v>
+      </c>
+      <c r="G508">
+        <v>2448</v>
+      </c>
+      <c r="H508">
+        <v>4</v>
+      </c>
+      <c r="I508">
+        <v>0</v>
+      </c>
+      <c r="J508">
+        <v>0</v>
+      </c>
+      <c r="K508">
+        <v>0</v>
+      </c>
+      <c r="L508">
+        <v>0</v>
+      </c>
+      <c r="M508" t="s">
+        <v>573</v>
+      </c>
+      <c r="N508" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>597</v>
+      </c>
+      <c r="B509" t="s">
+        <v>15</v>
+      </c>
+      <c r="C509" t="s">
+        <v>16</v>
+      </c>
+      <c r="D509" t="s">
+        <v>538</v>
+      </c>
+      <c r="E509" t="s">
+        <v>26</v>
+      </c>
+      <c r="F509">
+        <v>2448</v>
+      </c>
+      <c r="G509">
+        <v>2449</v>
+      </c>
+      <c r="H509">
+        <v>1</v>
+      </c>
+      <c r="I509">
+        <v>30</v>
+      </c>
+      <c r="J509">
+        <v>0</v>
+      </c>
+      <c r="K509">
+        <v>0</v>
+      </c>
+      <c r="L509">
+        <v>0</v>
+      </c>
+      <c r="M509" t="s">
+        <v>654</v>
+      </c>
+      <c r="N509" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>597</v>
+      </c>
+      <c r="B510" t="s">
+        <v>15</v>
+      </c>
+      <c r="C510" t="s">
+        <v>16</v>
+      </c>
+      <c r="D510" t="s">
+        <v>577</v>
+      </c>
+      <c r="E510" t="s">
+        <v>26</v>
+      </c>
+      <c r="F510">
+        <v>2449</v>
+      </c>
+      <c r="G510">
+        <v>2451</v>
+      </c>
+      <c r="H510">
+        <v>2</v>
+      </c>
+      <c r="I510">
+        <v>0</v>
+      </c>
+      <c r="J510">
+        <v>0</v>
+      </c>
+      <c r="K510">
+        <v>0</v>
+      </c>
+      <c r="L510">
+        <v>0</v>
+      </c>
+      <c r="M510" t="s">
+        <v>655</v>
+      </c>
+      <c r="N510" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>598</v>
+      </c>
+      <c r="B511" t="s">
+        <v>15</v>
+      </c>
+      <c r="C511" t="s">
+        <v>16</v>
+      </c>
+      <c r="D511" t="s">
+        <v>489</v>
+      </c>
+      <c r="E511" t="s">
+        <v>43</v>
+      </c>
+      <c r="F511">
+        <v>2451</v>
+      </c>
+      <c r="G511">
+        <v>2454</v>
+      </c>
+      <c r="H511">
+        <v>3</v>
+      </c>
+      <c r="I511">
+        <v>0</v>
+      </c>
+      <c r="J511">
+        <v>0</v>
+      </c>
+      <c r="K511">
+        <v>0</v>
+      </c>
+      <c r="L511">
+        <v>0</v>
+      </c>
+      <c r="M511" t="s">
+        <v>656</v>
+      </c>
+      <c r="N511" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="512" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>600</v>
+      </c>
+      <c r="B512" t="s">
+        <v>15</v>
+      </c>
+      <c r="C512" t="s">
+        <v>16</v>
+      </c>
+      <c r="D512" t="s">
+        <v>661</v>
+      </c>
+      <c r="E512" t="s">
+        <v>485</v>
+      </c>
+      <c r="F512">
+        <v>2454</v>
+      </c>
+      <c r="G512">
+        <v>2457</v>
+      </c>
+      <c r="H512">
+        <v>3</v>
+      </c>
+      <c r="I512">
+        <v>0</v>
+      </c>
+      <c r="J512">
+        <v>0</v>
+      </c>
+      <c r="K512">
+        <v>0</v>
+      </c>
+      <c r="L512">
+        <v>0</v>
+      </c>
+      <c r="M512" t="s">
+        <v>657</v>
+      </c>
+      <c r="N512" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>601</v>
+      </c>
+      <c r="B513" t="s">
+        <v>15</v>
+      </c>
+      <c r="C513" t="s">
+        <v>16</v>
+      </c>
+      <c r="D513" t="s">
+        <v>581</v>
+      </c>
+      <c r="E513" t="s">
+        <v>43</v>
+      </c>
+      <c r="F513">
+        <v>2457</v>
+      </c>
+      <c r="G513">
+        <v>2458</v>
+      </c>
+      <c r="H513">
+        <v>1</v>
+      </c>
+      <c r="I513">
+        <v>0</v>
+      </c>
+      <c r="J513">
+        <v>0</v>
+      </c>
+      <c r="K513">
+        <v>0</v>
+      </c>
+      <c r="L513">
+        <v>0</v>
+      </c>
+      <c r="M513" t="s">
+        <v>658</v>
+      </c>
+      <c r="N513" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="514" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>602</v>
+      </c>
+      <c r="B514" t="s">
+        <v>15</v>
+      </c>
+      <c r="C514" t="s">
+        <v>16</v>
+      </c>
+      <c r="D514" t="s">
+        <v>586</v>
+      </c>
+      <c r="E514" t="s">
+        <v>26</v>
+      </c>
+      <c r="F514">
+        <v>2458</v>
+      </c>
+      <c r="G514">
+        <v>2463</v>
+      </c>
+      <c r="H514">
+        <v>5</v>
+      </c>
+      <c r="I514">
+        <v>0</v>
+      </c>
+      <c r="J514">
+        <v>0</v>
+      </c>
+      <c r="K514">
+        <v>0</v>
+      </c>
+      <c r="L514">
+        <v>0</v>
+      </c>
+      <c r="M514" t="s">
+        <v>659</v>
+      </c>
+      <c r="N514" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="515" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>588</v>
+      </c>
+      <c r="B515" t="s">
+        <v>21</v>
+      </c>
+      <c r="C515" t="s">
+        <v>635</v>
+      </c>
+      <c r="D515" t="s">
+        <v>310</v>
+      </c>
+      <c r="E515" t="s">
+        <v>662</v>
+      </c>
+      <c r="F515">
+        <v>4671</v>
+      </c>
+      <c r="G515">
+        <v>4671</v>
+      </c>
+      <c r="H515">
+        <v>0</v>
+      </c>
+      <c r="I515">
+        <v>0</v>
+      </c>
+      <c r="J515">
+        <v>0</v>
+      </c>
+      <c r="K515">
+        <v>0</v>
+      </c>
+      <c r="L515">
+        <v>0</v>
+      </c>
+      <c r="M515" t="s">
+        <v>662</v>
+      </c>
+      <c r="N515" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>615</v>
+      </c>
+      <c r="B516" t="s">
+        <v>21</v>
+      </c>
+      <c r="C516" t="s">
+        <v>635</v>
+      </c>
+      <c r="D516" t="s">
+        <v>310</v>
+      </c>
+      <c r="E516" t="s">
+        <v>662</v>
+      </c>
+      <c r="F516">
+        <v>4671</v>
+      </c>
+      <c r="G516">
+        <v>4671</v>
+      </c>
+      <c r="H516">
+        <v>0</v>
+      </c>
+      <c r="I516">
+        <v>0</v>
+      </c>
+      <c r="J516">
+        <v>0</v>
+      </c>
+      <c r="K516">
+        <v>0</v>
+      </c>
+      <c r="L516">
+        <v>0</v>
+      </c>
+      <c r="M516" t="s">
+        <v>662</v>
+      </c>
+      <c r="N516" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>744</v>
+      </c>
+      <c r="B517" t="s">
+        <v>137</v>
+      </c>
+      <c r="C517" t="s">
+        <v>635</v>
+      </c>
+      <c r="D517" t="s">
+        <v>278</v>
+      </c>
+      <c r="E517" t="s">
+        <v>17</v>
+      </c>
+      <c r="F517">
+        <v>8822</v>
+      </c>
+      <c r="G517">
+        <v>8823</v>
+      </c>
+      <c r="H517">
+        <v>1</v>
+      </c>
+      <c r="I517">
+        <v>0</v>
+      </c>
+      <c r="J517">
+        <v>0</v>
+      </c>
+      <c r="K517">
+        <v>0</v>
+      </c>
+      <c r="L517">
+        <v>0</v>
+      </c>
+      <c r="M517" t="s">
+        <v>663</v>
+      </c>
+      <c r="N517" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="518" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>745</v>
+      </c>
+      <c r="B518" t="s">
+        <v>137</v>
+      </c>
+      <c r="C518" t="s">
+        <v>635</v>
+      </c>
+      <c r="D518" t="s">
+        <v>586</v>
+      </c>
+      <c r="E518" t="s">
+        <v>43</v>
+      </c>
+      <c r="F518">
+        <v>8823</v>
+      </c>
+      <c r="G518">
+        <v>8824</v>
+      </c>
+      <c r="H518">
+        <v>1</v>
+      </c>
+      <c r="I518">
+        <v>0</v>
+      </c>
+      <c r="J518">
+        <v>0</v>
+      </c>
+      <c r="K518">
+        <v>0</v>
+      </c>
+      <c r="L518">
+        <v>0</v>
+      </c>
+      <c r="M518" t="s">
+        <v>664</v>
+      </c>
+      <c r="N518" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A519" t="s">
+        <v>745</v>
+      </c>
+      <c r="B519" t="s">
+        <v>137</v>
+      </c>
+      <c r="C519" t="s">
+        <v>635</v>
+      </c>
+      <c r="D519" t="s">
+        <v>278</v>
+      </c>
+      <c r="E519" t="s">
+        <v>43</v>
+      </c>
+      <c r="F519">
+        <v>8824</v>
+      </c>
+      <c r="G519">
+        <v>8824.5</v>
+      </c>
+      <c r="H519">
+        <v>0.5</v>
+      </c>
+      <c r="I519">
+        <v>0</v>
+      </c>
+      <c r="J519">
+        <v>0</v>
+      </c>
+      <c r="K519">
+        <v>0</v>
+      </c>
+      <c r="L519">
+        <v>0</v>
+      </c>
+      <c r="M519" t="s">
+        <v>665</v>
+      </c>
+      <c r="N519" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="520" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A520" t="s">
+        <v>745</v>
+      </c>
+      <c r="B520" t="s">
+        <v>137</v>
+      </c>
+      <c r="C520" t="s">
+        <v>635</v>
+      </c>
+      <c r="D520" t="s">
+        <v>535</v>
+      </c>
+      <c r="E520" t="s">
+        <v>26</v>
+      </c>
+      <c r="F520">
+        <v>8824.5</v>
+      </c>
+      <c r="G520">
+        <v>8826</v>
+      </c>
+      <c r="H520">
+        <v>1.5</v>
+      </c>
+      <c r="I520">
+        <v>0</v>
+      </c>
+      <c r="J520">
+        <v>0</v>
+      </c>
+      <c r="K520">
+        <v>0</v>
+      </c>
+      <c r="L520">
+        <v>0</v>
+      </c>
+      <c r="M520" t="s">
+        <v>666</v>
+      </c>
+      <c r="N520" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="521" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A521" t="s">
+        <v>745</v>
+      </c>
+      <c r="B521" t="s">
+        <v>137</v>
+      </c>
+      <c r="C521" t="s">
+        <v>635</v>
+      </c>
+      <c r="D521" t="s">
+        <v>703</v>
+      </c>
+      <c r="E521" t="s">
+        <v>26</v>
+      </c>
+      <c r="F521">
+        <v>8826</v>
+      </c>
+      <c r="G521">
+        <v>8827</v>
+      </c>
+      <c r="H521">
+        <v>1</v>
+      </c>
+      <c r="I521">
+        <v>0</v>
+      </c>
+      <c r="J521">
+        <v>0</v>
+      </c>
+      <c r="K521">
+        <v>0</v>
+      </c>
+      <c r="L521">
+        <v>0</v>
+      </c>
+      <c r="M521" t="s">
+        <v>667</v>
+      </c>
+      <c r="N521" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="522" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A522" t="s">
+        <v>746</v>
+      </c>
+      <c r="B522" t="s">
+        <v>137</v>
+      </c>
+      <c r="C522" t="s">
+        <v>635</v>
+      </c>
+      <c r="D522" t="s">
+        <v>489</v>
+      </c>
+      <c r="E522" t="s">
+        <v>43</v>
+      </c>
+      <c r="F522">
+        <v>8827</v>
+      </c>
+      <c r="G522">
+        <v>8828</v>
+      </c>
+      <c r="H522">
+        <v>1</v>
+      </c>
+      <c r="I522">
+        <v>0</v>
+      </c>
+      <c r="J522">
+        <v>0</v>
+      </c>
+      <c r="K522">
+        <v>0</v>
+      </c>
+      <c r="L522">
+        <v>0</v>
+      </c>
+      <c r="M522" t="s">
+        <v>668</v>
+      </c>
+      <c r="N522" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="523" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A523" t="s">
+        <v>746</v>
+      </c>
+      <c r="B523" t="s">
+        <v>137</v>
+      </c>
+      <c r="C523" t="s">
+        <v>635</v>
+      </c>
+      <c r="D523" t="s">
+        <v>309</v>
+      </c>
+      <c r="E523" t="s">
+        <v>485</v>
+      </c>
+      <c r="F523">
+        <v>8828</v>
+      </c>
+      <c r="G523">
+        <v>8830</v>
+      </c>
+      <c r="H523">
+        <v>2</v>
+      </c>
+      <c r="I523">
+        <v>0</v>
+      </c>
+      <c r="J523">
+        <v>0</v>
+      </c>
+      <c r="K523">
+        <v>0</v>
+      </c>
+      <c r="L523">
+        <v>0</v>
+      </c>
+      <c r="M523" t="s">
+        <v>669</v>
+      </c>
+      <c r="N523" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="524" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A524" t="s">
+        <v>746</v>
+      </c>
+      <c r="B524" t="s">
+        <v>137</v>
+      </c>
+      <c r="C524" t="s">
+        <v>635</v>
+      </c>
+      <c r="D524" t="s">
+        <v>278</v>
+      </c>
+      <c r="E524" t="s">
+        <v>26</v>
+      </c>
+      <c r="F524">
+        <v>8830</v>
+      </c>
+      <c r="G524">
+        <v>8833</v>
+      </c>
+      <c r="H524">
+        <v>3</v>
+      </c>
+      <c r="I524">
+        <v>0</v>
+      </c>
+      <c r="J524">
+        <v>0</v>
+      </c>
+      <c r="K524">
+        <v>0</v>
+      </c>
+      <c r="L524">
+        <v>0</v>
+      </c>
+      <c r="M524" t="s">
+        <v>631</v>
+      </c>
+      <c r="N524" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="525" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A525" t="s">
+        <v>747</v>
+      </c>
+      <c r="B525" t="s">
+        <v>137</v>
+      </c>
+      <c r="C525" t="s">
+        <v>635</v>
+      </c>
+      <c r="D525" t="s">
+        <v>278</v>
+      </c>
+      <c r="E525" t="s">
+        <v>26</v>
+      </c>
+      <c r="F525">
+        <v>8833</v>
+      </c>
+      <c r="G525">
+        <v>8837</v>
+      </c>
+      <c r="H525">
+        <v>4</v>
+      </c>
+      <c r="I525">
+        <v>0</v>
+      </c>
+      <c r="J525">
+        <v>0</v>
+      </c>
+      <c r="K525">
+        <v>0</v>
+      </c>
+      <c r="L525">
+        <v>0</v>
+      </c>
+      <c r="M525" t="s">
+        <v>631</v>
+      </c>
+      <c r="N525" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="526" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A526" t="s">
+        <v>748</v>
+      </c>
+      <c r="B526" t="s">
+        <v>137</v>
+      </c>
+      <c r="C526" t="s">
+        <v>635</v>
+      </c>
+      <c r="D526" t="s">
+        <v>278</v>
+      </c>
+      <c r="E526" t="s">
+        <v>26</v>
+      </c>
+      <c r="F526">
+        <v>8837</v>
+      </c>
+      <c r="G526">
+        <v>8842</v>
+      </c>
+      <c r="H526">
+        <v>5</v>
+      </c>
+      <c r="I526">
+        <v>45</v>
+      </c>
+      <c r="J526">
+        <v>0</v>
+      </c>
+      <c r="K526">
+        <v>0</v>
+      </c>
+      <c r="L526">
+        <v>0</v>
+      </c>
+      <c r="M526" t="s">
+        <v>631</v>
+      </c>
+      <c r="N526" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="527" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A527" t="s">
+        <v>749</v>
+      </c>
+      <c r="B527" t="s">
+        <v>137</v>
+      </c>
+      <c r="C527" t="s">
+        <v>635</v>
+      </c>
+      <c r="D527" t="s">
+        <v>278</v>
+      </c>
+      <c r="E527" t="s">
+        <v>26</v>
+      </c>
+      <c r="F527">
+        <v>8842</v>
+      </c>
+      <c r="G527">
+        <v>8846</v>
+      </c>
+      <c r="H527">
+        <v>4</v>
+      </c>
+      <c r="I527">
+        <v>0</v>
+      </c>
+      <c r="J527">
+        <v>0</v>
+      </c>
+      <c r="K527">
+        <v>0</v>
+      </c>
+      <c r="L527">
+        <v>0</v>
+      </c>
+      <c r="M527" t="s">
+        <v>631</v>
+      </c>
+      <c r="N527" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="528" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A528" t="s">
+        <v>750</v>
+      </c>
+      <c r="B528" t="s">
+        <v>137</v>
+      </c>
+      <c r="C528" t="s">
+        <v>635</v>
+      </c>
+      <c r="D528" t="s">
+        <v>278</v>
+      </c>
+      <c r="E528" t="s">
+        <v>26</v>
+      </c>
+      <c r="F528">
+        <v>8846</v>
+      </c>
+      <c r="G528">
+        <v>8850</v>
+      </c>
+      <c r="H528">
+        <v>4</v>
+      </c>
+      <c r="I528">
+        <v>40</v>
+      </c>
+      <c r="J528">
+        <v>0</v>
+      </c>
+      <c r="K528">
+        <v>0</v>
+      </c>
+      <c r="L528">
+        <v>0</v>
+      </c>
+      <c r="M528" t="s">
+        <v>631</v>
+      </c>
+      <c r="N528" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="529" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A529" t="s">
+        <v>750</v>
+      </c>
+      <c r="B529" t="s">
+        <v>137</v>
+      </c>
+      <c r="C529" t="s">
+        <v>635</v>
+      </c>
+      <c r="E529" t="s">
+        <v>17</v>
+      </c>
+      <c r="F529">
+        <v>8850</v>
+      </c>
+      <c r="G529">
+        <v>8851</v>
+      </c>
+      <c r="H529">
+        <v>1</v>
+      </c>
+      <c r="I529">
+        <v>0</v>
+      </c>
+      <c r="J529">
+        <v>0</v>
+      </c>
+      <c r="K529">
+        <v>0</v>
+      </c>
+      <c r="L529">
+        <v>0</v>
+      </c>
+      <c r="M529" t="s">
+        <v>670</v>
+      </c>
+      <c r="N529" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="530" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A530" t="s">
+        <v>751</v>
+      </c>
+      <c r="B530" t="s">
+        <v>137</v>
+      </c>
+      <c r="C530" t="s">
+        <v>635</v>
+      </c>
+      <c r="D530" t="s">
+        <v>532</v>
+      </c>
+      <c r="E530" t="s">
+        <v>43</v>
+      </c>
+      <c r="F530">
+        <v>8851</v>
+      </c>
+      <c r="G530">
+        <v>8852</v>
+      </c>
+      <c r="H530">
+        <v>1</v>
+      </c>
+      <c r="I530">
+        <v>0</v>
+      </c>
+      <c r="J530">
+        <v>0</v>
+      </c>
+      <c r="K530">
+        <v>0</v>
+      </c>
+      <c r="L530">
+        <v>0</v>
+      </c>
+      <c r="M530" t="s">
+        <v>671</v>
+      </c>
+      <c r="N530" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="531" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A531" t="s">
+        <v>751</v>
+      </c>
+      <c r="B531" t="s">
+        <v>137</v>
+      </c>
+      <c r="C531" t="s">
+        <v>635</v>
+      </c>
+      <c r="D531" t="s">
+        <v>709</v>
+      </c>
+      <c r="E531" t="s">
+        <v>26</v>
+      </c>
+      <c r="F531">
+        <v>8852</v>
+      </c>
+      <c r="G531">
+        <v>8853</v>
+      </c>
+      <c r="H531">
+        <v>1</v>
+      </c>
+      <c r="I531">
+        <v>0</v>
+      </c>
+      <c r="J531">
+        <v>0</v>
+      </c>
+      <c r="K531">
+        <v>0</v>
+      </c>
+      <c r="L531">
+        <v>0</v>
+      </c>
+      <c r="M531" t="s">
+        <v>672</v>
+      </c>
+      <c r="N531" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="532" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A532" t="s">
+        <v>751</v>
+      </c>
+      <c r="B532" t="s">
+        <v>137</v>
+      </c>
+      <c r="C532" t="s">
+        <v>635</v>
+      </c>
+      <c r="D532" t="s">
+        <v>710</v>
+      </c>
+      <c r="E532" t="s">
+        <v>43</v>
+      </c>
+      <c r="F532">
+        <v>8853</v>
+      </c>
+      <c r="G532">
+        <v>8854</v>
+      </c>
+      <c r="H532">
+        <v>1</v>
+      </c>
+      <c r="I532">
+        <v>0</v>
+      </c>
+      <c r="J532">
+        <v>0</v>
+      </c>
+      <c r="K532">
+        <v>0</v>
+      </c>
+      <c r="L532">
+        <v>0</v>
+      </c>
+      <c r="M532" t="s">
+        <v>673</v>
+      </c>
+      <c r="N532" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="533" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A533" t="s">
+        <v>752</v>
+      </c>
+      <c r="B533" t="s">
+        <v>137</v>
+      </c>
+      <c r="C533" t="s">
+        <v>635</v>
+      </c>
+      <c r="D533" t="s">
+        <v>139</v>
+      </c>
+      <c r="E533" t="s">
+        <v>17</v>
+      </c>
+      <c r="F533">
+        <v>8854</v>
+      </c>
+      <c r="G533">
+        <v>8855</v>
+      </c>
+      <c r="H533">
+        <v>1</v>
+      </c>
+      <c r="I533">
+        <v>0</v>
+      </c>
+      <c r="J533">
+        <v>0</v>
+      </c>
+      <c r="K533">
+        <v>0</v>
+      </c>
+      <c r="L533">
+        <v>0</v>
+      </c>
+      <c r="M533" t="s">
+        <v>674</v>
+      </c>
+      <c r="N533" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="534" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A534" t="s">
+        <v>752</v>
+      </c>
+      <c r="B534" t="s">
+        <v>137</v>
+      </c>
+      <c r="C534" t="s">
+        <v>635</v>
+      </c>
+      <c r="D534" t="s">
+        <v>704</v>
+      </c>
+      <c r="E534" t="s">
+        <v>485</v>
+      </c>
+      <c r="F534">
+        <v>8855</v>
+      </c>
+      <c r="G534">
+        <v>8857</v>
+      </c>
+      <c r="H534">
+        <v>2</v>
+      </c>
+      <c r="I534">
+        <v>0</v>
+      </c>
+      <c r="J534">
+        <v>0</v>
+      </c>
+      <c r="K534">
+        <v>0</v>
+      </c>
+      <c r="L534">
+        <v>0</v>
+      </c>
+      <c r="M534" t="s">
+        <v>675</v>
+      </c>
+      <c r="N534" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="535" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A535" t="s">
+        <v>753</v>
+      </c>
+      <c r="B535" t="s">
+        <v>137</v>
+      </c>
+      <c r="C535" t="s">
+        <v>635</v>
+      </c>
+      <c r="D535" t="s">
+        <v>495</v>
+      </c>
+      <c r="E535" t="s">
+        <v>26</v>
+      </c>
+      <c r="F535">
+        <v>8857</v>
+      </c>
+      <c r="G535">
+        <v>8859</v>
+      </c>
+      <c r="H535">
+        <v>2</v>
+      </c>
+      <c r="I535">
+        <v>0</v>
+      </c>
+      <c r="J535">
+        <v>0</v>
+      </c>
+      <c r="K535">
+        <v>0</v>
+      </c>
+      <c r="L535">
+        <v>0</v>
+      </c>
+      <c r="M535" t="s">
+        <v>676</v>
+      </c>
+      <c r="N535" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A536" t="s">
+        <v>753</v>
+      </c>
+      <c r="B536" t="s">
+        <v>137</v>
+      </c>
+      <c r="C536" t="s">
+        <v>635</v>
+      </c>
+      <c r="D536" t="s">
+        <v>68</v>
+      </c>
+      <c r="E536" t="s">
+        <v>17</v>
+      </c>
+      <c r="F536">
+        <v>8859</v>
+      </c>
+      <c r="G536">
+        <v>8861</v>
+      </c>
+      <c r="H536">
+        <v>2</v>
+      </c>
+      <c r="I536">
+        <v>0</v>
+      </c>
+      <c r="J536">
+        <v>0</v>
+      </c>
+      <c r="K536">
+        <v>0</v>
+      </c>
+      <c r="L536">
+        <v>0</v>
+      </c>
+      <c r="M536" t="s">
+        <v>677</v>
+      </c>
+      <c r="N536" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="537" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A537" t="s">
+        <v>754</v>
+      </c>
+      <c r="B537" t="s">
+        <v>137</v>
+      </c>
+      <c r="C537" t="s">
+        <v>635</v>
+      </c>
+      <c r="D537" t="s">
+        <v>68</v>
+      </c>
+      <c r="E537" t="s">
+        <v>485</v>
+      </c>
+      <c r="F537">
+        <v>8861</v>
+      </c>
+      <c r="G537">
+        <v>8864</v>
+      </c>
+      <c r="H537">
+        <v>3</v>
+      </c>
+      <c r="I537">
+        <v>0</v>
+      </c>
+      <c r="J537">
+        <v>0</v>
+      </c>
+      <c r="K537">
+        <v>0</v>
+      </c>
+      <c r="L537">
+        <v>0</v>
+      </c>
+      <c r="M537" t="s">
+        <v>678</v>
+      </c>
+      <c r="N537" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="538" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A538" t="s">
+        <v>755</v>
+      </c>
+      <c r="B538" t="s">
+        <v>137</v>
+      </c>
+      <c r="C538" t="s">
+        <v>635</v>
+      </c>
+      <c r="D538" t="s">
+        <v>661</v>
+      </c>
+      <c r="E538" t="s">
+        <v>660</v>
+      </c>
+      <c r="F538">
+        <v>8864</v>
+      </c>
+      <c r="G538">
+        <v>8865</v>
+      </c>
+      <c r="H538">
+        <v>1</v>
+      </c>
+      <c r="I538">
+        <v>0</v>
+      </c>
+      <c r="J538">
+        <v>0</v>
+      </c>
+      <c r="K538">
+        <v>0</v>
+      </c>
+      <c r="L538">
+        <v>0</v>
+      </c>
+      <c r="M538" t="s">
+        <v>657</v>
+      </c>
+      <c r="N538" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A539" t="s">
+        <v>756</v>
+      </c>
+      <c r="B539" t="s">
+        <v>137</v>
+      </c>
+      <c r="C539" t="s">
+        <v>635</v>
+      </c>
+      <c r="D539" t="s">
+        <v>489</v>
+      </c>
+      <c r="E539" t="s">
+        <v>43</v>
+      </c>
+      <c r="F539">
+        <v>8865</v>
+      </c>
+      <c r="G539">
+        <v>8867</v>
+      </c>
+      <c r="H539">
+        <v>2</v>
+      </c>
+      <c r="I539">
+        <v>0</v>
+      </c>
+      <c r="J539">
+        <v>0</v>
+      </c>
+      <c r="K539">
+        <v>0</v>
+      </c>
+      <c r="L539">
+        <v>0</v>
+      </c>
+      <c r="M539" t="s">
+        <v>679</v>
+      </c>
+      <c r="N539" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="540" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A540" t="s">
+        <v>756</v>
+      </c>
+      <c r="B540" t="s">
+        <v>137</v>
+      </c>
+      <c r="C540" t="s">
+        <v>635</v>
+      </c>
+      <c r="D540" t="s">
+        <v>496</v>
+      </c>
+      <c r="E540" t="s">
+        <v>17</v>
+      </c>
+      <c r="F540">
+        <v>8867</v>
+      </c>
+      <c r="G540">
+        <v>8869</v>
+      </c>
+      <c r="H540">
+        <v>2</v>
+      </c>
+      <c r="I540">
+        <v>0</v>
+      </c>
+      <c r="J540">
+        <v>0</v>
+      </c>
+      <c r="K540">
+        <v>0</v>
+      </c>
+      <c r="L540">
+        <v>0</v>
+      </c>
+      <c r="M540" t="s">
+        <v>680</v>
+      </c>
+      <c r="N540" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="541" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A541" t="s">
+        <v>757</v>
+      </c>
+      <c r="B541" t="s">
+        <v>137</v>
+      </c>
+      <c r="C541" t="s">
+        <v>635</v>
+      </c>
+      <c r="D541" t="s">
+        <v>661</v>
+      </c>
+      <c r="E541" t="s">
+        <v>17</v>
+      </c>
+      <c r="F541">
+        <v>8869</v>
+      </c>
+      <c r="G541">
+        <v>8871</v>
+      </c>
+      <c r="H541">
+        <v>2</v>
+      </c>
+      <c r="I541">
+        <v>40</v>
+      </c>
+      <c r="J541">
+        <v>0</v>
+      </c>
+      <c r="K541">
+        <v>0</v>
+      </c>
+      <c r="L541">
+        <v>0</v>
+      </c>
+      <c r="M541" t="s">
+        <v>681</v>
+      </c>
+      <c r="N541" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="542" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A542" t="s">
+        <v>727</v>
+      </c>
+      <c r="B542" t="s">
+        <v>137</v>
+      </c>
+      <c r="C542" t="s">
+        <v>635</v>
+      </c>
+      <c r="D542" t="s">
+        <v>496</v>
+      </c>
+      <c r="E542" t="s">
+        <v>17</v>
+      </c>
+      <c r="F542">
+        <v>8871</v>
+      </c>
+      <c r="G542">
+        <v>8872</v>
+      </c>
+      <c r="H542">
+        <v>1</v>
+      </c>
+      <c r="I542">
+        <v>0</v>
+      </c>
+      <c r="J542">
+        <v>0</v>
+      </c>
+      <c r="K542">
+        <v>0</v>
+      </c>
+      <c r="L542">
+        <v>0</v>
+      </c>
+      <c r="M542" t="s">
+        <v>680</v>
+      </c>
+      <c r="N542" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="543" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A543" t="s">
+        <v>728</v>
+      </c>
+      <c r="B543" t="s">
+        <v>137</v>
+      </c>
+      <c r="C543" t="s">
+        <v>635</v>
+      </c>
+      <c r="D543" t="s">
+        <v>717</v>
+      </c>
+      <c r="E543" t="s">
+        <v>43</v>
+      </c>
+      <c r="F543">
+        <v>8872</v>
+      </c>
+      <c r="G543">
+        <v>8873</v>
+      </c>
+      <c r="H543">
+        <v>1</v>
+      </c>
+      <c r="I543">
+        <v>0</v>
+      </c>
+      <c r="J543">
+        <v>0</v>
+      </c>
+      <c r="K543">
+        <v>0</v>
+      </c>
+      <c r="L543">
+        <v>0</v>
+      </c>
+      <c r="M543" t="s">
+        <v>682</v>
+      </c>
+      <c r="N543" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="544" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A544" t="s">
+        <v>728</v>
+      </c>
+      <c r="B544" t="s">
+        <v>137</v>
+      </c>
+      <c r="C544" t="s">
+        <v>635</v>
+      </c>
+      <c r="D544" t="s">
+        <v>309</v>
+      </c>
+      <c r="E544" t="s">
+        <v>43</v>
+      </c>
+      <c r="F544">
+        <v>8873</v>
+      </c>
+      <c r="G544">
+        <v>8874</v>
+      </c>
+      <c r="H544">
+        <v>1</v>
+      </c>
+      <c r="I544">
+        <v>0</v>
+      </c>
+      <c r="J544">
+        <v>0</v>
+      </c>
+      <c r="K544">
+        <v>0</v>
+      </c>
+      <c r="L544">
+        <v>0</v>
+      </c>
+      <c r="M544" t="s">
+        <v>683</v>
+      </c>
+      <c r="N544" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A545" t="s">
+        <v>728</v>
+      </c>
+      <c r="B545" t="s">
+        <v>137</v>
+      </c>
+      <c r="C545" t="s">
+        <v>635</v>
+      </c>
+      <c r="D545" t="s">
+        <v>718</v>
+      </c>
+      <c r="E545" t="s">
+        <v>26</v>
+      </c>
+      <c r="F545">
+        <v>8874</v>
+      </c>
+      <c r="G545">
+        <v>8875</v>
+      </c>
+      <c r="H545">
+        <v>1</v>
+      </c>
+      <c r="I545">
+        <v>0</v>
+      </c>
+      <c r="J545">
+        <v>0</v>
+      </c>
+      <c r="K545">
+        <v>0</v>
+      </c>
+      <c r="L545">
+        <v>0</v>
+      </c>
+      <c r="M545" t="s">
+        <v>684</v>
+      </c>
+      <c r="N545" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="546" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A546" t="s">
+        <v>729</v>
+      </c>
+      <c r="B546" t="s">
+        <v>137</v>
+      </c>
+      <c r="C546" t="s">
+        <v>635</v>
+      </c>
+      <c r="D546" t="s">
+        <v>496</v>
+      </c>
+      <c r="E546" t="s">
+        <v>17</v>
+      </c>
+      <c r="F546">
+        <v>8875</v>
+      </c>
+      <c r="G546">
+        <v>8876</v>
+      </c>
+      <c r="H546">
+        <v>1</v>
+      </c>
+      <c r="I546">
+        <v>40</v>
+      </c>
+      <c r="J546">
+        <v>0</v>
+      </c>
+      <c r="K546">
+        <v>0</v>
+      </c>
+      <c r="L546">
+        <v>0</v>
+      </c>
+      <c r="M546" t="s">
+        <v>680</v>
+      </c>
+      <c r="N546" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A547" t="s">
+        <v>729</v>
+      </c>
+      <c r="B547" t="s">
+        <v>137</v>
+      </c>
+      <c r="C547" t="s">
+        <v>635</v>
+      </c>
+      <c r="D547" t="s">
+        <v>719</v>
+      </c>
+      <c r="E547" t="s">
+        <v>26</v>
+      </c>
+      <c r="F547">
+        <v>8876</v>
+      </c>
+      <c r="G547">
+        <v>8877</v>
+      </c>
+      <c r="H547">
+        <v>1</v>
+      </c>
+      <c r="I547">
+        <v>0</v>
+      </c>
+      <c r="J547">
+        <v>0</v>
+      </c>
+      <c r="K547">
+        <v>0</v>
+      </c>
+      <c r="L547">
+        <v>0</v>
+      </c>
+      <c r="M547" t="s">
+        <v>685</v>
+      </c>
+      <c r="N547" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="548" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A548" t="s">
+        <v>730</v>
+      </c>
+      <c r="B548" t="s">
+        <v>137</v>
+      </c>
+      <c r="C548" t="s">
+        <v>635</v>
+      </c>
+      <c r="D548" t="s">
+        <v>534</v>
+      </c>
+      <c r="E548" t="s">
+        <v>43</v>
+      </c>
+      <c r="F548">
+        <v>8877</v>
+      </c>
+      <c r="G548">
+        <v>8878</v>
+      </c>
+      <c r="H548">
+        <v>1</v>
+      </c>
+      <c r="I548">
+        <v>0</v>
+      </c>
+      <c r="J548">
+        <v>0</v>
+      </c>
+      <c r="K548">
+        <v>0</v>
+      </c>
+      <c r="L548">
+        <v>0</v>
+      </c>
+      <c r="M548" t="s">
+        <v>686</v>
+      </c>
+      <c r="N548" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="549" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A549" t="s">
+        <v>731</v>
+      </c>
+      <c r="B549" t="s">
+        <v>137</v>
+      </c>
+      <c r="C549" t="s">
+        <v>635</v>
+      </c>
+      <c r="D549" t="s">
+        <v>708</v>
+      </c>
+      <c r="E549" t="s">
+        <v>26</v>
+      </c>
+      <c r="F549">
+        <v>8878</v>
+      </c>
+      <c r="G549">
+        <v>8879</v>
+      </c>
+      <c r="H549">
+        <v>1</v>
+      </c>
+      <c r="I549">
+        <v>0</v>
+      </c>
+      <c r="J549">
+        <v>0</v>
+      </c>
+      <c r="K549">
+        <v>0</v>
+      </c>
+      <c r="L549">
+        <v>0</v>
+      </c>
+      <c r="M549" t="s">
+        <v>687</v>
+      </c>
+      <c r="N549" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="550" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A550" t="s">
+        <v>732</v>
+      </c>
+      <c r="B550" t="s">
+        <v>137</v>
+      </c>
+      <c r="C550" t="s">
+        <v>635</v>
+      </c>
+      <c r="D550" t="s">
+        <v>710</v>
+      </c>
+      <c r="E550" t="s">
+        <v>26</v>
+      </c>
+      <c r="F550">
+        <v>8879</v>
+      </c>
+      <c r="G550">
+        <v>8881</v>
+      </c>
+      <c r="H550">
+        <v>2</v>
+      </c>
+      <c r="I550">
+        <v>0</v>
+      </c>
+      <c r="J550">
+        <v>0</v>
+      </c>
+      <c r="K550">
+        <v>0</v>
+      </c>
+      <c r="L550">
+        <v>0</v>
+      </c>
+      <c r="M550" t="s">
+        <v>688</v>
+      </c>
+      <c r="N550" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="551" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A551" t="s">
+        <v>733</v>
+      </c>
+      <c r="B551" t="s">
+        <v>137</v>
+      </c>
+      <c r="C551" t="s">
+        <v>635</v>
+      </c>
+      <c r="D551" t="s">
+        <v>278</v>
+      </c>
+      <c r="E551" t="s">
+        <v>17</v>
+      </c>
+      <c r="F551">
+        <v>8881</v>
+      </c>
+      <c r="G551">
+        <v>8882</v>
+      </c>
+      <c r="H551">
+        <v>1</v>
+      </c>
+      <c r="I551">
+        <v>0</v>
+      </c>
+      <c r="J551">
+        <v>0</v>
+      </c>
+      <c r="K551">
+        <v>0</v>
+      </c>
+      <c r="L551">
+        <v>0</v>
+      </c>
+      <c r="M551" t="s">
+        <v>663</v>
+      </c>
+      <c r="N551" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="552" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A552" t="s">
+        <v>733</v>
+      </c>
+      <c r="B552" t="s">
+        <v>137</v>
+      </c>
+      <c r="C552" t="s">
+        <v>635</v>
+      </c>
+      <c r="D552" t="s">
+        <v>724</v>
+      </c>
+      <c r="E552" t="s">
+        <v>26</v>
+      </c>
+      <c r="F552">
+        <v>8882</v>
+      </c>
+      <c r="G552">
+        <v>8884</v>
+      </c>
+      <c r="H552">
+        <v>2</v>
+      </c>
+      <c r="I552">
+        <v>40</v>
+      </c>
+      <c r="J552">
+        <v>0</v>
+      </c>
+      <c r="K552">
+        <v>0</v>
+      </c>
+      <c r="L552">
+        <v>0</v>
+      </c>
+      <c r="M552" t="s">
+        <v>689</v>
+      </c>
+      <c r="N552" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="553" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A553" t="s">
+        <v>734</v>
+      </c>
+      <c r="B553" t="s">
+        <v>137</v>
+      </c>
+      <c r="C553" t="s">
+        <v>635</v>
+      </c>
+      <c r="D553" t="s">
+        <v>496</v>
+      </c>
+      <c r="E553" t="s">
+        <v>17</v>
+      </c>
+      <c r="F553">
+        <v>8884</v>
+      </c>
+      <c r="G553">
+        <v>8885</v>
+      </c>
+      <c r="H553">
+        <v>1</v>
+      </c>
+      <c r="I553">
+        <v>0</v>
+      </c>
+      <c r="J553">
+        <v>0</v>
+      </c>
+      <c r="K553">
+        <v>0</v>
+      </c>
+      <c r="L553">
+        <v>0</v>
+      </c>
+      <c r="M553" t="s">
+        <v>680</v>
+      </c>
+      <c r="N553" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="554" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A554" t="s">
+        <v>734</v>
+      </c>
+      <c r="B554" t="s">
+        <v>137</v>
+      </c>
+      <c r="C554" t="s">
+        <v>635</v>
+      </c>
+      <c r="D554" t="s">
+        <v>712</v>
+      </c>
+      <c r="E554" t="s">
+        <v>26</v>
+      </c>
+      <c r="F554">
+        <v>8885</v>
+      </c>
+      <c r="G554">
+        <v>8886</v>
+      </c>
+      <c r="H554">
+        <v>1</v>
+      </c>
+      <c r="I554">
+        <v>0</v>
+      </c>
+      <c r="J554">
+        <v>0</v>
+      </c>
+      <c r="K554">
+        <v>0</v>
+      </c>
+      <c r="L554">
+        <v>0</v>
+      </c>
+      <c r="M554" t="s">
+        <v>690</v>
+      </c>
+      <c r="N554" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="555" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A555" t="s">
+        <v>735</v>
+      </c>
+      <c r="B555" t="s">
+        <v>137</v>
+      </c>
+      <c r="C555" t="s">
+        <v>635</v>
+      </c>
+      <c r="D555" t="s">
+        <v>661</v>
+      </c>
+      <c r="E555" t="s">
+        <v>43</v>
+      </c>
+      <c r="F555">
+        <v>8886</v>
+      </c>
+      <c r="G555">
+        <v>8887</v>
+      </c>
+      <c r="H555">
+        <v>1</v>
+      </c>
+      <c r="I555">
+        <v>0</v>
+      </c>
+      <c r="J555">
+        <v>0</v>
+      </c>
+      <c r="K555">
+        <v>0</v>
+      </c>
+      <c r="L555">
+        <v>0</v>
+      </c>
+      <c r="M555" t="s">
+        <v>691</v>
+      </c>
+      <c r="N555" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="556" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A556" t="s">
+        <v>735</v>
+      </c>
+      <c r="B556" t="s">
+        <v>137</v>
+      </c>
+      <c r="C556" t="s">
+        <v>635</v>
+      </c>
+      <c r="D556" t="s">
+        <v>580</v>
+      </c>
+      <c r="E556" t="s">
+        <v>26</v>
+      </c>
+      <c r="F556">
+        <v>8887</v>
+      </c>
+      <c r="G556">
+        <v>8888</v>
+      </c>
+      <c r="H556">
+        <v>1</v>
+      </c>
+      <c r="I556">
+        <v>0</v>
+      </c>
+      <c r="J556">
+        <v>0</v>
+      </c>
+      <c r="K556">
+        <v>0</v>
+      </c>
+      <c r="L556">
+        <v>0</v>
+      </c>
+      <c r="M556" t="s">
+        <v>692</v>
+      </c>
+      <c r="N556" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="557" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A557" t="s">
+        <v>736</v>
+      </c>
+      <c r="B557" t="s">
+        <v>137</v>
+      </c>
+      <c r="C557" t="s">
+        <v>635</v>
+      </c>
+      <c r="D557" t="s">
+        <v>68</v>
+      </c>
+      <c r="E557" t="s">
+        <v>17</v>
+      </c>
+      <c r="F557">
+        <v>8888</v>
+      </c>
+      <c r="G557">
+        <v>8889</v>
+      </c>
+      <c r="H557">
+        <v>1</v>
+      </c>
+      <c r="I557">
+        <v>40</v>
+      </c>
+      <c r="J557">
+        <v>0</v>
+      </c>
+      <c r="K557">
+        <v>0</v>
+      </c>
+      <c r="L557">
+        <v>0</v>
+      </c>
+      <c r="M557" t="s">
+        <v>693</v>
+      </c>
+      <c r="N557" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="558" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A558" t="s">
+        <v>737</v>
+      </c>
+      <c r="B558" t="s">
+        <v>137</v>
+      </c>
+      <c r="C558" t="s">
+        <v>635</v>
+      </c>
+      <c r="D558" t="s">
+        <v>704</v>
+      </c>
+      <c r="E558" t="s">
+        <v>43</v>
+      </c>
+      <c r="F558">
+        <v>8889</v>
+      </c>
+      <c r="G558">
+        <v>8890</v>
+      </c>
+      <c r="H558">
+        <v>1</v>
+      </c>
+      <c r="I558">
+        <v>0</v>
+      </c>
+      <c r="J558">
+        <v>0</v>
+      </c>
+      <c r="K558">
+        <v>0</v>
+      </c>
+      <c r="L558">
+        <v>0</v>
+      </c>
+      <c r="M558" t="s">
+        <v>694</v>
+      </c>
+      <c r="N558" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="559" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A559" t="s">
+        <v>738</v>
+      </c>
+      <c r="B559" t="s">
+        <v>137</v>
+      </c>
+      <c r="C559" t="s">
+        <v>635</v>
+      </c>
+      <c r="D559" t="s">
+        <v>726</v>
+      </c>
+      <c r="E559" t="s">
+        <v>485</v>
+      </c>
+      <c r="F559">
+        <v>8890</v>
+      </c>
+      <c r="G559">
+        <v>8892</v>
+      </c>
+      <c r="H559">
+        <v>2</v>
+      </c>
+      <c r="I559">
+        <v>0</v>
+      </c>
+      <c r="J559">
+        <v>0</v>
+      </c>
+      <c r="K559">
+        <v>0</v>
+      </c>
+      <c r="L559">
+        <v>0</v>
+      </c>
+      <c r="M559" t="s">
+        <v>695</v>
+      </c>
+      <c r="N559" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="560" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A560" t="s">
+        <v>739</v>
+      </c>
+      <c r="B560" t="s">
+        <v>137</v>
+      </c>
+      <c r="C560" t="s">
+        <v>635</v>
+      </c>
+      <c r="D560" t="s">
+        <v>726</v>
+      </c>
+      <c r="E560" t="s">
+        <v>485</v>
+      </c>
+      <c r="F560">
+        <v>8892</v>
+      </c>
+      <c r="G560">
+        <v>8894</v>
+      </c>
+      <c r="H560">
+        <v>2</v>
+      </c>
+      <c r="I560">
+        <v>0</v>
+      </c>
+      <c r="J560">
+        <v>0</v>
+      </c>
+      <c r="K560">
+        <v>0</v>
+      </c>
+      <c r="L560">
+        <v>0</v>
+      </c>
+      <c r="M560" t="s">
+        <v>695</v>
+      </c>
+      <c r="N560" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="561" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A561" t="s">
+        <v>739</v>
+      </c>
+      <c r="B561" t="s">
+        <v>137</v>
+      </c>
+      <c r="C561" t="s">
+        <v>635</v>
+      </c>
+      <c r="D561" t="s">
+        <v>714</v>
+      </c>
+      <c r="E561" t="s">
+        <v>17</v>
+      </c>
+      <c r="F561">
+        <v>8894</v>
+      </c>
+      <c r="G561">
+        <v>8895</v>
+      </c>
+      <c r="H561">
+        <v>1</v>
+      </c>
+      <c r="I561">
+        <v>0</v>
+      </c>
+      <c r="J561">
+        <v>0</v>
+      </c>
+      <c r="K561">
+        <v>0</v>
+      </c>
+      <c r="L561">
+        <v>0</v>
+      </c>
+      <c r="M561" t="s">
+        <v>696</v>
+      </c>
+      <c r="N561" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="562" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A562" t="s">
+        <v>739</v>
+      </c>
+      <c r="B562" t="s">
+        <v>137</v>
+      </c>
+      <c r="C562" t="s">
+        <v>635</v>
+      </c>
+      <c r="D562" t="s">
+        <v>726</v>
+      </c>
+      <c r="E562" t="s">
+        <v>17</v>
+      </c>
+      <c r="F562">
+        <v>8895</v>
+      </c>
+      <c r="G562">
+        <v>8896</v>
+      </c>
+      <c r="H562">
+        <v>1</v>
+      </c>
+      <c r="I562">
+        <v>40</v>
+      </c>
+      <c r="J562">
+        <v>0</v>
+      </c>
+      <c r="K562">
+        <v>0</v>
+      </c>
+      <c r="L562">
+        <v>0</v>
+      </c>
+      <c r="M562" t="s">
+        <v>697</v>
+      </c>
+      <c r="N562" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="563" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A563" t="s">
+        <v>740</v>
+      </c>
+      <c r="B563" t="s">
+        <v>137</v>
+      </c>
+      <c r="C563" t="s">
+        <v>635</v>
+      </c>
+      <c r="D563" t="s">
+        <v>711</v>
+      </c>
+      <c r="E563" t="s">
+        <v>26</v>
+      </c>
+      <c r="F563">
+        <v>8896</v>
+      </c>
+      <c r="G563">
+        <v>8897</v>
+      </c>
+      <c r="H563">
+        <v>1</v>
+      </c>
+      <c r="I563">
+        <v>0</v>
+      </c>
+      <c r="J563">
+        <v>0</v>
+      </c>
+      <c r="K563">
+        <v>0</v>
+      </c>
+      <c r="L563">
+        <v>0</v>
+      </c>
+      <c r="M563" t="s">
+        <v>698</v>
+      </c>
+      <c r="N563" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="564" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A564" t="s">
+        <v>741</v>
+      </c>
+      <c r="B564" t="s">
+        <v>137</v>
+      </c>
+      <c r="C564" t="s">
+        <v>635</v>
+      </c>
+      <c r="D564" t="s">
+        <v>532</v>
+      </c>
+      <c r="E564" t="s">
+        <v>26</v>
+      </c>
+      <c r="F564">
+        <v>8897</v>
+      </c>
+      <c r="G564">
+        <v>8898</v>
+      </c>
+      <c r="H564">
+        <v>1</v>
+      </c>
+      <c r="I564">
+        <v>0</v>
+      </c>
+      <c r="J564">
+        <v>0</v>
+      </c>
+      <c r="K564">
+        <v>0</v>
+      </c>
+      <c r="L564">
+        <v>0</v>
+      </c>
+      <c r="M564" t="s">
+        <v>699</v>
+      </c>
+      <c r="N564" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="565" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A565" t="s">
+        <v>741</v>
+      </c>
+      <c r="B565" t="s">
+        <v>137</v>
+      </c>
+      <c r="C565" t="s">
+        <v>635</v>
+      </c>
+      <c r="D565" t="s">
+        <v>661</v>
+      </c>
+      <c r="E565" t="s">
+        <v>43</v>
+      </c>
+      <c r="F565">
+        <v>8898</v>
+      </c>
+      <c r="G565">
+        <v>8898.5</v>
+      </c>
+      <c r="H565">
+        <v>0.5</v>
+      </c>
+      <c r="I565">
+        <v>0</v>
+      </c>
+      <c r="J565">
+        <v>0</v>
+      </c>
+      <c r="K565">
+        <v>0</v>
+      </c>
+      <c r="L565">
+        <v>0</v>
+      </c>
+      <c r="M565" t="s">
+        <v>700</v>
+      </c>
+      <c r="N565" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="566" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A566" t="s">
+        <v>741</v>
+      </c>
+      <c r="B566" t="s">
+        <v>137</v>
+      </c>
+      <c r="C566" t="s">
+        <v>635</v>
+      </c>
+      <c r="D566" t="s">
+        <v>715</v>
+      </c>
+      <c r="E566" t="s">
+        <v>17</v>
+      </c>
+      <c r="F566">
+        <v>8898.5</v>
+      </c>
+      <c r="G566">
+        <v>8899</v>
+      </c>
+      <c r="H566">
+        <v>0.5</v>
+      </c>
+      <c r="I566">
+        <v>0</v>
+      </c>
+      <c r="J566">
+        <v>0</v>
+      </c>
+      <c r="K566">
+        <v>0</v>
+      </c>
+      <c r="L566">
+        <v>0</v>
+      </c>
+      <c r="M566" t="s">
+        <v>701</v>
+      </c>
+      <c r="N566" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="567" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A567" t="s">
+        <v>742</v>
+      </c>
+      <c r="B567" t="s">
+        <v>137</v>
+      </c>
+      <c r="C567" t="s">
+        <v>635</v>
+      </c>
+      <c r="D567" t="s">
+        <v>715</v>
+      </c>
+      <c r="E567" t="s">
+        <v>17</v>
+      </c>
+      <c r="F567">
+        <v>8899</v>
+      </c>
+      <c r="G567">
+        <v>8900</v>
+      </c>
+      <c r="H567">
+        <v>1</v>
+      </c>
+      <c r="I567">
+        <v>0</v>
+      </c>
+      <c r="J567">
+        <v>0</v>
+      </c>
+      <c r="K567">
+        <v>0</v>
+      </c>
+      <c r="L567">
+        <v>0</v>
+      </c>
+      <c r="M567" t="s">
+        <v>701</v>
+      </c>
+      <c r="N567" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="568" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A568" t="s">
+        <v>742</v>
+      </c>
+      <c r="B568" t="s">
+        <v>137</v>
+      </c>
+      <c r="C568" t="s">
+        <v>635</v>
+      </c>
+      <c r="D568" t="s">
+        <v>716</v>
+      </c>
+      <c r="E568" t="s">
+        <v>26</v>
+      </c>
+      <c r="F568">
+        <v>8900</v>
+      </c>
+      <c r="G568">
+        <v>8901</v>
+      </c>
+      <c r="H568">
+        <v>1</v>
+      </c>
+      <c r="I568">
+        <v>0</v>
+      </c>
+      <c r="J568">
+        <v>0</v>
+      </c>
+      <c r="K568">
+        <v>0</v>
+      </c>
+      <c r="L568">
+        <v>0</v>
+      </c>
+      <c r="M568" t="s">
+        <v>702</v>
+      </c>
+      <c r="N568" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="569" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A569" t="s">
+        <v>743</v>
+      </c>
+      <c r="B569" t="s">
+        <v>28</v>
+      </c>
+      <c r="C569" t="s">
+        <v>196</v>
+      </c>
+      <c r="D569" t="s">
+        <v>798</v>
+      </c>
+      <c r="E569" t="s">
+        <v>140</v>
+      </c>
+      <c r="F569">
+        <v>1541</v>
+      </c>
+      <c r="G569">
+        <v>1547</v>
+      </c>
+      <c r="H569">
+        <v>6</v>
+      </c>
+      <c r="I569">
+        <v>0</v>
+      </c>
+      <c r="J569">
+        <v>3.04</v>
+      </c>
+      <c r="K569">
+        <v>0</v>
+      </c>
+      <c r="L569">
+        <v>1.97</v>
+      </c>
+      <c r="M569" t="s">
+        <v>758</v>
+      </c>
+      <c r="N569" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="570" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A570" t="s">
+        <v>743</v>
+      </c>
+      <c r="B570" t="s">
+        <v>28</v>
+      </c>
+      <c r="C570" t="s">
+        <v>196</v>
+      </c>
+      <c r="D570" t="s">
+        <v>278</v>
+      </c>
+      <c r="E570" t="s">
+        <v>26</v>
+      </c>
+      <c r="F570">
+        <v>1547</v>
+      </c>
+      <c r="G570">
+        <v>1548</v>
+      </c>
+      <c r="H570">
+        <v>1</v>
+      </c>
+      <c r="I570">
+        <v>0</v>
+      </c>
+      <c r="J570">
+        <v>0</v>
+      </c>
+      <c r="K570">
+        <v>0</v>
+      </c>
+      <c r="L570">
+        <v>0</v>
+      </c>
+      <c r="M570" t="s">
+        <v>759</v>
+      </c>
+      <c r="N570" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="571" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A571" t="s">
+        <v>744</v>
+      </c>
+      <c r="B571" t="s">
+        <v>28</v>
+      </c>
+      <c r="C571" t="s">
+        <v>196</v>
+      </c>
+      <c r="D571" t="s">
+        <v>139</v>
+      </c>
+      <c r="E571" t="s">
+        <v>140</v>
+      </c>
+      <c r="F571">
+        <v>1548</v>
+      </c>
+      <c r="G571">
+        <v>1551</v>
+      </c>
+      <c r="H571">
+        <v>3</v>
+      </c>
+      <c r="I571">
+        <v>48</v>
+      </c>
+      <c r="J571">
+        <v>3.03</v>
+      </c>
+      <c r="K571">
+        <v>15.84</v>
+      </c>
+      <c r="L571">
+        <v>0.99</v>
+      </c>
+      <c r="M571" t="s">
+        <v>760</v>
+      </c>
+      <c r="N571" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="572" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A572" t="s">
+        <v>744</v>
+      </c>
+      <c r="B572" t="s">
+        <v>28</v>
+      </c>
+      <c r="C572" t="s">
+        <v>196</v>
+      </c>
+      <c r="D572" t="s">
+        <v>724</v>
+      </c>
+      <c r="E572" t="s">
+        <v>140</v>
+      </c>
+      <c r="F572">
+        <v>1551</v>
+      </c>
+      <c r="G572">
+        <v>1552</v>
+      </c>
+      <c r="H572">
+        <v>1</v>
+      </c>
+      <c r="I572">
+        <v>0</v>
+      </c>
+      <c r="J572">
+        <v>1.35</v>
+      </c>
+      <c r="K572">
+        <v>0</v>
+      </c>
+      <c r="L572">
+        <v>0.74</v>
+      </c>
+      <c r="M572" t="s">
+        <v>761</v>
+      </c>
+      <c r="N572" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="573" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A573" t="s">
+        <v>744</v>
+      </c>
+      <c r="B573" t="s">
+        <v>28</v>
+      </c>
+      <c r="C573" t="s">
+        <v>196</v>
+      </c>
+      <c r="D573" t="s">
+        <v>278</v>
+      </c>
+      <c r="E573" t="s">
+        <v>26</v>
+      </c>
+      <c r="F573">
+        <v>1552</v>
+      </c>
+      <c r="G573">
+        <v>1557</v>
+      </c>
+      <c r="H573">
+        <v>5</v>
+      </c>
+      <c r="I573">
+        <v>40</v>
+      </c>
+      <c r="J573">
+        <v>0</v>
+      </c>
+      <c r="K573">
+        <v>0</v>
+      </c>
+      <c r="L573">
+        <v>0</v>
+      </c>
+      <c r="M573" t="s">
+        <v>759</v>
+      </c>
+      <c r="N573" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="574" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A574" t="s">
+        <v>746</v>
+      </c>
+      <c r="B574" t="s">
+        <v>28</v>
+      </c>
+      <c r="C574" t="s">
+        <v>196</v>
+      </c>
+      <c r="D574" t="s">
+        <v>278</v>
+      </c>
+      <c r="E574" t="s">
+        <v>26</v>
+      </c>
+      <c r="F574">
+        <v>1557</v>
+      </c>
+      <c r="G574">
+        <v>1563</v>
+      </c>
+      <c r="H574">
+        <v>6</v>
+      </c>
+      <c r="I574">
+        <v>0</v>
+      </c>
+      <c r="J574">
+        <v>0</v>
+      </c>
+      <c r="K574">
+        <v>0</v>
+      </c>
+      <c r="L574">
+        <v>0</v>
+      </c>
+      <c r="M574" t="s">
+        <v>759</v>
+      </c>
+      <c r="N574" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="575" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A575" t="s">
+        <v>747</v>
+      </c>
+      <c r="B575" t="s">
+        <v>28</v>
+      </c>
+      <c r="C575" t="s">
+        <v>196</v>
+      </c>
+      <c r="D575" t="s">
+        <v>278</v>
+      </c>
+      <c r="E575" t="s">
+        <v>26</v>
+      </c>
+      <c r="F575">
+        <v>1563</v>
+      </c>
+      <c r="G575">
+        <v>1569</v>
+      </c>
+      <c r="H575">
+        <v>6</v>
+      </c>
+      <c r="I575">
+        <v>0</v>
+      </c>
+      <c r="J575">
+        <v>0</v>
+      </c>
+      <c r="K575">
+        <v>0</v>
+      </c>
+      <c r="L575">
+        <v>0</v>
+      </c>
+      <c r="M575" t="s">
+        <v>759</v>
+      </c>
+      <c r="N575" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="576" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A576" t="s">
+        <v>750</v>
+      </c>
+      <c r="B576" t="s">
+        <v>28</v>
+      </c>
+      <c r="C576" t="s">
+        <v>196</v>
+      </c>
+      <c r="D576" t="s">
+        <v>278</v>
+      </c>
+      <c r="E576" t="s">
+        <v>310</v>
+      </c>
+      <c r="F576">
+        <v>1569</v>
+      </c>
+      <c r="G576">
+        <v>1570</v>
+      </c>
+      <c r="H576">
+        <v>1</v>
+      </c>
+      <c r="I576">
+        <v>40</v>
+      </c>
+      <c r="J576">
+        <v>0</v>
+      </c>
+      <c r="K576">
+        <v>0</v>
+      </c>
+      <c r="L576">
+        <v>0</v>
+      </c>
+      <c r="M576" t="s">
+        <v>762</v>
+      </c>
+      <c r="N576" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="577" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A577" t="s">
+        <v>752</v>
+      </c>
+      <c r="B577" t="s">
+        <v>28</v>
+      </c>
+      <c r="C577" t="s">
+        <v>196</v>
+      </c>
+      <c r="D577" t="s">
+        <v>704</v>
+      </c>
+      <c r="E577" t="s">
+        <v>485</v>
+      </c>
+      <c r="F577">
+        <v>1570</v>
+      </c>
+      <c r="G577">
+        <v>1571</v>
+      </c>
+      <c r="H577">
+        <v>1</v>
+      </c>
+      <c r="I577">
+        <v>0</v>
+      </c>
+      <c r="J577">
+        <v>0</v>
+      </c>
+      <c r="K577">
+        <v>0</v>
+      </c>
+      <c r="L577">
+        <v>0</v>
+      </c>
+      <c r="M577" t="s">
+        <v>763</v>
+      </c>
+      <c r="N577" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="578" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A578" t="s">
+        <v>752</v>
+      </c>
+      <c r="B578" t="s">
+        <v>28</v>
+      </c>
+      <c r="C578" t="s">
+        <v>196</v>
+      </c>
+      <c r="E578" t="s">
+        <v>799</v>
+      </c>
+      <c r="F578">
+        <v>1571</v>
+      </c>
+      <c r="G578">
+        <v>1575</v>
+      </c>
+      <c r="H578">
+        <v>4</v>
+      </c>
+      <c r="I578">
+        <v>0</v>
+      </c>
+      <c r="J578">
+        <v>0</v>
+      </c>
+      <c r="K578">
+        <v>0</v>
+      </c>
+      <c r="L578">
+        <v>0</v>
+      </c>
+      <c r="M578" t="s">
+        <v>764</v>
+      </c>
+      <c r="N578" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="579" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A579" t="s">
+        <v>756</v>
+      </c>
+      <c r="B579" t="s">
+        <v>28</v>
+      </c>
+      <c r="C579" t="s">
+        <v>196</v>
+      </c>
+      <c r="E579" t="s">
+        <v>171</v>
+      </c>
+      <c r="F579">
+        <v>1575</v>
+      </c>
+      <c r="G579">
+        <v>1576</v>
+      </c>
+      <c r="H579">
+        <v>1</v>
+      </c>
+      <c r="I579">
+        <v>40</v>
+      </c>
+      <c r="J579">
+        <v>0</v>
+      </c>
+      <c r="K579">
+        <v>0</v>
+      </c>
+      <c r="L579">
+        <v>0</v>
+      </c>
+      <c r="M579" t="s">
+        <v>171</v>
+      </c>
+      <c r="N579" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="580" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A580" t="s">
+        <v>728</v>
+      </c>
+      <c r="B580" t="s">
+        <v>28</v>
+      </c>
+      <c r="C580" t="s">
+        <v>196</v>
+      </c>
+      <c r="D580" t="s">
+        <v>798</v>
+      </c>
+      <c r="E580" t="s">
+        <v>492</v>
+      </c>
+      <c r="F580">
+        <v>1576</v>
+      </c>
+      <c r="G580">
+        <v>1578</v>
+      </c>
+      <c r="H580">
+        <v>2</v>
+      </c>
+      <c r="I580">
+        <v>105</v>
+      </c>
+      <c r="J580">
+        <v>3.04</v>
+      </c>
+      <c r="K580">
+        <v>34.54</v>
+      </c>
+      <c r="L580">
+        <v>0.66</v>
+      </c>
+      <c r="M580" t="s">
+        <v>765</v>
+      </c>
+      <c r="N580" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="581" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A581" t="s">
+        <v>728</v>
+      </c>
+      <c r="B581" t="s">
+        <v>28</v>
+      </c>
+      <c r="C581" t="s">
+        <v>196</v>
+      </c>
+      <c r="D581" t="s">
+        <v>139</v>
+      </c>
+      <c r="E581" t="s">
+        <v>492</v>
+      </c>
+      <c r="F581">
+        <v>1578</v>
+      </c>
+      <c r="G581">
+        <v>1579</v>
+      </c>
+      <c r="H581">
+        <v>1</v>
+      </c>
+      <c r="I581">
+        <v>0</v>
+      </c>
+      <c r="J581">
+        <v>3.03</v>
+      </c>
+      <c r="K581">
+        <v>0</v>
+      </c>
+      <c r="L581">
+        <v>0.33</v>
+      </c>
+      <c r="M581" t="s">
+        <v>766</v>
+      </c>
+      <c r="N581" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="582" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A582" t="s">
+        <v>728</v>
+      </c>
+      <c r="B582" t="s">
+        <v>28</v>
+      </c>
+      <c r="C582" t="s">
+        <v>196</v>
+      </c>
+      <c r="D582" t="s">
+        <v>724</v>
+      </c>
+      <c r="E582" t="s">
+        <v>492</v>
+      </c>
+      <c r="F582">
+        <v>1579</v>
+      </c>
+      <c r="G582">
+        <v>1580</v>
+      </c>
+      <c r="H582">
+        <v>1</v>
+      </c>
+      <c r="I582">
+        <v>0</v>
+      </c>
+      <c r="J582">
+        <v>1.35</v>
+      </c>
+      <c r="K582">
+        <v>0</v>
+      </c>
+      <c r="L582">
+        <v>0.74</v>
+      </c>
+      <c r="M582" t="s">
+        <v>767</v>
+      </c>
+      <c r="N582" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="583" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A583" t="s">
+        <v>729</v>
+      </c>
+      <c r="B583" t="s">
+        <v>28</v>
+      </c>
+      <c r="C583" t="s">
+        <v>196</v>
+      </c>
+      <c r="D583" t="s">
+        <v>711</v>
+      </c>
+      <c r="E583" t="s">
+        <v>492</v>
+      </c>
+      <c r="F583">
+        <v>1580</v>
+      </c>
+      <c r="G583">
+        <v>1583</v>
+      </c>
+      <c r="H583">
+        <v>3</v>
+      </c>
+      <c r="I583">
+        <v>30</v>
+      </c>
+      <c r="J583">
+        <v>3</v>
+      </c>
+      <c r="K583">
+        <v>10</v>
+      </c>
+      <c r="L583">
+        <f t="shared" ref="L583" si="0">H583/J583</f>
+        <v>1</v>
+      </c>
+      <c r="M583" t="s">
+        <v>768</v>
+      </c>
+      <c r="N583" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="584" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A584" t="s">
+        <v>729</v>
+      </c>
+      <c r="B584" t="s">
+        <v>28</v>
+      </c>
+      <c r="C584" t="s">
+        <v>196</v>
+      </c>
+      <c r="D584" t="s">
+        <v>800</v>
+      </c>
+      <c r="E584" t="s">
+        <v>492</v>
+      </c>
+      <c r="F584">
+        <v>1583</v>
+      </c>
+      <c r="G584">
+        <v>1586</v>
+      </c>
+      <c r="H584">
+        <v>3</v>
+      </c>
+      <c r="I584">
+        <v>0</v>
+      </c>
+      <c r="J584">
+        <v>3.06</v>
+      </c>
+      <c r="K584">
+        <v>0</v>
+      </c>
+      <c r="L584">
+        <v>0.98</v>
+      </c>
+      <c r="M584" t="s">
+        <v>769</v>
+      </c>
+      <c r="N584" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="585" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A585" t="s">
+        <v>729</v>
+      </c>
+      <c r="B585" t="s">
+        <v>28</v>
+      </c>
+      <c r="C585" t="s">
+        <v>196</v>
+      </c>
+      <c r="E585" t="s">
+        <v>797</v>
+      </c>
+      <c r="F585">
+        <v>1586</v>
+      </c>
+      <c r="G585">
+        <v>1587</v>
+      </c>
+      <c r="H585">
+        <v>1</v>
+      </c>
+      <c r="I585">
+        <v>0</v>
+      </c>
+      <c r="J585">
+        <v>0</v>
+      </c>
+      <c r="K585">
+        <v>0</v>
+      </c>
+      <c r="L585">
+        <v>0</v>
+      </c>
+      <c r="M585" t="s">
+        <v>770</v>
+      </c>
+      <c r="N585" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="586" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A586" t="s">
+        <v>730</v>
+      </c>
+      <c r="B586" t="s">
+        <v>28</v>
+      </c>
+      <c r="C586" t="s">
+        <v>196</v>
+      </c>
+      <c r="D586" t="s">
+        <v>716</v>
+      </c>
+      <c r="E586" t="s">
+        <v>492</v>
+      </c>
+      <c r="F586">
+        <v>1587</v>
+      </c>
+      <c r="G586">
+        <v>1590</v>
+      </c>
+      <c r="H586">
+        <v>3</v>
+      </c>
+      <c r="I586">
+        <v>0</v>
+      </c>
+      <c r="J586">
+        <v>3.03</v>
+      </c>
+      <c r="K586">
+        <v>0</v>
+      </c>
+      <c r="L586">
+        <v>0.99</v>
+      </c>
+      <c r="M586" t="s">
+        <v>771</v>
+      </c>
+      <c r="N586" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="587" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A587" t="s">
+        <v>730</v>
+      </c>
+      <c r="B587" t="s">
+        <v>28</v>
+      </c>
+      <c r="C587" t="s">
+        <v>196</v>
+      </c>
+      <c r="D587" t="s">
+        <v>722</v>
+      </c>
+      <c r="E587" t="s">
+        <v>492</v>
+      </c>
+      <c r="F587">
+        <v>1590</v>
+      </c>
+      <c r="G587">
+        <v>1593</v>
+      </c>
+      <c r="H587">
+        <v>3</v>
+      </c>
+      <c r="I587">
+        <v>0</v>
+      </c>
+      <c r="J587">
+        <v>3.06</v>
+      </c>
+      <c r="K587">
+        <v>0</v>
+      </c>
+      <c r="L587">
+        <v>0.98</v>
+      </c>
+      <c r="M587" t="s">
+        <v>772</v>
+      </c>
+      <c r="N587" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="588" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A588" t="s">
+        <v>730</v>
+      </c>
+      <c r="B588" t="s">
+        <v>28</v>
+      </c>
+      <c r="C588" t="s">
+        <v>196</v>
+      </c>
+      <c r="D588" t="s">
+        <v>707</v>
+      </c>
+      <c r="E588" t="s">
+        <v>492</v>
+      </c>
+      <c r="F588">
+        <v>1593</v>
+      </c>
+      <c r="G588">
+        <v>1594</v>
+      </c>
+      <c r="H588">
+        <v>1</v>
+      </c>
+      <c r="I588">
+        <v>0</v>
+      </c>
+      <c r="J588">
+        <v>0.45</v>
+      </c>
+      <c r="K588">
+        <v>0</v>
+      </c>
+      <c r="L588">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="M588" t="s">
+        <v>773</v>
+      </c>
+      <c r="N588" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="589" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A589" t="s">
+        <v>732</v>
+      </c>
+      <c r="B589" t="s">
+        <v>28</v>
+      </c>
+      <c r="C589" t="s">
+        <v>196</v>
+      </c>
+      <c r="E589" t="s">
+        <v>171</v>
+      </c>
+      <c r="F589">
+        <v>1594</v>
+      </c>
+      <c r="G589">
+        <v>1594</v>
+      </c>
+      <c r="H589">
+        <v>0</v>
+      </c>
+      <c r="I589">
+        <v>185</v>
+      </c>
+      <c r="J589">
+        <v>0</v>
+      </c>
+      <c r="K589">
+        <v>0</v>
+      </c>
+      <c r="L589">
+        <v>0</v>
+      </c>
+      <c r="M589" t="s">
+        <v>171</v>
+      </c>
+      <c r="N589" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="590" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A590" t="s">
+        <v>733</v>
+      </c>
+      <c r="B590" t="s">
+        <v>28</v>
+      </c>
+      <c r="C590" t="s">
+        <v>196</v>
+      </c>
+      <c r="D590" t="s">
+        <v>537</v>
+      </c>
+      <c r="E590" t="s">
+        <v>43</v>
+      </c>
+      <c r="F590">
+        <v>1594</v>
+      </c>
+      <c r="G590">
+        <v>1595</v>
+      </c>
+      <c r="H590">
+        <v>1</v>
+      </c>
+      <c r="I590">
+        <v>0</v>
+      </c>
+      <c r="J590">
+        <v>0</v>
+      </c>
+      <c r="K590">
+        <v>0</v>
+      </c>
+      <c r="L590">
+        <v>0</v>
+      </c>
+      <c r="M590" t="s">
+        <v>774</v>
+      </c>
+      <c r="N590" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="591" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A591" t="s">
+        <v>733</v>
+      </c>
+      <c r="B591" t="s">
+        <v>28</v>
+      </c>
+      <c r="C591" t="s">
+        <v>196</v>
+      </c>
+      <c r="D591" t="s">
+        <v>68</v>
+      </c>
+      <c r="E591" t="s">
+        <v>43</v>
+      </c>
+      <c r="F591">
+        <v>1595</v>
+      </c>
+      <c r="G591">
+        <v>1596</v>
+      </c>
+      <c r="H591">
+        <v>1</v>
+      </c>
+      <c r="I591">
+        <v>0</v>
+      </c>
+      <c r="J591">
+        <v>0</v>
+      </c>
+      <c r="K591">
+        <v>0</v>
+      </c>
+      <c r="L591">
+        <v>0</v>
+      </c>
+      <c r="M591" t="s">
+        <v>775</v>
+      </c>
+      <c r="N591" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="592" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A592" t="s">
+        <v>733</v>
+      </c>
+      <c r="B592" t="s">
+        <v>28</v>
+      </c>
+      <c r="C592" t="s">
+        <v>196</v>
+      </c>
+      <c r="D592" t="s">
+        <v>801</v>
+      </c>
+      <c r="E592" t="s">
+        <v>492</v>
+      </c>
+      <c r="F592">
+        <v>1596</v>
+      </c>
+      <c r="G592">
+        <v>1598</v>
+      </c>
+      <c r="H592">
+        <v>2</v>
+      </c>
+      <c r="I592">
+        <v>0</v>
+      </c>
+      <c r="J592">
+        <v>3.03</v>
+      </c>
+      <c r="K592">
+        <v>0</v>
+      </c>
+      <c r="L592">
+        <v>0.66</v>
+      </c>
+      <c r="M592" t="s">
+        <v>776</v>
+      </c>
+      <c r="N592" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="593" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A593" t="s">
+        <v>733</v>
+      </c>
+      <c r="B593" t="s">
+        <v>28</v>
+      </c>
+      <c r="C593" t="s">
+        <v>196</v>
+      </c>
+      <c r="D593" t="s">
+        <v>802</v>
+      </c>
+      <c r="E593" t="s">
+        <v>492</v>
+      </c>
+      <c r="F593">
+        <v>1598</v>
+      </c>
+      <c r="G593">
+        <v>1600</v>
+      </c>
+      <c r="H593">
+        <v>2</v>
+      </c>
+      <c r="I593">
+        <v>0</v>
+      </c>
+      <c r="J593">
+        <v>3</v>
+      </c>
+      <c r="K593">
+        <v>0</v>
+      </c>
+      <c r="L593">
+        <v>0.67</v>
+      </c>
+      <c r="M593" t="s">
+        <v>777</v>
+      </c>
+      <c r="N593" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="594" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A594" t="s">
+        <v>733</v>
+      </c>
+      <c r="B594" t="s">
+        <v>28</v>
+      </c>
+      <c r="C594" t="s">
+        <v>196</v>
+      </c>
+      <c r="D594" t="s">
+        <v>806</v>
+      </c>
+      <c r="E594" t="s">
+        <v>492</v>
+      </c>
+      <c r="F594">
+        <v>1600</v>
+      </c>
+      <c r="G594">
+        <v>1602</v>
+      </c>
+      <c r="H594">
+        <v>2</v>
+      </c>
+      <c r="I594">
+        <v>0</v>
+      </c>
+      <c r="J594">
+        <v>3.04</v>
+      </c>
+      <c r="K594">
+        <v>0</v>
+      </c>
+      <c r="L594">
+        <v>0.66</v>
+      </c>
+      <c r="M594" t="s">
+        <v>778</v>
+      </c>
+      <c r="N594" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="595" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A595" t="s">
+        <v>733</v>
+      </c>
+      <c r="B595" t="s">
+        <v>28</v>
+      </c>
+      <c r="C595" t="s">
+        <v>196</v>
+      </c>
+      <c r="D595" t="s">
+        <v>720</v>
+      </c>
+      <c r="E595" t="s">
+        <v>492</v>
+      </c>
+      <c r="F595">
+        <v>1602</v>
+      </c>
+      <c r="G595">
+        <v>1604</v>
+      </c>
+      <c r="H595">
+        <v>2</v>
+      </c>
+      <c r="I595">
+        <v>0</v>
+      </c>
+      <c r="J595">
+        <v>3.04</v>
+      </c>
+      <c r="K595">
+        <v>0</v>
+      </c>
+      <c r="L595">
+        <v>0.66</v>
+      </c>
+      <c r="M595" t="s">
+        <v>779</v>
+      </c>
+      <c r="N595" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="596" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A596" t="s">
+        <v>735</v>
+      </c>
+      <c r="B596" t="s">
+        <v>28</v>
+      </c>
+      <c r="C596" t="s">
+        <v>196</v>
+      </c>
+      <c r="D596" t="s">
+        <v>804</v>
+      </c>
+      <c r="E596" t="s">
+        <v>492</v>
+      </c>
+      <c r="F596">
+        <v>1604</v>
+      </c>
+      <c r="G596">
+        <v>1606</v>
+      </c>
+      <c r="H596">
+        <v>2</v>
+      </c>
+      <c r="I596">
+        <v>0</v>
+      </c>
+      <c r="J596">
+        <v>3.1</v>
+      </c>
+      <c r="K596">
+        <v>0</v>
+      </c>
+      <c r="L596">
+        <v>0.65</v>
+      </c>
+      <c r="M596" t="s">
+        <v>780</v>
+      </c>
+      <c r="N596" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="597" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A597" t="s">
+        <v>735</v>
+      </c>
+      <c r="B597" t="s">
+        <v>28</v>
+      </c>
+      <c r="C597" t="s">
+        <v>196</v>
+      </c>
+      <c r="D597" t="s">
+        <v>714</v>
+      </c>
+      <c r="E597" t="s">
+        <v>492</v>
+      </c>
+      <c r="F597">
+        <v>1606</v>
+      </c>
+      <c r="G597">
+        <v>1609</v>
+      </c>
+      <c r="H597">
+        <v>3</v>
+      </c>
+      <c r="I597">
+        <v>0</v>
+      </c>
+      <c r="J597">
+        <v>3.11</v>
+      </c>
+      <c r="K597">
+        <v>0</v>
+      </c>
+      <c r="L597">
+        <v>0.97</v>
+      </c>
+      <c r="M597" t="s">
+        <v>781</v>
+      </c>
+      <c r="N597" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="598" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A598" t="s">
+        <v>735</v>
+      </c>
+      <c r="B598" t="s">
+        <v>28</v>
+      </c>
+      <c r="C598" t="s">
+        <v>196</v>
+      </c>
+      <c r="D598" t="s">
+        <v>706</v>
+      </c>
+      <c r="E598" t="s">
+        <v>492</v>
+      </c>
+      <c r="F598">
+        <v>1609</v>
+      </c>
+      <c r="G598">
+        <v>1612</v>
+      </c>
+      <c r="H598">
+        <v>3</v>
+      </c>
+      <c r="I598">
+        <v>0</v>
+      </c>
+      <c r="J598">
+        <v>3.09</v>
+      </c>
+      <c r="K598">
+        <v>0</v>
+      </c>
+      <c r="L598">
+        <v>0.97</v>
+      </c>
+      <c r="M598" t="s">
+        <v>782</v>
+      </c>
+      <c r="N598" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="599" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A599" t="s">
+        <v>735</v>
+      </c>
+      <c r="B599" t="s">
+        <v>28</v>
+      </c>
+      <c r="C599" t="s">
+        <v>196</v>
+      </c>
+      <c r="E599" t="s">
+        <v>310</v>
+      </c>
+      <c r="F599">
+        <v>1612</v>
+      </c>
+      <c r="G599">
+        <v>1614</v>
+      </c>
+      <c r="H599">
+        <v>2</v>
+      </c>
+      <c r="I599">
+        <v>0</v>
+      </c>
+      <c r="J599">
+        <v>0</v>
+      </c>
+      <c r="K599">
+        <v>0</v>
+      </c>
+      <c r="L599">
+        <v>0</v>
+      </c>
+      <c r="M599" t="s">
+        <v>783</v>
+      </c>
+      <c r="N599" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="600" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A600" t="s">
+        <v>736</v>
+      </c>
+      <c r="B600" t="s">
+        <v>28</v>
+      </c>
+      <c r="C600" t="s">
+        <v>196</v>
+      </c>
+      <c r="E600" t="s">
+        <v>171</v>
+      </c>
+      <c r="F600">
+        <v>1614</v>
+      </c>
+      <c r="G600">
+        <v>1614</v>
+      </c>
+      <c r="H600">
+        <v>0</v>
+      </c>
+      <c r="I600">
+        <v>112</v>
+      </c>
+      <c r="J600">
+        <v>0</v>
+      </c>
+      <c r="K600">
+        <v>0</v>
+      </c>
+      <c r="L600">
+        <v>0</v>
+      </c>
+      <c r="M600" t="s">
+        <v>171</v>
+      </c>
+      <c r="N600" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="601" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A601" t="s">
+        <v>737</v>
+      </c>
+      <c r="B601" t="s">
+        <v>28</v>
+      </c>
+      <c r="C601" t="s">
+        <v>196</v>
+      </c>
+      <c r="D601" t="s">
+        <v>713</v>
+      </c>
+      <c r="E601" t="s">
+        <v>492</v>
+      </c>
+      <c r="F601">
+        <v>1614</v>
+      </c>
+      <c r="G601">
+        <v>1617</v>
+      </c>
+      <c r="H601">
+        <v>3</v>
+      </c>
+      <c r="I601">
+        <v>0</v>
+      </c>
+      <c r="J601">
+        <v>3.03</v>
+      </c>
+      <c r="K601">
+        <v>0</v>
+      </c>
+      <c r="L601">
+        <v>0.99</v>
+      </c>
+      <c r="M601" t="s">
+        <v>784</v>
+      </c>
+      <c r="N601" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="602" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A602" t="s">
+        <v>737</v>
+      </c>
+      <c r="B602" t="s">
+        <v>28</v>
+      </c>
+      <c r="C602" t="s">
+        <v>196</v>
+      </c>
+      <c r="D602" t="s">
+        <v>807</v>
+      </c>
+      <c r="E602" t="s">
+        <v>492</v>
+      </c>
+      <c r="F602">
+        <v>1617</v>
+      </c>
+      <c r="G602">
+        <v>1620</v>
+      </c>
+      <c r="H602">
+        <v>3</v>
+      </c>
+      <c r="I602">
+        <v>0</v>
+      </c>
+      <c r="J602">
+        <v>3</v>
+      </c>
+      <c r="K602">
+        <v>0</v>
+      </c>
+      <c r="L602">
+        <v>1</v>
+      </c>
+      <c r="M602" t="s">
+        <v>785</v>
+      </c>
+      <c r="N602" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="603" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A603" t="s">
+        <v>737</v>
+      </c>
+      <c r="B603" t="s">
+        <v>28</v>
+      </c>
+      <c r="C603" t="s">
+        <v>196</v>
+      </c>
+      <c r="D603" t="s">
+        <v>805</v>
+      </c>
+      <c r="E603" t="s">
+        <v>492</v>
+      </c>
+      <c r="F603">
+        <v>1620</v>
+      </c>
+      <c r="G603">
+        <v>1622</v>
+      </c>
+      <c r="H603">
+        <v>2</v>
+      </c>
+      <c r="I603">
+        <v>0</v>
+      </c>
+      <c r="J603">
+        <v>3.04</v>
+      </c>
+      <c r="K603">
+        <v>0</v>
+      </c>
+      <c r="L603">
+        <v>0.66</v>
+      </c>
+      <c r="M603" t="s">
+        <v>786</v>
+      </c>
+      <c r="N603" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="604" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A604" t="s">
+        <v>737</v>
+      </c>
+      <c r="B604" t="s">
+        <v>28</v>
+      </c>
+      <c r="C604" t="s">
+        <v>196</v>
+      </c>
+      <c r="D604" t="s">
+        <v>721</v>
+      </c>
+      <c r="E604" t="s">
+        <v>492</v>
+      </c>
+      <c r="F604">
+        <v>1622</v>
+      </c>
+      <c r="G604">
+        <v>1624</v>
+      </c>
+      <c r="H604">
+        <v>2</v>
+      </c>
+      <c r="I604">
+        <v>0</v>
+      </c>
+      <c r="J604">
+        <v>3.04</v>
+      </c>
+      <c r="K604">
+        <v>0</v>
+      </c>
+      <c r="L604">
+        <v>0.66</v>
+      </c>
+      <c r="M604" t="s">
+        <v>787</v>
+      </c>
+      <c r="N604" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="605" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A605" t="s">
+        <v>738</v>
+      </c>
+      <c r="B605" t="s">
+        <v>28</v>
+      </c>
+      <c r="C605" t="s">
+        <v>196</v>
+      </c>
+      <c r="D605" t="s">
+        <v>715</v>
+      </c>
+      <c r="E605" t="s">
+        <v>492</v>
+      </c>
+      <c r="F605">
+        <v>1624</v>
+      </c>
+      <c r="G605">
+        <v>1626</v>
+      </c>
+      <c r="H605">
+        <v>2</v>
+      </c>
+      <c r="I605">
+        <v>0</v>
+      </c>
+      <c r="J605">
+        <v>1.75</v>
+      </c>
+      <c r="K605">
+        <v>0</v>
+      </c>
+      <c r="L605">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="M605" t="s">
+        <v>788</v>
+      </c>
+      <c r="N605" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="606" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A606" t="s">
+        <v>738</v>
+      </c>
+      <c r="B606" t="s">
+        <v>28</v>
+      </c>
+      <c r="C606" t="s">
+        <v>196</v>
+      </c>
+      <c r="D606" t="s">
+        <v>803</v>
+      </c>
+      <c r="E606" t="s">
+        <v>492</v>
+      </c>
+      <c r="F606">
+        <v>1626</v>
+      </c>
+      <c r="G606">
+        <v>1628</v>
+      </c>
+      <c r="H606">
+        <v>2</v>
+      </c>
+      <c r="I606">
+        <v>0</v>
+      </c>
+      <c r="J606">
+        <v>3.1</v>
+      </c>
+      <c r="K606">
+        <v>0</v>
+      </c>
+      <c r="L606">
+        <v>0.65</v>
+      </c>
+      <c r="M606" t="s">
+        <v>789</v>
+      </c>
+      <c r="N606" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="607" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A607" t="s">
+        <v>739</v>
+      </c>
+      <c r="B607" t="s">
+        <v>28</v>
+      </c>
+      <c r="C607" t="s">
+        <v>196</v>
+      </c>
+      <c r="D607" t="s">
+        <v>705</v>
+      </c>
+      <c r="E607" t="s">
+        <v>492</v>
+      </c>
+      <c r="F607">
+        <v>1628</v>
+      </c>
+      <c r="G607">
+        <v>1631</v>
+      </c>
+      <c r="H607">
+        <v>3</v>
+      </c>
+      <c r="I607">
+        <v>192</v>
+      </c>
+      <c r="J607">
+        <v>3.04</v>
+      </c>
+      <c r="K607">
+        <v>63.16</v>
+      </c>
+      <c r="L607">
+        <v>0.99</v>
+      </c>
+      <c r="M607" t="s">
+        <v>790</v>
+      </c>
+      <c r="N607" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="608" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A608" t="s">
+        <v>739</v>
+      </c>
+      <c r="B608" t="s">
+        <v>28</v>
+      </c>
+      <c r="C608" t="s">
+        <v>196</v>
+      </c>
+      <c r="D608" t="s">
+        <v>723</v>
+      </c>
+      <c r="E608" t="s">
+        <v>492</v>
+      </c>
+      <c r="F608">
+        <v>1631</v>
+      </c>
+      <c r="G608">
+        <v>1633</v>
+      </c>
+      <c r="H608">
+        <v>2</v>
+      </c>
+      <c r="I608">
+        <v>0</v>
+      </c>
+      <c r="J608">
+        <v>3.04</v>
+      </c>
+      <c r="K608">
+        <v>0</v>
+      </c>
+      <c r="L608">
+        <v>0.66</v>
+      </c>
+      <c r="M608" t="s">
+        <v>791</v>
+      </c>
+      <c r="N608" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="609" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A609" t="s">
+        <v>739</v>
+      </c>
+      <c r="B609" t="s">
+        <v>28</v>
+      </c>
+      <c r="C609" t="s">
+        <v>196</v>
+      </c>
+      <c r="D609" t="s">
+        <v>808</v>
+      </c>
+      <c r="E609" t="s">
+        <v>492</v>
+      </c>
+      <c r="F609">
+        <v>1633</v>
+      </c>
+      <c r="G609">
+        <v>1635</v>
+      </c>
+      <c r="H609">
+        <v>2</v>
+      </c>
+      <c r="I609">
+        <v>0</v>
+      </c>
+      <c r="J609">
+        <v>3.04</v>
+      </c>
+      <c r="K609">
+        <v>0</v>
+      </c>
+      <c r="L609">
+        <v>0.66</v>
+      </c>
+      <c r="M609" t="s">
+        <v>792</v>
+      </c>
+      <c r="N609" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="610" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A610" t="s">
+        <v>739</v>
+      </c>
+      <c r="B610" t="s">
+        <v>28</v>
+      </c>
+      <c r="C610" t="s">
+        <v>196</v>
+      </c>
+      <c r="D610" t="s">
+        <v>725</v>
+      </c>
+      <c r="E610" t="s">
+        <v>492</v>
+      </c>
+      <c r="F610">
+        <v>1635</v>
+      </c>
+      <c r="G610">
+        <v>1636</v>
+      </c>
+      <c r="H610">
+        <v>1</v>
+      </c>
+      <c r="I610">
+        <v>0</v>
+      </c>
+      <c r="J610">
+        <v>1.67</v>
+      </c>
+      <c r="K610">
+        <v>0</v>
+      </c>
+      <c r="L610">
+        <v>0.6</v>
+      </c>
+      <c r="M610" t="s">
+        <v>793</v>
+      </c>
+      <c r="N610" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="611" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A611" t="s">
+        <v>740</v>
+      </c>
+      <c r="B611" t="s">
+        <v>28</v>
+      </c>
+      <c r="C611" t="s">
+        <v>196</v>
+      </c>
+      <c r="D611" t="s">
+        <v>809</v>
+      </c>
+      <c r="E611" t="s">
+        <v>492</v>
+      </c>
+      <c r="F611">
+        <v>1636</v>
+      </c>
+      <c r="G611">
+        <v>1639</v>
+      </c>
+      <c r="H611">
+        <v>3</v>
+      </c>
+      <c r="I611">
+        <v>125</v>
+      </c>
+      <c r="J611">
+        <v>3.08</v>
+      </c>
+      <c r="K611">
+        <v>40.58</v>
+      </c>
+      <c r="L611">
+        <v>0.97</v>
+      </c>
+      <c r="M611" t="s">
+        <v>794</v>
+      </c>
+      <c r="N611" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="612" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A612" t="s">
+        <v>740</v>
+      </c>
+      <c r="B612" t="s">
+        <v>28</v>
+      </c>
+      <c r="C612" t="s">
+        <v>196</v>
+      </c>
+      <c r="D612" t="s">
+        <v>810</v>
+      </c>
+      <c r="E612" t="s">
+        <v>492</v>
+      </c>
+      <c r="F612">
+        <v>1639</v>
+      </c>
+      <c r="G612">
+        <v>1641</v>
+      </c>
+      <c r="H612">
+        <v>2</v>
+      </c>
+      <c r="I612">
+        <v>0</v>
+      </c>
+      <c r="J612">
+        <v>3.05</v>
+      </c>
+      <c r="K612">
+        <v>0</v>
+      </c>
+      <c r="L612">
+        <v>0.66</v>
+      </c>
+      <c r="M612" t="s">
+        <v>795</v>
+      </c>
+      <c r="N612" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="613" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A613" t="s">
+        <v>740</v>
+      </c>
+      <c r="B613" t="s">
+        <v>28</v>
+      </c>
+      <c r="C613" t="s">
+        <v>196</v>
+      </c>
+      <c r="D613" t="s">
+        <v>811</v>
+      </c>
+      <c r="E613" t="s">
+        <v>492</v>
+      </c>
+      <c r="F613">
+        <v>1641</v>
+      </c>
+      <c r="G613">
+        <v>1643</v>
+      </c>
+      <c r="H613">
+        <v>2</v>
+      </c>
+      <c r="I613">
+        <v>0</v>
+      </c>
+      <c r="J613">
+        <v>3.05</v>
+      </c>
+      <c r="K613">
+        <v>0</v>
+      </c>
+      <c r="L613">
+        <v>0.66</v>
+      </c>
+      <c r="M613" t="s">
+        <v>796</v>
+      </c>
+      <c r="N613" t="s">
+        <v>413</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
